--- a/_ForDRA/BVSimulationFiles/100.xlsx
+++ b/_ForDRA/BVSimulationFiles/100.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-4770" windowWidth="18240" windowHeight="28440" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="plot-data (6)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="plot-data (5)" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="18">
+  <fonts count="1">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -24,316 +24,16 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Display"/>
-      <family val="2"/>
-      <color theme="3"/>
-      <sz val="18"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <color rgb="FF9C5700"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.7999816888943144"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.5999938962981048"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.3999755851924192"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7999816888943144"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.5999938962981048"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.3999755851924192"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.7999816888943144"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.5999938962981048"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.3999755851924192"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.7999816888943144"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.5999938962981048"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.3999755851924192"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.7999816888943144"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.5999938962981048"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.3999755851924192"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.7999816888943144"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.5999938962981048"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.3999755851924192"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -341,204 +41,15 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.3999755851924192"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="42">
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6"/>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="8"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9"/>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Title" xfId="1" builtinId="15"/>
-    <cellStyle name="Heading 1" xfId="2" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="3" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="4" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="5" builtinId="19"/>
-    <cellStyle name="Good" xfId="6" builtinId="26"/>
-    <cellStyle name="Bad" xfId="7" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="8" builtinId="28"/>
-    <cellStyle name="Input" xfId="9" builtinId="20"/>
-    <cellStyle name="Output" xfId="10" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="11" builtinId="22"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24"/>
-    <cellStyle name="Check Cell" xfId="13" builtinId="23"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11"/>
-    <cellStyle name="Note" xfId="15" builtinId="10"/>
-    <cellStyle name="Explanatory Text" xfId="16" builtinId="53"/>
-    <cellStyle name="Total" xfId="17" builtinId="25"/>
-    <cellStyle name="Accent1" xfId="18" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="20" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="21" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="22" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="23" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="24" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="25" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="26" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="27" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="28" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="29" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="30" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="31" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="32" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="33" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="34" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="35" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="36" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="37" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="38" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="39" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="40" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="41" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -956,7 +467,7 @@
         <v>0.005921052631578947</v>
       </c>
       <c r="H1" t="n">
-        <v>0.007105263157894736</v>
+        <v>0.007105263157894737</v>
       </c>
       <c r="I1" t="n">
         <v>0.008289473684210525</v>
@@ -1003,4939 +514,4939 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.288841185822983e-08</v>
+        <v>0.1998776935824765</v>
       </c>
       <c r="C2" t="n">
-        <v>5.333590827430223e-08</v>
+        <v>0.2010184980346904</v>
       </c>
       <c r="D2" t="n">
-        <v>5.378719102154553e-08</v>
+        <v>0.2021658136426758</v>
       </c>
       <c r="E2" t="n">
-        <v>5.42422921366492e-08</v>
+        <v>0.2033196775689365</v>
       </c>
       <c r="F2" t="n">
-        <v>5.470124392736979e-08</v>
+        <v>0.2044801271880813</v>
       </c>
       <c r="G2" t="n">
-        <v>5.516407897482435e-08</v>
+        <v>0.2056472000880353</v>
       </c>
       <c r="H2" t="n">
-        <v>5.563083013580343e-08</v>
+        <v>0.2068209340712571</v>
       </c>
       <c r="I2" t="n">
-        <v>5.61015305451036e-08</v>
+        <v>0.2080013671559632</v>
       </c>
       <c r="J2" t="n">
-        <v>5.657621361787964e-08</v>
+        <v>0.2091885375773598</v>
       </c>
       <c r="K2" t="n">
-        <v>5.70549130520168e-08</v>
+        <v>0.2103824837888808</v>
       </c>
       <c r="L2" t="n">
-        <v>5.753766283052291e-08</v>
+        <v>0.2115832444634336</v>
       </c>
       <c r="M2" t="n">
-        <v>5.802449722394088e-08</v>
+        <v>0.2127908584946518</v>
       </c>
       <c r="N2" t="n">
-        <v>5.851545079278161e-08</v>
+        <v>0.2140053649981549</v>
       </c>
       <c r="O2" t="n">
-        <v>5.901055838997743e-08</v>
+        <v>0.2152268033128151</v>
       </c>
       <c r="P2" t="n">
-        <v>5.950985516335629e-08</v>
+        <v>0.2164552130020317</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.001337655813693e-08</v>
+        <v>0.2176906338550132</v>
       </c>
       <c r="R2" t="n">
-        <v>6.05211583194452e-08</v>
+        <v>0.2189331058880646</v>
       </c>
       <c r="S2" t="n">
-        <v>6.103323649485155e-08</v>
+        <v>0.2201826693458851</v>
       </c>
       <c r="T2" t="n">
-        <v>6.154964743693007e-08</v>
+        <v>0.2214393647028708</v>
       </c>
       <c r="U2" t="n">
-        <v>6.207042780583918e-08</v>
+        <v>0.222703232664426</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.01205808080808071</v>
+        <v>0.01701781970649904</v>
       </c>
       <c r="B3" t="n">
-        <v>5.334044956641974e-08</v>
+        <v>0.2005765666369608</v>
       </c>
       <c r="C3" t="n">
-        <v>5.379177073818506e-08</v>
+        <v>0.2017213599159306</v>
       </c>
       <c r="D3" t="n">
-        <v>5.424691060292616e-08</v>
+        <v>0.202872687116951</v>
       </c>
       <c r="E3" t="n">
-        <v>5.470590147115038e-08</v>
+        <v>0.2040305855324643</v>
       </c>
       <c r="F3" t="n">
-        <v>5.516877592674893e-08</v>
+        <v>0.20519509266776</v>
       </c>
       <c r="G3" t="n">
-        <v>5.563556682930993e-08</v>
+        <v>0.2063662462421893</v>
       </c>
       <c r="H3" t="n">
-        <v>5.610630731645123e-08</v>
+        <v>0.2075440841903874</v>
       </c>
       <c r="I3" t="n">
-        <v>5.658103080617276e-08</v>
+        <v>0.2087286446635016</v>
       </c>
       <c r="J3" t="n">
-        <v>5.705977099922894e-08</v>
+        <v>0.2099199660304276</v>
       </c>
       <c r="K3" t="n">
-        <v>5.754256188152111e-08</v>
+        <v>0.2111180868790518</v>
       </c>
       <c r="L3" t="n">
-        <v>5.802943772651018e-08</v>
+        <v>0.2123230460175016</v>
       </c>
       <c r="M3" t="n">
-        <v>5.852043309764968e-08</v>
+        <v>0.2135348824754024</v>
       </c>
       <c r="N3" t="n">
-        <v>5.901558285083948e-08</v>
+        <v>0.2147536355051415</v>
       </c>
       <c r="O3" t="n">
-        <v>5.95149221369002e-08</v>
+        <v>0.2159793445831397</v>
       </c>
       <c r="P3" t="n">
-        <v>6.001848640406863e-08</v>
+        <v>0.2172120494111299</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.052631140051406e-08</v>
+        <v>0.2184517899174434</v>
       </c>
       <c r="R3" t="n">
-        <v>6.103843317687624e-08</v>
+        <v>0.2196986062583026</v>
       </c>
       <c r="S3" t="n">
-        <v>6.155488808882454e-08</v>
+        <v>0.2209525388191226</v>
       </c>
       <c r="T3" t="n">
-        <v>6.207571279963876e-08</v>
+        <v>0.222213628215818</v>
       </c>
       <c r="U3" t="n">
-        <v>6.260094428281205e-08</v>
+        <v>0.2234819152961199</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.0325568181818182</v>
+        <v>0.03503668763102729</v>
       </c>
       <c r="B4" t="n">
-        <v>5.334044956641974e-08</v>
+        <v>0.2005765666369608</v>
       </c>
       <c r="C4" t="n">
-        <v>5.379177073818506e-08</v>
+        <v>0.2017213599159306</v>
       </c>
       <c r="D4" t="n">
-        <v>5.424691060292616e-08</v>
+        <v>0.202872687116951</v>
       </c>
       <c r="E4" t="n">
-        <v>5.470590147115038e-08</v>
+        <v>0.2040305855324643</v>
       </c>
       <c r="F4" t="n">
-        <v>5.516877592674893e-08</v>
+        <v>0.20519509266776</v>
       </c>
       <c r="G4" t="n">
-        <v>5.563556682930993e-08</v>
+        <v>0.2063662462421893</v>
       </c>
       <c r="H4" t="n">
-        <v>5.610630731645123e-08</v>
+        <v>0.2075440841903874</v>
       </c>
       <c r="I4" t="n">
-        <v>5.658103080617276e-08</v>
+        <v>0.2087286446635016</v>
       </c>
       <c r="J4" t="n">
-        <v>5.705977099922894e-08</v>
+        <v>0.2099199660304276</v>
       </c>
       <c r="K4" t="n">
-        <v>5.754256188152111e-08</v>
+        <v>0.2111180868790518</v>
       </c>
       <c r="L4" t="n">
-        <v>5.802943772651018e-08</v>
+        <v>0.2123230460175016</v>
       </c>
       <c r="M4" t="n">
-        <v>5.852043309764968e-08</v>
+        <v>0.2135348824754024</v>
       </c>
       <c r="N4" t="n">
-        <v>5.901558285083948e-08</v>
+        <v>0.2147536355051415</v>
       </c>
       <c r="O4" t="n">
-        <v>5.95149221369002e-08</v>
+        <v>0.2159793445831397</v>
       </c>
       <c r="P4" t="n">
-        <v>6.001848640406863e-08</v>
+        <v>0.2172120494111299</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.052631140051406e-08</v>
+        <v>0.2184517899174434</v>
       </c>
       <c r="R4" t="n">
-        <v>6.103843317687624e-08</v>
+        <v>0.2196986062583026</v>
       </c>
       <c r="S4" t="n">
-        <v>6.155488808882454e-08</v>
+        <v>0.2209525388191226</v>
       </c>
       <c r="T4" t="n">
-        <v>6.207571279963876e-08</v>
+        <v>0.222213628215818</v>
       </c>
       <c r="U4" t="n">
-        <v>6.260094428281205e-08</v>
+        <v>0.2234819152961199</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.05064393939393943</v>
+        <v>0.05005241090146761</v>
       </c>
       <c r="B5" t="n">
-        <v>5.334044956641974e-08</v>
+        <v>0.2005765666369608</v>
       </c>
       <c r="C5" t="n">
-        <v>5.379177073818506e-08</v>
+        <v>0.2017213599159306</v>
       </c>
       <c r="D5" t="n">
-        <v>5.424691060292616e-08</v>
+        <v>0.202872687116951</v>
       </c>
       <c r="E5" t="n">
-        <v>5.470590147115038e-08</v>
+        <v>0.2040305855324643</v>
       </c>
       <c r="F5" t="n">
-        <v>5.516877592674893e-08</v>
+        <v>0.20519509266776</v>
       </c>
       <c r="G5" t="n">
-        <v>5.563556682930993e-08</v>
+        <v>0.2063662462421893</v>
       </c>
       <c r="H5" t="n">
-        <v>5.610630731645123e-08</v>
+        <v>0.2075440841903874</v>
       </c>
       <c r="I5" t="n">
-        <v>5.658103080617276e-08</v>
+        <v>0.2087286446635016</v>
       </c>
       <c r="J5" t="n">
-        <v>5.705977099922894e-08</v>
+        <v>0.2099199660304276</v>
       </c>
       <c r="K5" t="n">
-        <v>5.754256188152111e-08</v>
+        <v>0.2111180868790518</v>
       </c>
       <c r="L5" t="n">
-        <v>5.802943772651018e-08</v>
+        <v>0.2123230460175016</v>
       </c>
       <c r="M5" t="n">
-        <v>5.852043309764968e-08</v>
+        <v>0.2135348824754024</v>
       </c>
       <c r="N5" t="n">
-        <v>5.901558285083948e-08</v>
+        <v>0.2147536355051415</v>
       </c>
       <c r="O5" t="n">
-        <v>5.95149221369002e-08</v>
+        <v>0.2159793445831397</v>
       </c>
       <c r="P5" t="n">
-        <v>6.001848640406863e-08</v>
+        <v>0.2172120494111299</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.052631140051406e-08</v>
+        <v>0.2184517899174434</v>
       </c>
       <c r="R5" t="n">
-        <v>6.103843317687624e-08</v>
+        <v>0.2196986062583026</v>
       </c>
       <c r="S5" t="n">
-        <v>6.155488808882454e-08</v>
+        <v>0.2209525388191226</v>
       </c>
       <c r="T5" t="n">
-        <v>6.207571279963876e-08</v>
+        <v>0.222213628215818</v>
       </c>
       <c r="U5" t="n">
-        <v>6.260094428281205e-08</v>
+        <v>0.2234819152961199</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.07355429292929287</v>
+        <v>0.06606918238993716</v>
       </c>
       <c r="B6" t="n">
-        <v>5.311443071232474e-08</v>
+        <v>0.1998776935824765</v>
       </c>
       <c r="C6" t="n">
-        <v>5.356383950624359e-08</v>
+        <v>0.2010184980346904</v>
       </c>
       <c r="D6" t="n">
-        <v>5.40170508122358e-08</v>
+        <v>0.2021658136426758</v>
       </c>
       <c r="E6" t="n">
-        <v>5.447409680389975e-08</v>
+        <v>0.2033196775689365</v>
       </c>
       <c r="F6" t="n">
-        <v>5.493500992705931e-08</v>
+        <v>0.2044801271880813</v>
       </c>
       <c r="G6" t="n">
-        <v>5.53998229020671e-08</v>
+        <v>0.2056472000880353</v>
       </c>
       <c r="H6" t="n">
-        <v>5.586856872612728e-08</v>
+        <v>0.2068209340712571</v>
       </c>
       <c r="I6" t="n">
-        <v>5.634128067563813e-08</v>
+        <v>0.2080013671559632</v>
       </c>
       <c r="J6" t="n">
-        <v>5.681799230855424e-08</v>
+        <v>0.2091885375773598</v>
       </c>
       <c r="K6" t="n">
-        <v>5.72987374667689e-08</v>
+        <v>0.2103824837888808</v>
       </c>
       <c r="L6" t="n">
-        <v>5.77835502785165e-08</v>
+        <v>0.2115832444634336</v>
       </c>
       <c r="M6" t="n">
-        <v>5.827246516079524e-08</v>
+        <v>0.2127908584946518</v>
       </c>
       <c r="N6" t="n">
-        <v>5.876551682181049e-08</v>
+        <v>0.2140053649981549</v>
       </c>
       <c r="O6" t="n">
-        <v>5.926274026343876e-08</v>
+        <v>0.2152268033128151</v>
       </c>
       <c r="P6" t="n">
-        <v>5.97641707837124e-08</v>
+        <v>0.2164552130020317</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.026984397932545e-08</v>
+        <v>0.2176906338550132</v>
       </c>
       <c r="R6" t="n">
-        <v>6.077979574816067e-08</v>
+        <v>0.2189331058880646</v>
       </c>
       <c r="S6" t="n">
-        <v>6.129406229183799e-08</v>
+        <v>0.2201826693458851</v>
       </c>
       <c r="T6" t="n">
-        <v>6.181268011828436e-08</v>
+        <v>0.2214393647028708</v>
       </c>
       <c r="U6" t="n">
-        <v>6.233568604432556e-08</v>
+        <v>0.222703232664426</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.09043560606060608</v>
+        <v>0.0850890985324949</v>
       </c>
       <c r="B7" t="n">
-        <v>5.243637415003974e-08</v>
+        <v>0.1956844552555715</v>
       </c>
       <c r="C7" t="n">
-        <v>5.288004581041921e-08</v>
+        <v>0.1968013267472493</v>
       </c>
       <c r="D7" t="n">
-        <v>5.33274714401647e-08</v>
+        <v>0.1979245727970253</v>
       </c>
       <c r="E7" t="n">
-        <v>5.377868280214783e-08</v>
+        <v>0.19905422978777</v>
       </c>
       <c r="F7" t="n">
-        <v>5.423371192799047e-08</v>
+        <v>0.2001903343100097</v>
       </c>
       <c r="G7" t="n">
-        <v>5.469259112033857e-08</v>
+        <v>0.2013329231631115</v>
       </c>
       <c r="H7" t="n">
-        <v>5.515535295515545e-08</v>
+        <v>0.2024820333564754</v>
       </c>
       <c r="I7" t="n">
-        <v>5.562203028403424e-08</v>
+        <v>0.2036377021107332</v>
       </c>
       <c r="J7" t="n">
-        <v>5.609265623653014e-08</v>
+        <v>0.2047999668589537</v>
       </c>
       <c r="K7" t="n">
-        <v>5.656726422251228e-08</v>
+        <v>0.2059688652478553</v>
       </c>
       <c r="L7" t="n">
-        <v>5.704588793453543e-08</v>
+        <v>0.2071444351390259</v>
       </c>
       <c r="M7" t="n">
-        <v>5.752856135023189e-08</v>
+        <v>0.2083267146101486</v>
       </c>
       <c r="N7" t="n">
-        <v>5.801531873472355e-08</v>
+        <v>0.2095157419562355</v>
       </c>
       <c r="O7" t="n">
-        <v>5.850619464305444e-08</v>
+        <v>0.2107115556908679</v>
       </c>
       <c r="P7" t="n">
-        <v>5.900122392264374e-08</v>
+        <v>0.2119141945474437</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.950044171575958e-08</v>
+        <v>0.2131236974804324</v>
       </c>
       <c r="R7" t="n">
-        <v>6.000388346201393e-08</v>
+        <v>0.2143401036666366</v>
       </c>
       <c r="S7" t="n">
-        <v>6.051158490087836e-08</v>
+        <v>0.215563452506461</v>
       </c>
       <c r="T7" t="n">
-        <v>6.102358207422115e-08</v>
+        <v>0.2167937836251883</v>
       </c>
       <c r="U7" t="n">
-        <v>6.153991132886609e-08</v>
+        <v>0.2180311368742632</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.104905303030303</v>
+        <v>0.09910377358490574</v>
       </c>
       <c r="B8" t="n">
-        <v>5.175831758775474e-08</v>
+        <v>0.1935878360921187</v>
       </c>
       <c r="C8" t="n">
-        <v>5.219625211459482e-08</v>
+        <v>0.1946927411035286</v>
       </c>
       <c r="D8" t="n">
-        <v>5.26378920680936e-08</v>
+        <v>0.1958039523741998</v>
       </c>
       <c r="E8" t="n">
-        <v>5.308326880039591e-08</v>
+        <v>0.1969215058971866</v>
       </c>
       <c r="F8" t="n">
-        <v>5.353241392892162e-08</v>
+        <v>0.1980454378709736</v>
       </c>
       <c r="G8" t="n">
-        <v>5.398535933861005e-08</v>
+        <v>0.1991757847006494</v>
       </c>
       <c r="H8" t="n">
-        <v>5.444213718418361e-08</v>
+        <v>0.2003125829990844</v>
       </c>
       <c r="I8" t="n">
-        <v>5.490277989243035e-08</v>
+        <v>0.201455869588118</v>
       </c>
       <c r="J8" t="n">
-        <v>5.536732016450605e-08</v>
+        <v>0.2026056814997504</v>
       </c>
       <c r="K8" t="n">
-        <v>5.583579097825566e-08</v>
+        <v>0.2037620559773424</v>
       </c>
       <c r="L8" t="n">
-        <v>5.630822559055437e-08</v>
+        <v>0.2049250304768219</v>
       </c>
       <c r="M8" t="n">
-        <v>5.678465753966854e-08</v>
+        <v>0.2060946426678969</v>
       </c>
       <c r="N8" t="n">
-        <v>5.72651206476366e-08</v>
+        <v>0.2072709304352757</v>
       </c>
       <c r="O8" t="n">
-        <v>5.774964902267012e-08</v>
+        <v>0.2084539318798942</v>
       </c>
       <c r="P8" t="n">
-        <v>5.823827706157507e-08</v>
+        <v>0.2096436853201495</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.873103945219373e-08</v>
+        <v>0.2108402292931419</v>
       </c>
       <c r="R8" t="n">
-        <v>5.922797117586721e-08</v>
+        <v>0.2120436025559225</v>
       </c>
       <c r="S8" t="n">
-        <v>5.972910750991873e-08</v>
+        <v>0.2132538440867487</v>
       </c>
       <c r="T8" t="n">
-        <v>6.023448403015795e-08</v>
+        <v>0.2144709930863468</v>
       </c>
       <c r="U8" t="n">
-        <v>6.07441366134066e-08</v>
+        <v>0.2156950889791817</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.119375</v>
+        <v>0.1151205450733754</v>
       </c>
       <c r="B9" t="n">
-        <v>5.085424217137484e-08</v>
+        <v>0.1886957247107297</v>
       </c>
       <c r="C9" t="n">
-        <v>5.128452718682907e-08</v>
+        <v>0.1897727079348477</v>
       </c>
       <c r="D9" t="n">
-        <v>5.171845290533223e-08</v>
+        <v>0.1908558380542745</v>
       </c>
       <c r="E9" t="n">
-        <v>5.215605013139346e-08</v>
+        <v>0.1919451501524927</v>
       </c>
       <c r="F9" t="n">
-        <v>5.259734993016326e-08</v>
+        <v>0.1930406795132237</v>
       </c>
       <c r="G9" t="n">
-        <v>5.30423836296388e-08</v>
+        <v>0.1941424616215719</v>
       </c>
       <c r="H9" t="n">
-        <v>5.349118282288792e-08</v>
+        <v>0.1952505321651729</v>
       </c>
       <c r="I9" t="n">
-        <v>5.394377937029192e-08</v>
+        <v>0.19636492703535</v>
       </c>
       <c r="J9" t="n">
-        <v>5.440020540180735e-08</v>
+        <v>0.1974856823282769</v>
       </c>
       <c r="K9" t="n">
-        <v>5.486049331924692e-08</v>
+        <v>0.1986128343461463</v>
       </c>
       <c r="L9" t="n">
-        <v>5.532467579857972e-08</v>
+        <v>0.1997464195983465</v>
       </c>
       <c r="M9" t="n">
-        <v>5.579278579225085e-08</v>
+        <v>0.2008864748026435</v>
       </c>
       <c r="N9" t="n">
-        <v>5.626485653152078e-08</v>
+        <v>0.2020330368863701</v>
       </c>
       <c r="O9" t="n">
-        <v>5.674092152882445e-08</v>
+        <v>0.2031861429876227</v>
       </c>
       <c r="P9" t="n">
-        <v>5.722101458015028e-08</v>
+        <v>0.2043458304564637</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.770516976743936e-08</v>
+        <v>0.2055121368561314</v>
       </c>
       <c r="R9" t="n">
-        <v>5.8193421461005e-08</v>
+        <v>0.2066850999642569</v>
       </c>
       <c r="S9" t="n">
-        <v>5.868580432197265e-08</v>
+        <v>0.2078647577740875</v>
       </c>
       <c r="T9" t="n">
-        <v>5.918235330474045e-08</v>
+        <v>0.2090511484957173</v>
       </c>
       <c r="U9" t="n">
-        <v>5.968310365946075e-08</v>
+        <v>0.2102443105573254</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.1350505050505049</v>
+        <v>0.1271331236897268</v>
       </c>
       <c r="B10" t="n">
-        <v>4.972414790089975e-08</v>
+        <v>0.186599105547277</v>
       </c>
       <c r="C10" t="n">
-        <v>5.014487102712166e-08</v>
+        <v>0.1876641222911269</v>
       </c>
       <c r="D10" t="n">
-        <v>5.056915395188032e-08</v>
+        <v>0.188735217631449</v>
       </c>
       <c r="E10" t="n">
-        <v>5.099702679514018e-08</v>
+        <v>0.1898124262619092</v>
       </c>
       <c r="F10" t="n">
-        <v>5.142851993171509e-08</v>
+        <v>0.1908957830741877</v>
       </c>
       <c r="G10" t="n">
-        <v>5.18636639934245e-08</v>
+        <v>0.1919853231591098</v>
       </c>
       <c r="H10" t="n">
-        <v>5.230248987126809e-08</v>
+        <v>0.1930810818077818</v>
       </c>
       <c r="I10" t="n">
-        <v>5.274502871761867e-08</v>
+        <v>0.1941830945127348</v>
       </c>
       <c r="J10" t="n">
-        <v>5.319131194843376e-08</v>
+        <v>0.1952913969690736</v>
       </c>
       <c r="K10" t="n">
-        <v>5.364137124548578e-08</v>
+        <v>0.1964060250756334</v>
       </c>
       <c r="L10" t="n">
-        <v>5.409523855861119e-08</v>
+        <v>0.1975270149361425</v>
       </c>
       <c r="M10" t="n">
-        <v>5.45529461079785e-08</v>
+        <v>0.1986544028603917</v>
       </c>
       <c r="N10" t="n">
-        <v>5.501452638637577e-08</v>
+        <v>0.1997882253654102</v>
       </c>
       <c r="O10" t="n">
-        <v>5.548001216151714e-08</v>
+        <v>0.2009285191766489</v>
       </c>
       <c r="P10" t="n">
-        <v>5.594943647836906e-08</v>
+        <v>0.2020753212291694</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.642283266149615e-08</v>
+        <v>0.2032286686688409</v>
       </c>
       <c r="R10" t="n">
-        <v>5.690023431742701e-08</v>
+        <v>0.2043885988535427</v>
       </c>
       <c r="S10" t="n">
-        <v>5.738167533703982e-08</v>
+        <v>0.2055551493543752</v>
       </c>
       <c r="T10" t="n">
-        <v>5.786718989796833e-08</v>
+        <v>0.2067283579568759</v>
       </c>
       <c r="U10" t="n">
-        <v>5.835681246702818e-08</v>
+        <v>0.2079082626622438</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.1531376262626256</v>
+        <v>0.1431498951781965</v>
       </c>
       <c r="B11" t="n">
-        <v>4.882007248451985e-08</v>
+        <v>0.1845024863838246</v>
       </c>
       <c r="C11" t="n">
-        <v>4.92331460993559e-08</v>
+        <v>0.1855555366474066</v>
       </c>
       <c r="D11" t="n">
-        <v>4.964971478911894e-08</v>
+        <v>0.186614597208624</v>
       </c>
       <c r="E11" t="n">
-        <v>5.006980812613773e-08</v>
+        <v>0.1876797023713262</v>
       </c>
       <c r="F11" t="n">
-        <v>5.049345593295673e-08</v>
+        <v>0.1887508866351521</v>
       </c>
       <c r="G11" t="n">
-        <v>5.092068828445324e-08</v>
+        <v>0.1898281846966481</v>
       </c>
       <c r="H11" t="n">
-        <v>5.135153550997239e-08</v>
+        <v>0.1909116314503913</v>
       </c>
       <c r="I11" t="n">
-        <v>5.178602819548024e-08</v>
+        <v>0.19200126199012</v>
       </c>
       <c r="J11" t="n">
-        <v>5.222419718573505e-08</v>
+        <v>0.1930971116098708</v>
       </c>
       <c r="K11" t="n">
-        <v>5.266607358647705e-08</v>
+        <v>0.1941992158051208</v>
       </c>
       <c r="L11" t="n">
-        <v>5.311168876663653e-08</v>
+        <v>0.1953076102739388</v>
       </c>
       <c r="M11" t="n">
-        <v>5.356107436056082e-08</v>
+        <v>0.1964223309181403</v>
       </c>
       <c r="N11" t="n">
-        <v>5.401426227025996e-08</v>
+        <v>0.1975434138444508</v>
       </c>
       <c r="O11" t="n">
-        <v>5.447128466767147e-08</v>
+        <v>0.1986708953656756</v>
       </c>
       <c r="P11" t="n">
-        <v>5.493217399694427e-08</v>
+        <v>0.1998048120018756</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.539696297674178e-08</v>
+        <v>0.2009452004815507</v>
       </c>
       <c r="R11" t="n">
-        <v>5.58656846025648e-08</v>
+        <v>0.202092097742829</v>
       </c>
       <c r="S11" t="n">
-        <v>5.633837214909374e-08</v>
+        <v>0.2032455409346633</v>
       </c>
       <c r="T11" t="n">
-        <v>5.681505917255083e-08</v>
+        <v>0.2044055674180348</v>
       </c>
       <c r="U11" t="n">
-        <v>5.729577951308232e-08</v>
+        <v>0.2055722147671626</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.1676073232323233</v>
+        <v>0.1581656184486361</v>
       </c>
       <c r="B12" t="n">
-        <v>4.814201592223485e-08</v>
+        <v>0.1796103750024353</v>
       </c>
       <c r="C12" t="n">
-        <v>4.854935240353152e-08</v>
+        <v>0.1806355034787253</v>
       </c>
       <c r="D12" t="n">
-        <v>4.896013541704785e-08</v>
+        <v>0.1816664828886983</v>
       </c>
       <c r="E12" t="n">
-        <v>4.937439412438582e-08</v>
+        <v>0.1827033466266318</v>
       </c>
       <c r="F12" t="n">
-        <v>4.979215793388788e-08</v>
+        <v>0.1837461282774017</v>
       </c>
       <c r="G12" t="n">
-        <v>5.021345650272473e-08</v>
+        <v>0.1847948616175702</v>
       </c>
       <c r="H12" t="n">
-        <v>5.063831973900056e-08</v>
+        <v>0.1858495806164793</v>
       </c>
       <c r="I12" t="n">
-        <v>5.106677780387636e-08</v>
+        <v>0.1869103194373516</v>
       </c>
       <c r="J12" t="n">
-        <v>5.149886111371096e-08</v>
+        <v>0.1879771124383968</v>
       </c>
       <c r="K12" t="n">
-        <v>5.193460034222042e-08</v>
+        <v>0.1890499941739244</v>
       </c>
       <c r="L12" t="n">
-        <v>5.237402642265548e-08</v>
+        <v>0.1901289993954631</v>
       </c>
       <c r="M12" t="n">
-        <v>5.281717054999747e-08</v>
+        <v>0.1912141630528865</v>
       </c>
       <c r="N12" t="n">
-        <v>5.326406418317301e-08</v>
+        <v>0.1923055202955448</v>
       </c>
       <c r="O12" t="n">
-        <v>5.371473904728714e-08</v>
+        <v>0.1934031064734038</v>
       </c>
       <c r="P12" t="n">
-        <v>5.41692271358756e-08</v>
+        <v>0.1945069571381894</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.462756071317592e-08</v>
+        <v>0.1956171080445398</v>
       </c>
       <c r="R12" t="n">
-        <v>5.508977231641807e-08</v>
+        <v>0.196733595151163</v>
       </c>
       <c r="S12" t="n">
-        <v>5.55558947581341e-08</v>
+        <v>0.1978564546220017</v>
       </c>
       <c r="T12" t="n">
-        <v>5.602596112848762e-08</v>
+        <v>0.198985722827405</v>
       </c>
       <c r="U12" t="n">
-        <v>5.650000479762285e-08</v>
+        <v>0.2001214363453059</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.1832828282828282</v>
+        <v>0.1721802935010471</v>
       </c>
       <c r="B13" t="n">
-        <v>4.791599706813976e-08</v>
+        <v>0.1796103750024353</v>
       </c>
       <c r="C13" t="n">
-        <v>4.832142117158996e-08</v>
+        <v>0.1806355034787253</v>
       </c>
       <c r="D13" t="n">
-        <v>4.873027562635739e-08</v>
+        <v>0.1816664828886983</v>
       </c>
       <c r="E13" t="n">
-        <v>4.914258945713508e-08</v>
+        <v>0.1827033466266318</v>
       </c>
       <c r="F13" t="n">
-        <v>4.955839193419818e-08</v>
+        <v>0.1837461282774017</v>
       </c>
       <c r="G13" t="n">
-        <v>4.997771257548179e-08</v>
+        <v>0.1847948616175702</v>
       </c>
       <c r="H13" t="n">
-        <v>5.040058114867652e-08</v>
+        <v>0.1858495806164793</v>
       </c>
       <c r="I13" t="n">
-        <v>5.082702767334162e-08</v>
+        <v>0.1869103194373516</v>
       </c>
       <c r="J13" t="n">
-        <v>5.125708242303615e-08</v>
+        <v>0.1879771124383968</v>
       </c>
       <c r="K13" t="n">
-        <v>5.16907759274681e-08</v>
+        <v>0.1890499941739244</v>
       </c>
       <c r="L13" t="n">
-        <v>5.212813897466168e-08</v>
+        <v>0.1901289993954631</v>
       </c>
       <c r="M13" t="n">
-        <v>5.256920261314293e-08</v>
+        <v>0.1912141630528865</v>
       </c>
       <c r="N13" t="n">
-        <v>5.301399815414392e-08</v>
+        <v>0.1923055202955448</v>
       </c>
       <c r="O13" t="n">
-        <v>5.34625571738256e-08</v>
+        <v>0.1934031064734038</v>
       </c>
       <c r="P13" t="n">
-        <v>5.391491151551926e-08</v>
+        <v>0.1945069571381894</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.437109329198719e-08</v>
+        <v>0.1956171080445398</v>
       </c>
       <c r="R13" t="n">
-        <v>5.483113488770238e-08</v>
+        <v>0.196733595151163</v>
       </c>
       <c r="S13" t="n">
-        <v>5.529506896114746e-08</v>
+        <v>0.1978564546220017</v>
       </c>
       <c r="T13" t="n">
-        <v>5.576292844713311e-08</v>
+        <v>0.198985722827405</v>
       </c>
       <c r="U13" t="n">
-        <v>5.623474655913624e-08</v>
+        <v>0.2001214363453059</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.1965467171717172</v>
+        <v>0.1881970649895168</v>
       </c>
       <c r="B14" t="n">
-        <v>4.791599706813976e-08</v>
+        <v>0.1803092480569195</v>
       </c>
       <c r="C14" t="n">
-        <v>4.832142117158996e-08</v>
+        <v>0.1813383653599655</v>
       </c>
       <c r="D14" t="n">
-        <v>4.873027562635739e-08</v>
+        <v>0.1823733563629734</v>
       </c>
       <c r="E14" t="n">
-        <v>4.914258945713508e-08</v>
+        <v>0.1834142545901597</v>
       </c>
       <c r="F14" t="n">
-        <v>4.955839193419818e-08</v>
+        <v>0.1844610937570804</v>
       </c>
       <c r="G14" t="n">
-        <v>4.997771257548179e-08</v>
+        <v>0.1855139077717242</v>
       </c>
       <c r="H14" t="n">
-        <v>5.040058114867652e-08</v>
+        <v>0.1865727307356096</v>
       </c>
       <c r="I14" t="n">
-        <v>5.082702767334162e-08</v>
+        <v>0.18763759694489</v>
       </c>
       <c r="J14" t="n">
-        <v>5.125708242303615e-08</v>
+        <v>0.1887085408914646</v>
       </c>
       <c r="K14" t="n">
-        <v>5.16907759274681e-08</v>
+        <v>0.1897855972640954</v>
       </c>
       <c r="L14" t="n">
-        <v>5.212813897466168e-08</v>
+        <v>0.1908688009495311</v>
       </c>
       <c r="M14" t="n">
-        <v>5.256920261314293e-08</v>
+        <v>0.1919581870336371</v>
       </c>
       <c r="N14" t="n">
-        <v>5.301399815414392e-08</v>
+        <v>0.1930537908025314</v>
       </c>
       <c r="O14" t="n">
-        <v>5.34625571738256e-08</v>
+        <v>0.1941556477437284</v>
       </c>
       <c r="P14" t="n">
-        <v>5.391491151551926e-08</v>
+        <v>0.1952637935472875</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.437109329198719e-08</v>
+        <v>0.19637826410697</v>
       </c>
       <c r="R14" t="n">
-        <v>5.483113488770238e-08</v>
+        <v>0.197499095521401</v>
       </c>
       <c r="S14" t="n">
-        <v>5.529506896114746e-08</v>
+        <v>0.1986263240952391</v>
       </c>
       <c r="T14" t="n">
-        <v>5.576292844713311e-08</v>
+        <v>0.1997599863403521</v>
       </c>
       <c r="U14" t="n">
-        <v>5.623474655913624e-08</v>
+        <v>0.2009001189769998</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.2110164141414135</v>
+        <v>0.2032127882599578</v>
       </c>
       <c r="B15" t="n">
-        <v>4.836803477632975e-08</v>
+        <v>0.1824058672203719</v>
       </c>
       <c r="C15" t="n">
-        <v>4.877728363547288e-08</v>
+        <v>0.1834469510036859</v>
       </c>
       <c r="D15" t="n">
-        <v>4.918999520773813e-08</v>
+        <v>0.1844939767857985</v>
       </c>
       <c r="E15" t="n">
-        <v>4.960619879163636e-08</v>
+        <v>0.1855469784807427</v>
       </c>
       <c r="F15" t="n">
-        <v>5.002592393357741e-08</v>
+        <v>0.1866059901961161</v>
       </c>
       <c r="G15" t="n">
-        <v>5.044920042996747e-08</v>
+        <v>0.187671046234186</v>
       </c>
       <c r="H15" t="n">
-        <v>5.087605832932441e-08</v>
+        <v>0.1887421810930002</v>
       </c>
       <c r="I15" t="n">
-        <v>5.130652793441089e-08</v>
+        <v>0.1898194294675048</v>
       </c>
       <c r="J15" t="n">
-        <v>5.174063980438556e-08</v>
+        <v>0.1909028262506675</v>
       </c>
       <c r="K15" t="n">
-        <v>5.217842475697252e-08</v>
+        <v>0.1919924065346079</v>
       </c>
       <c r="L15" t="n">
-        <v>5.261991387064905e-08</v>
+        <v>0.1930882056117348</v>
       </c>
       <c r="M15" t="n">
-        <v>5.306513848685182e-08</v>
+        <v>0.1941902589758885</v>
       </c>
       <c r="N15" t="n">
-        <v>5.351413021220188e-08</v>
+        <v>0.1952986023234909</v>
       </c>
       <c r="O15" t="n">
-        <v>5.396692092074848e-08</v>
+        <v>0.1964132715547018</v>
       </c>
       <c r="P15" t="n">
-        <v>5.442354275623171e-08</v>
+        <v>0.1975343027745814</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.488402813436444e-08</v>
+        <v>0.1986617322942602</v>
       </c>
       <c r="R15" t="n">
-        <v>5.534840974513354e-08</v>
+        <v>0.1997955966321148</v>
       </c>
       <c r="S15" t="n">
-        <v>5.581672055512055e-08</v>
+        <v>0.200935932514951</v>
       </c>
       <c r="T15" t="n">
-        <v>5.628899380984192e-08</v>
+        <v>0.2020827768791932</v>
       </c>
       <c r="U15" t="n">
-        <v>5.676526303610923e-08</v>
+        <v>0.203236166872081</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.2218686868686867</v>
+        <v>0.2172274633123688</v>
       </c>
       <c r="B16" t="n">
-        <v>4.972414790089975e-08</v>
+        <v>0.1879968516562455</v>
       </c>
       <c r="C16" t="n">
-        <v>5.014487102712166e-08</v>
+        <v>0.1890698460536074</v>
       </c>
       <c r="D16" t="n">
-        <v>5.056915395188032e-08</v>
+        <v>0.1901489645799994</v>
       </c>
       <c r="E16" t="n">
-        <v>5.099702679514018e-08</v>
+        <v>0.1912342421889648</v>
       </c>
       <c r="F16" t="n">
-        <v>5.142851993171509e-08</v>
+        <v>0.1923257140335451</v>
       </c>
       <c r="G16" t="n">
-        <v>5.18636639934245e-08</v>
+        <v>0.1934234154674178</v>
       </c>
       <c r="H16" t="n">
-        <v>5.230248987126809e-08</v>
+        <v>0.1945273820460426</v>
       </c>
       <c r="I16" t="n">
-        <v>5.274502871761867e-08</v>
+        <v>0.1956376495278116</v>
       </c>
       <c r="J16" t="n">
-        <v>5.319131194843376e-08</v>
+        <v>0.1967542538752091</v>
       </c>
       <c r="K16" t="n">
-        <v>5.364137124548578e-08</v>
+        <v>0.1978772312559753</v>
       </c>
       <c r="L16" t="n">
-        <v>5.409523855861119e-08</v>
+        <v>0.1990066180442785</v>
       </c>
       <c r="M16" t="n">
-        <v>5.45529461079785e-08</v>
+        <v>0.2001424508218929</v>
       </c>
       <c r="N16" t="n">
-        <v>5.501452638637577e-08</v>
+        <v>0.2012847663793835</v>
       </c>
       <c r="O16" t="n">
-        <v>5.548001216151714e-08</v>
+        <v>0.2024336017172982</v>
       </c>
       <c r="P16" t="n">
-        <v>5.594943647836906e-08</v>
+        <v>0.2035889940473656</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.642283266149615e-08</v>
+        <v>0.2047509807937013</v>
       </c>
       <c r="R16" t="n">
-        <v>5.690023431742701e-08</v>
+        <v>0.2059195995940189</v>
       </c>
       <c r="S16" t="n">
-        <v>5.738167533703982e-08</v>
+        <v>0.2070948883008501</v>
       </c>
       <c r="T16" t="n">
-        <v>5.786718989796833e-08</v>
+        <v>0.2082768849827702</v>
       </c>
       <c r="U16" t="n">
-        <v>5.835681246702818e-08</v>
+        <v>0.2094656279256315</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.2315151515151514</v>
+        <v>0.2272379454926623</v>
       </c>
       <c r="B17" t="n">
-        <v>5.085424217137484e-08</v>
+        <v>0.194286709146603</v>
       </c>
       <c r="C17" t="n">
-        <v>5.128452718682907e-08</v>
+        <v>0.1953956029847689</v>
       </c>
       <c r="D17" t="n">
-        <v>5.171845290533223e-08</v>
+        <v>0.196510825848475</v>
       </c>
       <c r="E17" t="n">
-        <v>5.215605013139346e-08</v>
+        <v>0.1976324138607144</v>
       </c>
       <c r="F17" t="n">
-        <v>5.259734993016326e-08</v>
+        <v>0.1987604033506523</v>
       </c>
       <c r="G17" t="n">
-        <v>5.30423836296388e-08</v>
+        <v>0.1998948308548034</v>
       </c>
       <c r="H17" t="n">
-        <v>5.349118282288792e-08</v>
+        <v>0.2010357331182148</v>
       </c>
       <c r="I17" t="n">
-        <v>5.394377937029192e-08</v>
+        <v>0.2021831470956564</v>
       </c>
       <c r="J17" t="n">
-        <v>5.440020540180735e-08</v>
+        <v>0.2033371099528182</v>
       </c>
       <c r="K17" t="n">
-        <v>5.486049331924692e-08</v>
+        <v>0.2044976590675134</v>
       </c>
       <c r="L17" t="n">
-        <v>5.532467579857972e-08</v>
+        <v>0.2056648320308899</v>
       </c>
       <c r="M17" t="n">
-        <v>5.579278579225085e-08</v>
+        <v>0.2068386666486474</v>
       </c>
       <c r="N17" t="n">
-        <v>5.626485653152078e-08</v>
+        <v>0.2080192009422623</v>
       </c>
       <c r="O17" t="n">
-        <v>5.674092152882445e-08</v>
+        <v>0.2092064731502187</v>
       </c>
       <c r="P17" t="n">
-        <v>5.722101458015028e-08</v>
+        <v>0.2104005217292475</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.770516976743936e-08</v>
+        <v>0.2116013853555721</v>
       </c>
       <c r="R17" t="n">
-        <v>5.8193421461005e-08</v>
+        <v>0.2128091029261605</v>
       </c>
       <c r="S17" t="n">
-        <v>5.868580432197265e-08</v>
+        <v>0.2140237135599861</v>
       </c>
       <c r="T17" t="n">
-        <v>5.918235330474045e-08</v>
+        <v>0.2152452565992939</v>
       </c>
       <c r="U17" t="n">
-        <v>5.968310365946075e-08</v>
+        <v>0.2164737716108755</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.2399558080808074</v>
+        <v>0.2412526205450733</v>
       </c>
       <c r="B18" t="n">
-        <v>5.221035529594483e-08</v>
+        <v>0.2019743127459289</v>
       </c>
       <c r="C18" t="n">
-        <v>5.265211457847784e-08</v>
+        <v>0.2031270836784107</v>
       </c>
       <c r="D18" t="n">
-        <v>5.309761164947443e-08</v>
+        <v>0.204286434065501</v>
       </c>
       <c r="E18" t="n">
-        <v>5.354687813489729e-08</v>
+        <v>0.2054524014595196</v>
       </c>
       <c r="F18" t="n">
-        <v>5.399994592830095e-08</v>
+        <v>0.206625023627117</v>
       </c>
       <c r="G18" t="n">
-        <v>5.445684719309583e-08</v>
+        <v>0.207804338550497</v>
       </c>
       <c r="H18" t="n">
-        <v>5.491761436483159e-08</v>
+        <v>0.2089903844286477</v>
       </c>
       <c r="I18" t="n">
-        <v>5.53822801534997e-08</v>
+        <v>0.2101831996785781</v>
       </c>
       <c r="J18" t="n">
-        <v>5.585087754585555e-08</v>
+        <v>0.2113828229365627</v>
       </c>
       <c r="K18" t="n">
-        <v>5.632343980776017e-08</v>
+        <v>0.2125892930593933</v>
       </c>
       <c r="L18" t="n">
-        <v>5.680000048654185e-08</v>
+        <v>0.2138026491256373</v>
       </c>
       <c r="M18" t="n">
-        <v>5.728059341337754e-08</v>
+        <v>0.2150229304369033</v>
       </c>
       <c r="N18" t="n">
-        <v>5.776525270569467e-08</v>
+        <v>0.2162501765191144</v>
       </c>
       <c r="O18" t="n">
-        <v>5.82540127695931e-08</v>
+        <v>0.2174844271237885</v>
       </c>
       <c r="P18" t="n">
-        <v>5.874690830228762e-08</v>
+        <v>0.2187257222293256</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.924397429457107e-08</v>
+        <v>0.2199741020423033</v>
       </c>
       <c r="R18" t="n">
-        <v>5.974524603329847e-08</v>
+        <v>0.2212296069987784</v>
       </c>
       <c r="S18" t="n">
-        <v>6.025075910389193e-08</v>
+        <v>0.222492277765597</v>
       </c>
       <c r="T18" t="n">
-        <v>6.076054939286687e-08</v>
+        <v>0.223762155241712</v>
       </c>
       <c r="U18" t="n">
-        <v>6.127465309037971e-08</v>
+        <v>0.2250392805595072</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.2483964646464649</v>
+        <v>0.2492610062893081</v>
       </c>
       <c r="B19" t="n">
-        <v>5.424452498279983e-08</v>
+        <v>0.2096619163452552</v>
       </c>
       <c r="C19" t="n">
-        <v>5.4703495665951e-08</v>
+        <v>0.2108585643720529</v>
       </c>
       <c r="D19" t="n">
-        <v>5.516634976568772e-08</v>
+        <v>0.2120620422825272</v>
       </c>
       <c r="E19" t="n">
-        <v>5.563312014015303e-08</v>
+        <v>0.2132723890583252</v>
       </c>
       <c r="F19" t="n">
-        <v>5.610383992550747e-08</v>
+        <v>0.2144896439035819</v>
       </c>
       <c r="G19" t="n">
-        <v>5.657854253828138e-08</v>
+        <v>0.215713846246191</v>
       </c>
       <c r="H19" t="n">
-        <v>5.705726167774711e-08</v>
+        <v>0.2169450357390809</v>
       </c>
       <c r="I19" t="n">
-        <v>5.754003132831138e-08</v>
+        <v>0.2181832522615</v>
       </c>
       <c r="J19" t="n">
-        <v>5.802688576192784e-08</v>
+        <v>0.2194285359203076</v>
       </c>
       <c r="K19" t="n">
-        <v>5.851785954053005e-08</v>
+        <v>0.2206809270512737</v>
       </c>
       <c r="L19" t="n">
-        <v>5.901298751848503e-08</v>
+        <v>0.221940466220385</v>
       </c>
       <c r="M19" t="n">
-        <v>5.951230484506757e-08</v>
+        <v>0.2232071942251594</v>
       </c>
       <c r="N19" t="n">
-        <v>6.00158469669555e-08</v>
+        <v>0.2244811520959668</v>
       </c>
       <c r="O19" t="n">
-        <v>6.052364963074608e-08</v>
+        <v>0.2257623810973586</v>
       </c>
       <c r="P19" t="n">
-        <v>6.103574888549362e-08</v>
+        <v>0.2270509227294041</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.155218108526865e-08</v>
+        <v>0.2283468187290349</v>
       </c>
       <c r="R19" t="n">
-        <v>6.207298289173867e-08</v>
+        <v>0.2296501110713965</v>
       </c>
       <c r="S19" t="n">
-        <v>6.259819127677083e-08</v>
+        <v>0.2309608419712083</v>
       </c>
       <c r="T19" t="n">
-        <v>6.312784352505647e-08</v>
+        <v>0.2322790538841304</v>
       </c>
       <c r="U19" t="n">
-        <v>6.366197723675814e-08</v>
+        <v>0.2336047895081393</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.2604545454545453</v>
+        <v>0.2582704402515716</v>
       </c>
       <c r="B20" t="n">
-        <v>5.650471352374973e-08</v>
+        <v>0.2187472660535493</v>
       </c>
       <c r="C20" t="n">
-        <v>5.698280798536554e-08</v>
+        <v>0.219995768828175</v>
       </c>
       <c r="D20" t="n">
-        <v>5.746494767259128e-08</v>
+        <v>0.2212513974481031</v>
       </c>
       <c r="E20" t="n">
-        <v>5.795116681265931e-08</v>
+        <v>0.2225141925841856</v>
       </c>
       <c r="F20" t="n">
-        <v>5.844149992240353e-08</v>
+        <v>0.2237841951394035</v>
       </c>
       <c r="G20" t="n">
-        <v>5.893598181070968e-08</v>
+        <v>0.2250614462501923</v>
       </c>
       <c r="H20" t="n">
-        <v>5.943464758098648e-08</v>
+        <v>0.2263459872877742</v>
       </c>
       <c r="I20" t="n">
-        <v>5.993753263365759e-08</v>
+        <v>0.2276378598594981</v>
       </c>
       <c r="J20" t="n">
-        <v>6.044467266867474e-08</v>
+        <v>0.2289371058101873</v>
       </c>
       <c r="K20" t="n">
-        <v>6.095610368805203e-08</v>
+        <v>0.2302437672234952</v>
       </c>
       <c r="L20" t="n">
-        <v>6.147186199842182e-08</v>
+        <v>0.2315578864232681</v>
       </c>
       <c r="M20" t="n">
-        <v>6.199198421361195e-08</v>
+        <v>0.232879505974916</v>
       </c>
       <c r="N20" t="n">
-        <v>6.251650725724522e-08</v>
+        <v>0.2342086686867917</v>
       </c>
       <c r="O20" t="n">
-        <v>6.304546836536039e-08</v>
+        <v>0.2355454176115772</v>
       </c>
       <c r="P20" t="n">
-        <v>6.357890508905576e-08</v>
+        <v>0.236889796047678</v>
       </c>
       <c r="Q20" t="n">
-        <v>6.411685529715473e-08</v>
+        <v>0.2382418475406261</v>
       </c>
       <c r="R20" t="n">
-        <v>6.465935717889433e-08</v>
+        <v>0.2396016158844901</v>
       </c>
       <c r="S20" t="n">
-        <v>6.520644924663616e-08</v>
+        <v>0.2409691451232937</v>
       </c>
       <c r="T20" t="n">
-        <v>6.57581703386004e-08</v>
+        <v>0.2423444795524424</v>
       </c>
       <c r="U20" t="n">
-        <v>6.631455962162295e-08</v>
+        <v>0.2437276637201584</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.27010101010101</v>
+        <v>0.2692819706498952</v>
       </c>
       <c r="B21" t="n">
-        <v>5.899092091879481e-08</v>
+        <v>0.2278326157618438</v>
       </c>
       <c r="C21" t="n">
-        <v>5.949005153672172e-08</v>
+        <v>0.2291329732842973</v>
       </c>
       <c r="D21" t="n">
-        <v>5.999340537018539e-08</v>
+        <v>0.2304407526136793</v>
       </c>
       <c r="E21" t="n">
-        <v>6.050101815241641e-08</v>
+        <v>0.2317559961100464</v>
       </c>
       <c r="F21" t="n">
-        <v>6.101292591898939e-08</v>
+        <v>0.2330787463752254</v>
       </c>
       <c r="G21" t="n">
-        <v>6.1529165010381e-08</v>
+        <v>0.234409046254194</v>
       </c>
       <c r="H21" t="n">
-        <v>6.204977207454999e-08</v>
+        <v>0.2357469388364677</v>
       </c>
       <c r="I21" t="n">
-        <v>6.257478406953863e-08</v>
+        <v>0.2370924674574964</v>
       </c>
       <c r="J21" t="n">
-        <v>6.310423826609652e-08</v>
+        <v>0.2384456757000674</v>
       </c>
       <c r="K21" t="n">
-        <v>6.363817225032643e-08</v>
+        <v>0.2398066073957171</v>
       </c>
       <c r="L21" t="n">
-        <v>6.417662392635248e-08</v>
+        <v>0.2411753066261514</v>
       </c>
       <c r="M21" t="n">
-        <v>6.471963151901099e-08</v>
+        <v>0.2425518177246729</v>
       </c>
       <c r="N21" t="n">
-        <v>6.52672335765641e-08</v>
+        <v>0.243936185277617</v>
       </c>
       <c r="O21" t="n">
-        <v>6.581946897343635e-08</v>
+        <v>0.2453284541257961</v>
       </c>
       <c r="P21" t="n">
-        <v>6.637637691297433e-08</v>
+        <v>0.2467286693659522</v>
       </c>
       <c r="Q21" t="n">
-        <v>6.693799693022965e-08</v>
+        <v>0.2481368763522177</v>
       </c>
       <c r="R21" t="n">
-        <v>6.75043688947658e-08</v>
+        <v>0.249553120697584</v>
       </c>
       <c r="S21" t="n">
-        <v>6.807553301348828e-08</v>
+        <v>0.2509774482753794</v>
       </c>
       <c r="T21" t="n">
-        <v>6.865152983349892e-08</v>
+        <v>0.2524099052207548</v>
       </c>
       <c r="U21" t="n">
-        <v>6.923240024497446e-08</v>
+        <v>0.2538505379321778</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.2845707070707063</v>
+        <v>0.2772903563941301</v>
       </c>
       <c r="B22" t="n">
-        <v>6.30592602925048e-08</v>
+        <v>0.236219092415654</v>
       </c>
       <c r="C22" t="n">
-        <v>6.359281371166805e-08</v>
+        <v>0.2375673158591794</v>
       </c>
       <c r="D22" t="n">
-        <v>6.413088160261197e-08</v>
+        <v>0.2389232343049804</v>
       </c>
       <c r="E22" t="n">
-        <v>6.467350216292789e-08</v>
+        <v>0.2402868916723794</v>
       </c>
       <c r="F22" t="n">
-        <v>6.522071391340244e-08</v>
+        <v>0.2416583321313687</v>
       </c>
       <c r="G22" t="n">
-        <v>6.577255570075211e-08</v>
+        <v>0.2430376001040416</v>
       </c>
       <c r="H22" t="n">
-        <v>6.632906670038101e-08</v>
+        <v>0.2444247402660309</v>
       </c>
       <c r="I22" t="n">
-        <v>6.689028641916199e-08</v>
+        <v>0.2458197975479564</v>
       </c>
       <c r="J22" t="n">
-        <v>6.74562546982411e-08</v>
+        <v>0.2472228171368797</v>
       </c>
       <c r="K22" t="n">
-        <v>6.802701171586618e-08</v>
+        <v>0.2486338444777681</v>
       </c>
       <c r="L22" t="n">
-        <v>6.860259799023885e-08</v>
+        <v>0.2500529252749669</v>
       </c>
       <c r="M22" t="n">
-        <v>6.918305438239105e-08</v>
+        <v>0.2514801054936793</v>
       </c>
       <c r="N22" t="n">
-        <v>6.976842209908577e-08</v>
+        <v>0.2529154313614556</v>
       </c>
       <c r="O22" t="n">
-        <v>7.035874269574231e-08</v>
+        <v>0.2543589493696904</v>
       </c>
       <c r="P22" t="n">
-        <v>7.095405807938634e-08</v>
+        <v>0.2558107062751283</v>
       </c>
       <c r="Q22" t="n">
-        <v>7.15544105116248e-08</v>
+        <v>0.2572707491013791</v>
       </c>
       <c r="R22" t="n">
-        <v>7.21598426116462e-08</v>
+        <v>0.2587391251404398</v>
       </c>
       <c r="S22" t="n">
-        <v>7.277039735924608e-08</v>
+        <v>0.2602158819542277</v>
       </c>
       <c r="T22" t="n">
-        <v>7.338611809787815e-08</v>
+        <v>0.26170106737612</v>
       </c>
       <c r="U22" t="n">
-        <v>7.400704853773132e-08</v>
+        <v>0.2631947295125033</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0.2954229797979795</v>
+        <v>0.2862997903563936</v>
       </c>
       <c r="B23" t="n">
-        <v>6.69015808121198e-08</v>
+        <v>0.2501965535053378</v>
       </c>
       <c r="C23" t="n">
-        <v>6.746764465467291e-08</v>
+        <v>0.251624553483983</v>
       </c>
       <c r="D23" t="n">
-        <v>6.803849804434818e-08</v>
+        <v>0.2530607037904823</v>
       </c>
       <c r="E23" t="n">
-        <v>6.861418150618873e-08</v>
+        <v>0.2545050509429345</v>
       </c>
       <c r="F23" t="n">
-        <v>6.919473590812588e-08</v>
+        <v>0.255957641724941</v>
       </c>
       <c r="G23" t="n">
-        <v>6.978020246388037e-08</v>
+        <v>0.2574185231871211</v>
       </c>
       <c r="H23" t="n">
-        <v>7.037062273588811e-08</v>
+        <v>0.2588877426486365</v>
       </c>
       <c r="I23" t="n">
-        <v>7.096603863825071e-08</v>
+        <v>0.2603653476987232</v>
       </c>
       <c r="J23" t="n">
-        <v>7.156649243971099e-08</v>
+        <v>0.2618513861982337</v>
       </c>
       <c r="K23" t="n">
-        <v>7.217202676665372e-08</v>
+        <v>0.2633459062811864</v>
       </c>
       <c r="L23" t="n">
-        <v>7.278268460613154e-08</v>
+        <v>0.264848956356326</v>
       </c>
       <c r="M23" t="n">
-        <v>7.339850930891667e-08</v>
+        <v>0.26636058510869</v>
       </c>
       <c r="N23" t="n">
-        <v>7.401954459257845e-08</v>
+        <v>0.2678808415011869</v>
       </c>
       <c r="O23" t="n">
-        <v>7.464583454458682e-08</v>
+        <v>0.2694097747761811</v>
       </c>
       <c r="P23" t="n">
-        <v>7.527742362544215e-08</v>
+        <v>0.2709474344570887</v>
       </c>
       <c r="Q23" t="n">
-        <v>7.591435667183132e-08</v>
+        <v>0.2724938703499815</v>
       </c>
       <c r="R23" t="n">
-        <v>7.655667889981103e-08</v>
+        <v>0.2740491325451997</v>
       </c>
       <c r="S23" t="n">
-        <v>7.720443590801736e-08</v>
+        <v>0.2756132714189751</v>
       </c>
       <c r="T23" t="n">
-        <v>7.785767368090299e-08</v>
+        <v>0.2771863376350621</v>
       </c>
       <c r="U23" t="n">
-        <v>7.851643859200169e-08</v>
+        <v>0.2787683821463794</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0.3014520202020198</v>
+        <v>0.2973113207547172</v>
       </c>
       <c r="B24" t="n">
-        <v>6.938778820716479e-08</v>
+        <v>0.2634751415405374</v>
       </c>
       <c r="C24" t="n">
-        <v>6.997488820602899e-08</v>
+        <v>0.2649789292275465</v>
       </c>
       <c r="D24" t="n">
-        <v>7.056695574194221e-08</v>
+        <v>0.2664912998017092</v>
       </c>
       <c r="E24" t="n">
-        <v>7.116403284594575e-08</v>
+        <v>0.2680123022499619</v>
       </c>
       <c r="F24" t="n">
-        <v>7.176616190471165e-08</v>
+        <v>0.2695419858388345</v>
       </c>
       <c r="G24" t="n">
-        <v>7.237338566355161e-08</v>
+        <v>0.2710804001160466</v>
       </c>
       <c r="H24" t="n">
-        <v>7.298574722945152e-08</v>
+        <v>0.2726275949121117</v>
       </c>
       <c r="I24" t="n">
-        <v>7.360329007413164e-08</v>
+        <v>0.2741836203419517</v>
       </c>
       <c r="J24" t="n">
-        <v>7.42260580371327e-08</v>
+        <v>0.2757485268065199</v>
       </c>
       <c r="K24" t="n">
-        <v>7.485409532892802e-08</v>
+        <v>0.2773223649944339</v>
       </c>
       <c r="L24" t="n">
-        <v>7.54874465340621e-08</v>
+        <v>0.2789051858836171</v>
       </c>
       <c r="M24" t="n">
-        <v>7.612615661431561e-08</v>
+        <v>0.2804970407429502</v>
       </c>
       <c r="N24" t="n">
-        <v>7.677027091189724e-08</v>
+        <v>0.2820979811339315</v>
       </c>
       <c r="O24" t="n">
-        <v>7.741983515266269e-08</v>
+        <v>0.2837080589123473</v>
       </c>
       <c r="P24" t="n">
-        <v>7.807489544936061e-08</v>
+        <v>0.2853273262299511</v>
       </c>
       <c r="Q24" t="n">
-        <v>7.873549830490615e-08</v>
+        <v>0.2869558355361538</v>
       </c>
       <c r="R24" t="n">
-        <v>7.940169061568239e-08</v>
+        <v>0.2885936395797216</v>
       </c>
       <c r="S24" t="n">
-        <v>8.007351967486937e-08</v>
+        <v>0.2902407914104851</v>
       </c>
       <c r="T24" t="n">
-        <v>8.075103317580142e-08</v>
+        <v>0.2918973443810572</v>
       </c>
       <c r="U24" t="n">
-        <v>8.143427921535312e-08</v>
+        <v>0.2935633521485617</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.3110984848484844</v>
+        <v>0.3063207547169807</v>
       </c>
       <c r="B25" t="n">
-        <v>7.232603331039977e-08</v>
+        <v>0.2739582373577999</v>
       </c>
       <c r="C25" t="n">
-        <v>7.2937994221268e-08</v>
+        <v>0.2755218574461489</v>
       </c>
       <c r="D25" t="n">
-        <v>7.355513302091695e-08</v>
+        <v>0.2770944019158353</v>
       </c>
       <c r="E25" t="n">
-        <v>7.417749352020403e-08</v>
+        <v>0.278675921702878</v>
       </c>
       <c r="F25" t="n">
-        <v>7.480511990067664e-08</v>
+        <v>0.2802664680340134</v>
       </c>
       <c r="G25" t="n">
-        <v>7.543805671770851e-08</v>
+        <v>0.281866092428356</v>
       </c>
       <c r="H25" t="n">
-        <v>7.607634890366282e-08</v>
+        <v>0.2834748466990655</v>
       </c>
       <c r="I25" t="n">
-        <v>7.672004177108185e-08</v>
+        <v>0.2850927829550264</v>
       </c>
       <c r="J25" t="n">
-        <v>7.736918101590379e-08</v>
+        <v>0.2867199536025351</v>
       </c>
       <c r="K25" t="n">
-        <v>7.802381272070674e-08</v>
+        <v>0.2883564113469974</v>
       </c>
       <c r="L25" t="n">
-        <v>7.868398335798005e-08</v>
+        <v>0.2900022091946362</v>
       </c>
       <c r="M25" t="n">
-        <v>7.934973979342344e-08</v>
+        <v>0.291657400454208</v>
       </c>
       <c r="N25" t="n">
-        <v>8.0021129289274e-08</v>
+        <v>0.2933220387387296</v>
       </c>
       <c r="O25" t="n">
-        <v>8.069819950766143e-08</v>
+        <v>0.294996177967215</v>
       </c>
       <c r="P25" t="n">
-        <v>8.138099851399152e-08</v>
+        <v>0.2966798723664211</v>
       </c>
       <c r="Q25" t="n">
-        <v>8.206957478035819e-08</v>
+        <v>0.2983731764726054</v>
       </c>
       <c r="R25" t="n">
-        <v>8.27639771889849e-08</v>
+        <v>0.3000761451332912</v>
       </c>
       <c r="S25" t="n">
-        <v>8.346425503569444e-08</v>
+        <v>0.3017888335090452</v>
       </c>
       <c r="T25" t="n">
-        <v>8.417045803340865e-08</v>
+        <v>0.3035112970752635</v>
       </c>
       <c r="U25" t="n">
-        <v>8.48826363156775e-08</v>
+        <v>0.3052435916239684</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0.3219507575757576</v>
+        <v>0.3143291404612155</v>
       </c>
       <c r="B26" t="n">
-        <v>7.662039153820476e-08</v>
+        <v>0.2851402062295471</v>
       </c>
       <c r="C26" t="n">
-        <v>7.72686876281558e-08</v>
+        <v>0.286767647545992</v>
       </c>
       <c r="D26" t="n">
-        <v>7.79224690440339e-08</v>
+        <v>0.288404377504237</v>
       </c>
       <c r="E26" t="n">
-        <v>7.858178219796616e-08</v>
+        <v>0.2900504491193223</v>
       </c>
       <c r="F26" t="n">
-        <v>7.924667389477932e-08</v>
+        <v>0.2917059157088714</v>
       </c>
       <c r="G26" t="n">
-        <v>7.991719133532244e-08</v>
+        <v>0.2933708308948197</v>
       </c>
       <c r="H26" t="n">
-        <v>8.059338211981778e-08</v>
+        <v>0.2950452486051501</v>
       </c>
       <c r="I26" t="n">
-        <v>8.127529425123982e-08</v>
+        <v>0.29672922307564</v>
       </c>
       <c r="J26" t="n">
-        <v>8.196297613872307e-08</v>
+        <v>0.2984228088516184</v>
       </c>
       <c r="K26" t="n">
-        <v>8.265647660099868e-08</v>
+        <v>0.3001260607897322</v>
       </c>
       <c r="L26" t="n">
-        <v>8.335584486986011e-08</v>
+        <v>0.3018390340597236</v>
       </c>
       <c r="M26" t="n">
-        <v>8.406113059365794e-08</v>
+        <v>0.3035617841462168</v>
       </c>
       <c r="N26" t="n">
-        <v>8.477238384082465e-08</v>
+        <v>0.3052943668505148</v>
       </c>
       <c r="O26" t="n">
-        <v>8.548965510342884e-08</v>
+        <v>0.3070368382924077</v>
       </c>
       <c r="P26" t="n">
-        <v>8.621299530075975e-08</v>
+        <v>0.3087892549119896</v>
       </c>
       <c r="Q26" t="n">
-        <v>8.694245578294196e-08</v>
+        <v>0.3105516734714875</v>
       </c>
       <c r="R26" t="n">
-        <v>8.767808833458087e-08</v>
+        <v>0.3123241510570993</v>
       </c>
       <c r="S26" t="n">
-        <v>8.841994517843879e-08</v>
+        <v>0.3141067450808432</v>
       </c>
       <c r="T26" t="n">
-        <v>8.916807897914227e-08</v>
+        <v>0.3158995132824173</v>
       </c>
       <c r="U26" t="n">
-        <v>8.992254284692086e-08</v>
+        <v>0.3177025137310694</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0.3315972222222223</v>
+        <v>0.3243396226415091</v>
       </c>
       <c r="B27" t="n">
-        <v>8.046271205781974e-08</v>
+        <v>0.2984187942647464</v>
       </c>
       <c r="C27" t="n">
-        <v>8.114351857116066e-08</v>
+        <v>0.3001220232895551</v>
       </c>
       <c r="D27" t="n">
-        <v>8.183008548577012e-08</v>
+        <v>0.3018349735154635</v>
       </c>
       <c r="E27" t="n">
-        <v>8.2522461541227e-08</v>
+        <v>0.3035577004263492</v>
       </c>
       <c r="F27" t="n">
-        <v>8.322069588950275e-08</v>
+        <v>0.3052902598227646</v>
       </c>
       <c r="G27" t="n">
-        <v>8.392483809845072e-08</v>
+        <v>0.3070327078237449</v>
       </c>
       <c r="H27" t="n">
-        <v>8.463493815532488e-08</v>
+        <v>0.3087851008686249</v>
       </c>
       <c r="I27" t="n">
-        <v>8.535104647032856e-08</v>
+        <v>0.3105474957188681</v>
       </c>
       <c r="J27" t="n">
-        <v>8.607321388019295e-08</v>
+        <v>0.3123199494599043</v>
       </c>
       <c r="K27" t="n">
-        <v>8.680149165178623e-08</v>
+        <v>0.3141025195029792</v>
       </c>
       <c r="L27" t="n">
-        <v>8.753593148575281e-08</v>
+        <v>0.3158952635870144</v>
       </c>
       <c r="M27" t="n">
-        <v>8.827658552018357e-08</v>
+        <v>0.3176982397804766</v>
       </c>
       <c r="N27" t="n">
-        <v>8.902350633431732e-08</v>
+        <v>0.319511506483259</v>
       </c>
       <c r="O27" t="n">
-        <v>8.977674695227334e-08</v>
+        <v>0.3213351224285734</v>
       </c>
       <c r="P27" t="n">
-        <v>9.053636084681554e-08</v>
+        <v>0.3231691466848515</v>
       </c>
       <c r="Q27" t="n">
-        <v>9.130240194314849e-08</v>
+        <v>0.3250136386576594</v>
       </c>
       <c r="R27" t="n">
-        <v>9.207492462274569e-08</v>
+        <v>0.3268686580916208</v>
       </c>
       <c r="S27" t="n">
-        <v>9.285398372721006e-08</v>
+        <v>0.3287342650723529</v>
       </c>
       <c r="T27" t="n">
-        <v>9.36396345621671e-08</v>
+        <v>0.330610520028412</v>
       </c>
       <c r="U27" t="n">
-        <v>9.443193290119123e-08</v>
+        <v>0.3324974837332513</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0.3424494949494942</v>
+        <v>0.3293448637316552</v>
       </c>
       <c r="B28" t="n">
-        <v>8.453105143152974e-08</v>
+        <v>0.3109985092454616</v>
       </c>
       <c r="C28" t="n">
-        <v>8.524628074610699e-08</v>
+        <v>0.3127735371518783</v>
       </c>
       <c r="D28" t="n">
-        <v>8.59675617181967e-08</v>
+        <v>0.3145586960524151</v>
       </c>
       <c r="E28" t="n">
-        <v>8.669494555173846e-08</v>
+        <v>0.3163540437698487</v>
       </c>
       <c r="F28" t="n">
-        <v>8.742848388391583e-08</v>
+        <v>0.3181596384569795</v>
       </c>
       <c r="G28" t="n">
-        <v>8.816822878882183e-08</v>
+        <v>0.3199755385985163</v>
       </c>
       <c r="H28" t="n">
-        <v>8.891423278115592e-08</v>
+        <v>0.3218018030129698</v>
       </c>
       <c r="I28" t="n">
-        <v>8.966654881995191e-08</v>
+        <v>0.323638490854558</v>
       </c>
       <c r="J28" t="n">
-        <v>9.042523031233755e-08</v>
+        <v>0.3254856616151227</v>
       </c>
       <c r="K28" t="n">
-        <v>9.1190331117326e-08</v>
+        <v>0.3273433751260557</v>
       </c>
       <c r="L28" t="n">
-        <v>9.196190554963918e-08</v>
+        <v>0.3292116915602374</v>
       </c>
       <c r="M28" t="n">
-        <v>9.274000838356363e-08</v>
+        <v>0.3310906714339861</v>
       </c>
       <c r="N28" t="n">
-        <v>9.352469485683898e-08</v>
+        <v>0.3329803756090171</v>
       </c>
       <c r="O28" t="n">
-        <v>9.43160206745793e-08</v>
+        <v>0.334880865294415</v>
       </c>
       <c r="P28" t="n">
-        <v>9.511404201322757e-08</v>
+        <v>0.3367922020486157</v>
       </c>
       <c r="Q28" t="n">
-        <v>9.591881552454363e-08</v>
+        <v>0.3387144477814015</v>
       </c>
       <c r="R28" t="n">
-        <v>9.673039833962609e-08</v>
+        <v>0.3406476647559045</v>
       </c>
       <c r="S28" t="n">
-        <v>9.754884807296787e-08</v>
+        <v>0.3425919155906253</v>
       </c>
       <c r="T28" t="n">
-        <v>9.837422282654633e-08</v>
+        <v>0.3445472632614597</v>
       </c>
       <c r="U28" t="n">
-        <v>9.920658119394808e-08</v>
+        <v>0.3465137711037397</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0.3508901515151515</v>
+        <v>0.33735324947589</v>
       </c>
       <c r="B29" t="n">
-        <v>8.814735309704972e-08</v>
+        <v>0.3200838589537561</v>
       </c>
       <c r="C29" t="n">
-        <v>8.889318045717038e-08</v>
+        <v>0.3219107416080007</v>
       </c>
       <c r="D29" t="n">
-        <v>8.964531836924254e-08</v>
+        <v>0.3237480512179913</v>
       </c>
       <c r="E29" t="n">
-        <v>9.040382022774867e-08</v>
+        <v>0.3255958472957095</v>
       </c>
       <c r="F29" t="n">
-        <v>9.116873987894966e-08</v>
+        <v>0.3274541896928014</v>
       </c>
       <c r="G29" t="n">
-        <v>9.194013162470726e-08</v>
+        <v>0.3293231386025181</v>
       </c>
       <c r="H29" t="n">
-        <v>9.271805022633907e-08</v>
+        <v>0.3312027545616633</v>
       </c>
       <c r="I29" t="n">
-        <v>9.3502550908506e-08</v>
+        <v>0.3330930984525564</v>
       </c>
       <c r="J29" t="n">
-        <v>9.429368936313273e-08</v>
+        <v>0.3349942315050028</v>
       </c>
       <c r="K29" t="n">
-        <v>9.509152175336132e-08</v>
+        <v>0.3369062152982776</v>
       </c>
       <c r="L29" t="n">
-        <v>9.589610471753819e-08</v>
+        <v>0.3388291117631209</v>
       </c>
       <c r="M29" t="n">
-        <v>9.670749537323481e-08</v>
+        <v>0.340762983183743</v>
       </c>
       <c r="N29" t="n">
-        <v>9.752575132130268e-08</v>
+        <v>0.3427078921998424</v>
       </c>
       <c r="O29" t="n">
-        <v>9.835093064996237e-08</v>
+        <v>0.3446639018086339</v>
       </c>
       <c r="P29" t="n">
-        <v>9.918309193892715e-08</v>
+        <v>0.34663107536689</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.000222942635615e-07</v>
+        <v>0.3486094765929931</v>
       </c>
       <c r="R29" t="n">
-        <v>1.008685971990753e-07</v>
+        <v>0.3505991695689985</v>
       </c>
       <c r="S29" t="n">
-        <v>1.017220608247526e-07</v>
+        <v>0.3526002187427111</v>
       </c>
       <c r="T29" t="n">
-        <v>1.025827457282168e-07</v>
+        <v>0.3546126889297722</v>
       </c>
       <c r="U29" t="n">
-        <v>1.03450713009732e-07</v>
+        <v>0.3566366453157591</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0.3617424242424234</v>
+        <v>0.3443605870020962</v>
       </c>
       <c r="B30" t="n">
-        <v>9.31197678871396e-08</v>
+        <v>0.3354590661524084</v>
       </c>
       <c r="C30" t="n">
-        <v>9.390766755988246e-08</v>
+        <v>0.3373737029952848</v>
       </c>
       <c r="D30" t="n">
-        <v>9.470223376443049e-08</v>
+        <v>0.3392992676520435</v>
       </c>
       <c r="E30" t="n">
-        <v>9.550352290726259e-08</v>
+        <v>0.3412358224933203</v>
       </c>
       <c r="F30" t="n">
-        <v>9.631159187212108e-08</v>
+        <v>0.3431834302457311</v>
       </c>
       <c r="G30" t="n">
-        <v>9.712649802404959e-08</v>
+        <v>0.3451421539939056</v>
       </c>
       <c r="H30" t="n">
-        <v>9.794829921346577e-08</v>
+        <v>0.3471120571825296</v>
       </c>
       <c r="I30" t="n">
-        <v>9.877705378026778e-08</v>
+        <v>0.3490932036184</v>
       </c>
       <c r="J30" t="n">
-        <v>9.961282055797602e-08</v>
+        <v>0.3510856574724922</v>
       </c>
       <c r="K30" t="n">
-        <v>1.004556588779098e-07</v>
+        <v>0.3530894832820379</v>
       </c>
       <c r="L30" t="n">
-        <v>1.013056285733992e-07</v>
+        <v>0.355104745952616</v>
       </c>
       <c r="M30" t="n">
-        <v>1.021627899840326e-07</v>
+        <v>0.3571315107602551</v>
       </c>
       <c r="N30" t="n">
-        <v>1.030272039599402e-07</v>
+        <v>0.3591698433535468</v>
       </c>
       <c r="O30" t="n">
-        <v>1.03898931866114e-07</v>
+        <v>0.3612198097557738</v>
       </c>
       <c r="P30" t="n">
-        <v>1.04778035586764e-07</v>
+        <v>0.3632814763670466</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.056645775297111e-07</v>
+        <v>0.3653549099664559</v>
       </c>
       <c r="R30" t="n">
-        <v>1.065586206308179e-07</v>
+        <v>0.3674401777142345</v>
       </c>
       <c r="S30" t="n">
-        <v>1.074602283584565e-07</v>
+        <v>0.3695373471539333</v>
       </c>
       <c r="T30" t="n">
-        <v>1.083694647180135e-07</v>
+        <v>0.3716464862146087</v>
       </c>
       <c r="U30" t="n">
-        <v>1.092863942564347e-07</v>
+        <v>0.3737676632130229</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0.3738005050505053</v>
+        <v>0.3543710691823898</v>
       </c>
       <c r="B31" t="n">
-        <v>9.809218267722876e-08</v>
+        <v>0.345942161969671</v>
       </c>
       <c r="C31" t="n">
-        <v>9.892215466259378e-08</v>
+        <v>0.3479166312138872</v>
       </c>
       <c r="D31" t="n">
-        <v>9.975914915961767e-08</v>
+        <v>0.3499023697661698</v>
       </c>
       <c r="E31" t="n">
-        <v>1.006032255867758e-07</v>
+        <v>0.3518994419462363</v>
       </c>
       <c r="F31" t="n">
-        <v>1.014544438652917e-07</v>
+        <v>0.35390791244091</v>
       </c>
       <c r="G31" t="n">
-        <v>1.023128644233912e-07</v>
+        <v>0.3559278463062149</v>
       </c>
       <c r="H31" t="n">
-        <v>1.031785482005917e-07</v>
+        <v>0.3579593089694834</v>
       </c>
       <c r="I31" t="n">
-        <v>1.040515566520288e-07</v>
+        <v>0.3600023662314749</v>
       </c>
       <c r="J31" t="n">
-        <v>1.049319517528185e-07</v>
+        <v>0.3620570842685074</v>
       </c>
       <c r="K31" t="n">
-        <v>1.058197960024575e-07</v>
+        <v>0.3641235296346014</v>
       </c>
       <c r="L31" t="n">
-        <v>1.067151524292594e-07</v>
+        <v>0.3662017692636351</v>
       </c>
       <c r="M31" t="n">
-        <v>1.076180845948295e-07</v>
+        <v>0.3682918704715128</v>
       </c>
       <c r="N31" t="n">
-        <v>1.085286565985768e-07</v>
+        <v>0.370393900958345</v>
       </c>
       <c r="O31" t="n">
-        <v>1.094469330822648e-07</v>
+        <v>0.3725079288106415</v>
       </c>
       <c r="P31" t="n">
-        <v>1.103729792345999e-07</v>
+        <v>0.3746340225035166</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.113068607958597e-07</v>
+        <v>0.3767722509029074</v>
       </c>
       <c r="R31" t="n">
-        <v>1.122486440625597e-07</v>
+        <v>0.3789226832678041</v>
       </c>
       <c r="S31" t="n">
-        <v>1.131983958921595e-07</v>
+        <v>0.3810853892524935</v>
       </c>
       <c r="T31" t="n">
-        <v>1.141561837078094e-07</v>
+        <v>0.383260438908815</v>
       </c>
       <c r="U31" t="n">
-        <v>1.151220755031365e-07</v>
+        <v>0.3854479026884297</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0.3810353535353528</v>
+        <v>0.3613784067085945</v>
       </c>
       <c r="B32" t="n">
-        <v>1.014824654886537e-07</v>
+        <v>0.3599196230593534</v>
       </c>
       <c r="C32" t="n">
-        <v>1.023411231417157e-07</v>
+        <v>0.3619738688386894</v>
       </c>
       <c r="D32" t="n">
-        <v>1.032070460199732e-07</v>
+        <v>0.3640398392516703</v>
       </c>
       <c r="E32" t="n">
-        <v>1.040802955955353e-07</v>
+        <v>0.36611760121679</v>
       </c>
       <c r="F32" t="n">
-        <v>1.049609338606359e-07</v>
+        <v>0.3682072220344808</v>
       </c>
       <c r="G32" t="n">
-        <v>1.058490233320338e-07</v>
+        <v>0.370308769389293</v>
       </c>
       <c r="H32" t="n">
-        <v>1.067446270554509e-07</v>
+        <v>0.3724223113520875</v>
       </c>
       <c r="I32" t="n">
-        <v>1.076478086100482e-07</v>
+        <v>0.3745479163822402</v>
       </c>
       <c r="J32" t="n">
-        <v>1.08558632112939e-07</v>
+        <v>0.3766856533298599</v>
       </c>
       <c r="K32" t="n">
-        <v>1.094771622237406e-07</v>
+        <v>0.3788355914380183</v>
       </c>
       <c r="L32" t="n">
-        <v>1.104034641491647e-07</v>
+        <v>0.3809978003449928</v>
       </c>
       <c r="M32" t="n">
-        <v>1.113376036476462e-07</v>
+        <v>0.3831723500865221</v>
       </c>
       <c r="N32" t="n">
-        <v>1.122796470340115e-07</v>
+        <v>0.3853593110980747</v>
       </c>
       <c r="O32" t="n">
-        <v>1.132296611841864e-07</v>
+        <v>0.3875587542171307</v>
       </c>
       <c r="P32" t="n">
-        <v>1.141877135399433e-07</v>
+        <v>0.3897707506854754</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.15153872113689e-07</v>
+        <v>0.3919953721515083</v>
       </c>
       <c r="R32" t="n">
-        <v>1.161282054932933e-07</v>
+        <v>0.3942326906725625</v>
       </c>
       <c r="S32" t="n">
-        <v>1.171107828469577e-07</v>
+        <v>0.3964827787172394</v>
       </c>
       <c r="T32" t="n">
-        <v>1.181016739281254e-07</v>
+        <v>0.3987457091677556</v>
       </c>
       <c r="U32" t="n">
-        <v>1.191009490804339e-07</v>
+        <v>0.4010215553223042</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0.3942992424242417</v>
+        <v>0.3693867924528294</v>
       </c>
       <c r="B33" t="n">
-        <v>1.062288614246487e-07</v>
+        <v>0.370402718876617</v>
       </c>
       <c r="C33" t="n">
-        <v>1.071276790124864e-07</v>
+        <v>0.372516797057293</v>
       </c>
       <c r="D33" t="n">
-        <v>1.080341016244708e-07</v>
+        <v>0.3746429413657975</v>
       </c>
       <c r="E33" t="n">
-        <v>1.089481936077987e-07</v>
+        <v>0.3767812206697072</v>
       </c>
       <c r="F33" t="n">
-        <v>1.098700198541178e-07</v>
+        <v>0.3789317042296607</v>
       </c>
       <c r="G33" t="n">
-        <v>1.107996458041334e-07</v>
+        <v>0.3810944617016034</v>
       </c>
       <c r="H33" t="n">
-        <v>1.117371374522538e-07</v>
+        <v>0.3832695631390424</v>
       </c>
       <c r="I33" t="n">
-        <v>1.126825613512755e-07</v>
+        <v>0.3854570789953161</v>
       </c>
       <c r="J33" t="n">
-        <v>1.136359846171077e-07</v>
+        <v>0.3876570801258762</v>
       </c>
       <c r="K33" t="n">
-        <v>1.14597474933537e-07</v>
+        <v>0.3898696377905829</v>
       </c>
       <c r="L33" t="n">
-        <v>1.155671005570322e-07</v>
+        <v>0.3920948236560129</v>
       </c>
       <c r="M33" t="n">
-        <v>1.165449303215896e-07</v>
+        <v>0.394332709797781</v>
       </c>
       <c r="N33" t="n">
-        <v>1.175310336436202e-07</v>
+        <v>0.396583368702874</v>
       </c>
       <c r="O33" t="n">
-        <v>1.185254805268767e-07</v>
+        <v>0.3988468732719996</v>
       </c>
       <c r="P33" t="n">
-        <v>1.19528341567424e-07</v>
+        <v>0.4011232968219465</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.2053968795865e-07</v>
+        <v>0.403412713087961</v>
       </c>
       <c r="R33" t="n">
-        <v>1.215595914963205e-07</v>
+        <v>0.4057151962261332</v>
       </c>
       <c r="S33" t="n">
-        <v>1.225881245836751e-07</v>
+        <v>0.4080308208158007</v>
       </c>
       <c r="T33" t="n">
-        <v>1.236253602365678e-07</v>
+        <v>0.410359661861963</v>
       </c>
       <c r="U33" t="n">
-        <v>1.246713720886502e-07</v>
+        <v>0.4127017947977121</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.4075631313131309</v>
+        <v>0.3743920335429768</v>
       </c>
       <c r="B34" t="n">
-        <v>1.116533139229287e-07</v>
+        <v>0.3787891955304258</v>
       </c>
       <c r="C34" t="n">
-        <v>1.125980285790815e-07</v>
+        <v>0.3809511396321736</v>
       </c>
       <c r="D34" t="n">
-        <v>1.135507366010396e-07</v>
+        <v>0.3831254230570971</v>
       </c>
       <c r="E34" t="n">
-        <v>1.14511505621814e-07</v>
+        <v>0.3853121162320388</v>
       </c>
       <c r="F34" t="n">
-        <v>1.154804038466686e-07</v>
+        <v>0.3875112899858026</v>
       </c>
       <c r="G34" t="n">
-        <v>1.164575000579615e-07</v>
+        <v>0.3897230155514497</v>
       </c>
       <c r="H34" t="n">
-        <v>1.174428636200285e-07</v>
+        <v>0.3919473645686042</v>
       </c>
       <c r="I34" t="n">
-        <v>1.184365644841066e-07</v>
+        <v>0.3941844090857746</v>
       </c>
       <c r="J34" t="n">
-        <v>1.194386731933005e-07</v>
+        <v>0.396434221562687</v>
       </c>
       <c r="K34" t="n">
-        <v>1.2044926088759e-07</v>
+        <v>0.3986968748726323</v>
       </c>
       <c r="L34" t="n">
-        <v>1.214683993088807e-07</v>
+        <v>0.4009724423048268</v>
       </c>
       <c r="M34" t="n">
-        <v>1.224961608060964e-07</v>
+        <v>0.4032609975667859</v>
       </c>
       <c r="N34" t="n">
-        <v>1.235326183403157e-07</v>
+        <v>0.4055626147867112</v>
       </c>
       <c r="O34" t="n">
-        <v>1.245778454899513e-07</v>
+        <v>0.4078773685158923</v>
       </c>
       <c r="P34" t="n">
-        <v>1.256319164559733e-07</v>
+        <v>0.4102053337311212</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.266949060671769e-07</v>
+        <v>0.4125465858371209</v>
       </c>
       <c r="R34" t="n">
-        <v>1.277668897854943e-07</v>
+        <v>0.4149012006689876</v>
       </c>
       <c r="S34" t="n">
-        <v>1.288479437113522e-07</v>
+        <v>0.4172692544946475</v>
       </c>
       <c r="T34" t="n">
-        <v>1.299381445890735e-07</v>
+        <v>0.4196508240173267</v>
       </c>
       <c r="U34" t="n">
-        <v>1.31037569812326e-07</v>
+        <v>0.4220459863780361</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0.4172095959595955</v>
+        <v>0.3864046121593291</v>
       </c>
       <c r="B35" t="n">
-        <v>1.152696155884496e-07</v>
+        <v>0.395562148838047</v>
       </c>
       <c r="C35" t="n">
-        <v>1.162449282901459e-07</v>
+        <v>0.3978198247819387</v>
       </c>
       <c r="D35" t="n">
-        <v>1.172284932520864e-07</v>
+        <v>0.4000903864397001</v>
       </c>
       <c r="E35" t="n">
-        <v>1.182203802978252e-07</v>
+        <v>0.4023739073567055</v>
       </c>
       <c r="F35" t="n">
-        <v>1.192206598417034e-07</v>
+        <v>0.4046704614980899</v>
       </c>
       <c r="G35" t="n">
-        <v>1.202294028938479e-07</v>
+        <v>0.4069801232511457</v>
       </c>
       <c r="H35" t="n">
-        <v>1.212466810652126e-07</v>
+        <v>0.4093029674277314</v>
       </c>
       <c r="I35" t="n">
-        <v>1.222725665726617e-07</v>
+        <v>0.4116390692666954</v>
       </c>
       <c r="J35" t="n">
-        <v>1.233071322440967e-07</v>
+        <v>0.4139885044363125</v>
       </c>
       <c r="K35" t="n">
-        <v>1.243504515236263e-07</v>
+        <v>0.416351349036735</v>
       </c>
       <c r="L35" t="n">
-        <v>1.254025984767807e-07</v>
+        <v>0.4187276796024584</v>
       </c>
       <c r="M35" t="n">
-        <v>1.264636477957686e-07</v>
+        <v>0.4211175731047994</v>
       </c>
       <c r="N35" t="n">
-        <v>1.275336748047804e-07</v>
+        <v>0.4235211069543893</v>
       </c>
       <c r="O35" t="n">
-        <v>1.286127554653354e-07</v>
+        <v>0.4259383590036818</v>
       </c>
       <c r="P35" t="n">
-        <v>1.29700966381674e-07</v>
+        <v>0.4283694075494743</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.307983848061959e-07</v>
+        <v>0.4308143313354445</v>
       </c>
       <c r="R35" t="n">
-        <v>1.319050886449447e-07</v>
+        <v>0.4332732095547001</v>
       </c>
       <c r="S35" t="n">
-        <v>1.33021156463138e-07</v>
+        <v>0.4357461218523449</v>
       </c>
       <c r="T35" t="n">
-        <v>1.34146667490745e-07</v>
+        <v>0.438233148328058</v>
       </c>
       <c r="U35" t="n">
-        <v>1.35281701628111e-07</v>
+        <v>0.4407343695386882</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0.429267676767676</v>
+        <v>0.3954140461215926</v>
       </c>
       <c r="B36" t="n">
-        <v>1.195639738162546e-07</v>
+        <v>0.412335102145668</v>
       </c>
       <c r="C36" t="n">
-        <v>1.205756216970337e-07</v>
+        <v>0.4146885099317036</v>
       </c>
       <c r="D36" t="n">
-        <v>1.215958292752033e-07</v>
+        <v>0.417055349822303</v>
       </c>
       <c r="E36" t="n">
-        <v>1.226246689755873e-07</v>
+        <v>0.4194356984813722</v>
       </c>
       <c r="F36" t="n">
-        <v>1.236622138358061e-07</v>
+        <v>0.4218296330103771</v>
       </c>
       <c r="G36" t="n">
-        <v>1.247085375114619e-07</v>
+        <v>0.4242372309508416</v>
       </c>
       <c r="H36" t="n">
-        <v>1.257637142813676e-07</v>
+        <v>0.4266585702868586</v>
       </c>
       <c r="I36" t="n">
-        <v>1.268278190528197e-07</v>
+        <v>0.4290937294476161</v>
       </c>
       <c r="J36" t="n">
-        <v>1.279009273669159e-07</v>
+        <v>0.4315427873099377</v>
       </c>
       <c r="K36" t="n">
-        <v>1.289831154039183e-07</v>
+        <v>0.4340058232008376</v>
       </c>
       <c r="L36" t="n">
-        <v>1.300744599886608e-07</v>
+        <v>0.4364829169000899</v>
       </c>
       <c r="M36" t="n">
-        <v>1.311750385960031e-07</v>
+        <v>0.4389741486428129</v>
       </c>
       <c r="N36" t="n">
-        <v>1.322849293563311e-07</v>
+        <v>0.4414795991220674</v>
       </c>
       <c r="O36" t="n">
-        <v>1.334042110611028e-07</v>
+        <v>0.4439993494914713</v>
       </c>
       <c r="P36" t="n">
-        <v>1.345329631684422e-07</v>
+        <v>0.4465334813678273</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.356712658087796e-07</v>
+        <v>0.4490820768337681</v>
       </c>
       <c r="R36" t="n">
-        <v>1.368191997905407e-07</v>
+        <v>0.4516452184404126</v>
       </c>
       <c r="S36" t="n">
-        <v>1.379768466058824e-07</v>
+        <v>0.4542229892100423</v>
       </c>
       <c r="T36" t="n">
-        <v>1.391442884364786e-07</v>
+        <v>0.4568154726387892</v>
       </c>
       <c r="U36" t="n">
-        <v>1.403216081593544e-07</v>
+        <v>0.45942275269934</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0.4401199494949493</v>
+        <v>0.4054245283018862</v>
       </c>
       <c r="B37" t="n">
-        <v>1.227282377735837e-07</v>
+        <v>0.4242159440718981</v>
       </c>
       <c r="C37" t="n">
-        <v>1.237666589442132e-07</v>
+        <v>0.4266371619127854</v>
       </c>
       <c r="D37" t="n">
-        <v>1.248138663448675e-07</v>
+        <v>0.4290721988849783</v>
       </c>
       <c r="E37" t="n">
-        <v>1.258699343170953e-07</v>
+        <v>0.4315211338613428</v>
       </c>
       <c r="F37" t="n">
-        <v>1.269349378314597e-07</v>
+        <v>0.4339840461649123</v>
       </c>
       <c r="G37" t="n">
-        <v>1.280089524928607e-07</v>
+        <v>0.436461015571458</v>
       </c>
       <c r="H37" t="n">
-        <v>1.290920545459019e-07</v>
+        <v>0.4389521223120719</v>
       </c>
       <c r="I37" t="n">
-        <v>1.301843208803035e-07</v>
+        <v>0.4414574470757666</v>
       </c>
       <c r="J37" t="n">
-        <v>1.312858290363607e-07</v>
+        <v>0.4439770710120873</v>
       </c>
       <c r="K37" t="n">
-        <v>1.323966572104482e-07</v>
+        <v>0.4465110757337419</v>
       </c>
       <c r="L37" t="n">
-        <v>1.335168842605714e-07</v>
+        <v>0.4490595433192439</v>
       </c>
       <c r="M37" t="n">
-        <v>1.346465897119644e-07</v>
+        <v>0.4516225563155707</v>
       </c>
       <c r="N37" t="n">
-        <v>1.357858537627358e-07</v>
+        <v>0.4542001977408376</v>
       </c>
       <c r="O37" t="n">
-        <v>1.36934757289562e-07</v>
+        <v>0.456792551086987</v>
       </c>
       <c r="P37" t="n">
-        <v>1.380933818534283e-07</v>
+        <v>0.4593997003224924</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.392618097054192e-07</v>
+        <v>0.4620217298950788</v>
       </c>
       <c r="R37" t="n">
-        <v>1.404401237925577e-07</v>
+        <v>0.4646587247344571</v>
       </c>
       <c r="S37" t="n">
-        <v>1.416284077636929e-07</v>
+        <v>0.4673107702550762</v>
       </c>
       <c r="T37" t="n">
-        <v>1.428267459754392e-07</v>
+        <v>0.4699779523588886</v>
       </c>
       <c r="U37" t="n">
-        <v>1.440352234981642e-07</v>
+        <v>0.4726603574381333</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0.4485606060606052</v>
+        <v>0.4114308176100622</v>
       </c>
       <c r="B38" t="n">
-        <v>1.254404640227237e-07</v>
+        <v>0.4381934051615829</v>
       </c>
       <c r="C38" t="n">
-        <v>1.265018337275108e-07</v>
+        <v>0.4406943995375902</v>
       </c>
       <c r="D38" t="n">
-        <v>1.275721838331519e-07</v>
+        <v>0.4432096683704814</v>
       </c>
       <c r="E38" t="n">
-        <v>1.286515903241029e-07</v>
+        <v>0.445739293131899</v>
       </c>
       <c r="F38" t="n">
-        <v>1.297401298277351e-07</v>
+        <v>0.4482833557584857</v>
       </c>
       <c r="G38" t="n">
-        <v>1.308378796197747e-07</v>
+        <v>0.4508419386545386</v>
       </c>
       <c r="H38" t="n">
-        <v>1.319449176297892e-07</v>
+        <v>0.4534151246946787</v>
       </c>
       <c r="I38" t="n">
-        <v>1.330613224467191e-07</v>
+        <v>0.4560029972265345</v>
       </c>
       <c r="J38" t="n">
-        <v>1.341871733244571e-07</v>
+        <v>0.4586056400734425</v>
       </c>
       <c r="K38" t="n">
-        <v>1.353225501874747e-07</v>
+        <v>0.4612231375371614</v>
       </c>
       <c r="L38" t="n">
-        <v>1.364675336364956e-07</v>
+        <v>0.4638555744006042</v>
       </c>
       <c r="M38" t="n">
-        <v>1.376222049542178e-07</v>
+        <v>0.4665030359305826</v>
       </c>
       <c r="N38" t="n">
-        <v>1.387866461110836e-07</v>
+        <v>0.46916560788057</v>
       </c>
       <c r="O38" t="n">
-        <v>1.399609397710993e-07</v>
+        <v>0.471843376493479</v>
       </c>
       <c r="P38" t="n">
-        <v>1.41145169297703e-07</v>
+        <v>0.4745364285044539</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.423394187596827e-07</v>
+        <v>0.4772448511436824</v>
       </c>
       <c r="R38" t="n">
-        <v>1.435437729371446e-07</v>
+        <v>0.4799687321392183</v>
       </c>
       <c r="S38" t="n">
-        <v>1.447583173275315e-07</v>
+        <v>0.4827081597198248</v>
       </c>
       <c r="T38" t="n">
-        <v>1.45983138151692e-07</v>
+        <v>0.485463222617832</v>
       </c>
       <c r="U38" t="n">
-        <v>1.472183223600021e-07</v>
+        <v>0.4882340100720106</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0.4582070707070698</v>
+        <v>0.4234433962264145</v>
       </c>
       <c r="B39" t="n">
-        <v>1.281526902718637e-07</v>
+        <v>0.4472787548698766</v>
       </c>
       <c r="C39" t="n">
-        <v>1.292370085108083e-07</v>
+        <v>0.4498316039937117</v>
       </c>
       <c r="D39" t="n">
-        <v>1.303305013214363e-07</v>
+        <v>0.4523990235360569</v>
       </c>
       <c r="E39" t="n">
-        <v>1.314332463311106e-07</v>
+        <v>0.4549810966577592</v>
       </c>
       <c r="F39" t="n">
-        <v>1.325453218240105e-07</v>
+        <v>0.4575779069943068</v>
       </c>
       <c r="G39" t="n">
-        <v>1.336668067466888e-07</v>
+        <v>0.4601895386585396</v>
       </c>
       <c r="H39" t="n">
-        <v>1.347977807136766e-07</v>
+        <v>0.4628160762433716</v>
       </c>
       <c r="I39" t="n">
-        <v>1.359383240131347e-07</v>
+        <v>0.4654576048245321</v>
       </c>
       <c r="J39" t="n">
-        <v>1.370885176125535e-07</v>
+        <v>0.4681142099633218</v>
       </c>
       <c r="K39" t="n">
-        <v>1.382484431645012e-07</v>
+        <v>0.4707859777093826</v>
       </c>
       <c r="L39" t="n">
-        <v>1.394181830124199e-07</v>
+        <v>0.4734729946034868</v>
       </c>
       <c r="M39" t="n">
-        <v>1.405978201964711e-07</v>
+        <v>0.4761753476803388</v>
       </c>
       <c r="N39" t="n">
-        <v>1.417874384594313e-07</v>
+        <v>0.4788931244713945</v>
       </c>
       <c r="O39" t="n">
-        <v>1.429871222526366e-07</v>
+        <v>0.481626413007697</v>
       </c>
       <c r="P39" t="n">
-        <v>1.441969567419777e-07</v>
+        <v>0.4843753018227275</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.454170278139461e-07</v>
+        <v>0.4871398799552732</v>
       </c>
       <c r="R39" t="n">
-        <v>1.466474220817316e-07</v>
+        <v>0.4899202369523113</v>
       </c>
       <c r="S39" t="n">
-        <v>1.4788822689137e-07</v>
+        <v>0.4927164628719097</v>
       </c>
       <c r="T39" t="n">
-        <v>1.491395303279448e-07</v>
+        <v>0.4955286482861435</v>
       </c>
       <c r="U39" t="n">
-        <v>1.5040142122184e-07</v>
+        <v>0.4983568842840292</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.4666477272727274</v>
+        <v>0.4354559748427667</v>
       </c>
       <c r="B40" t="n">
-        <v>1.299608411046246e-07</v>
+        <v>0.4640517081774979</v>
       </c>
       <c r="C40" t="n">
-        <v>1.310604583663409e-07</v>
+        <v>0.4667002891434768</v>
       </c>
       <c r="D40" t="n">
-        <v>1.321693796469602e-07</v>
+        <v>0.4693639869186598</v>
       </c>
       <c r="E40" t="n">
-        <v>1.332876836691166e-07</v>
+        <v>0.472042887782426</v>
       </c>
       <c r="F40" t="n">
-        <v>1.344154498215283e-07</v>
+        <v>0.4747370785065941</v>
       </c>
       <c r="G40" t="n">
-        <v>1.355527581646325e-07</v>
+        <v>0.4774466463582356</v>
       </c>
       <c r="H40" t="n">
-        <v>1.366996894362691e-07</v>
+        <v>0.4801716791024987</v>
       </c>
       <c r="I40" t="n">
-        <v>1.378563250574127e-07</v>
+        <v>0.4829122650054529</v>
       </c>
       <c r="J40" t="n">
-        <v>1.390227471379521e-07</v>
+        <v>0.4856684928369471</v>
       </c>
       <c r="K40" t="n">
-        <v>1.401990384825199e-07</v>
+        <v>0.4884404518734852</v>
       </c>
       <c r="L40" t="n">
-        <v>1.413852825963704e-07</v>
+        <v>0.4912282319011184</v>
       </c>
       <c r="M40" t="n">
-        <v>1.425815636913077e-07</v>
+        <v>0.4940319232183523</v>
       </c>
       <c r="N40" t="n">
-        <v>1.437879666916642e-07</v>
+        <v>0.4968516166390727</v>
       </c>
       <c r="O40" t="n">
-        <v>1.450045772403292e-07</v>
+        <v>0.4996874034954865</v>
       </c>
       <c r="P40" t="n">
-        <v>1.462314817048285e-07</v>
+        <v>0.5025393756410805</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.474687671834561e-07</v>
+        <v>0.505407625453597</v>
       </c>
       <c r="R40" t="n">
-        <v>1.487165215114572e-07</v>
+        <v>0.5082922458380239</v>
       </c>
       <c r="S40" t="n">
-        <v>1.499748332672635e-07</v>
+        <v>0.5111933302296072</v>
       </c>
       <c r="T40" t="n">
-        <v>1.512437917787811e-07</v>
+        <v>0.5141109725968747</v>
       </c>
       <c r="U40" t="n">
-        <v>1.52523487129733e-07</v>
+        <v>0.5170452674446812</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0.4787058080808078</v>
+        <v>0.447468553459119</v>
       </c>
       <c r="B41" t="n">
-        <v>1.322210296455746e-07</v>
+        <v>0.4780291692671791</v>
       </c>
       <c r="C41" t="n">
-        <v>1.333397706857556e-07</v>
+        <v>0.4807575267682779</v>
       </c>
       <c r="D41" t="n">
-        <v>1.344679775538638e-07</v>
+        <v>0.4835014564041591</v>
       </c>
       <c r="E41" t="n">
-        <v>1.35605730341623e-07</v>
+        <v>0.4862610470529785</v>
       </c>
       <c r="F41" t="n">
-        <v>1.367531098184245e-07</v>
+        <v>0.4890363881001639</v>
       </c>
       <c r="G41" t="n">
-        <v>1.379101974370609e-07</v>
+        <v>0.4918275694413125</v>
       </c>
       <c r="H41" t="n">
-        <v>1.390770753395086e-07</v>
+        <v>0.4946346814851016</v>
       </c>
       <c r="I41" t="n">
-        <v>1.40253826362759e-07</v>
+        <v>0.4974578151562171</v>
       </c>
       <c r="J41" t="n">
-        <v>1.414405340446991e-07</v>
+        <v>0.5002970618982985</v>
       </c>
       <c r="K41" t="n">
-        <v>1.42637282630042e-07</v>
+        <v>0.5031525136769009</v>
       </c>
       <c r="L41" t="n">
-        <v>1.438441570763073e-07</v>
+        <v>0.5060242629824747</v>
       </c>
       <c r="M41" t="n">
-        <v>1.450612430598522e-07</v>
+        <v>0.5089124028333604</v>
       </c>
       <c r="N41" t="n">
-        <v>1.46288626981954e-07</v>
+        <v>0.5118170267788011</v>
       </c>
       <c r="O41" t="n">
-        <v>1.475263959749436e-07</v>
+        <v>0.5147382289019745</v>
       </c>
       <c r="P41" t="n">
-        <v>1.487746379083907e-07</v>
+        <v>0.5176761038230381</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.500334413953423e-07</v>
+        <v>0.5206307467021964</v>
       </c>
       <c r="R41" t="n">
-        <v>1.51302895798613e-07</v>
+        <v>0.523602253242781</v>
       </c>
       <c r="S41" t="n">
-        <v>1.525830912371289e-07</v>
+        <v>0.5265907196943518</v>
       </c>
       <c r="T41" t="n">
-        <v>1.538741185923252e-07</v>
+        <v>0.5295962428558142</v>
       </c>
       <c r="U41" t="n">
-        <v>1.55176069514598e-07</v>
+        <v>0.5326189200785545</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0.4919696969696969</v>
+        <v>0.4584800838574427</v>
       </c>
       <c r="B42" t="n">
-        <v>1.344812181865236e-07</v>
+        <v>0.4864156459209915</v>
       </c>
       <c r="C42" t="n">
-        <v>1.356190830051693e-07</v>
+        <v>0.4891918693431622</v>
       </c>
       <c r="D42" t="n">
-        <v>1.367665754607665e-07</v>
+        <v>0.4919839380954625</v>
       </c>
       <c r="E42" t="n">
-        <v>1.379237770141284e-07</v>
+        <v>0.4947919426153137</v>
       </c>
       <c r="F42" t="n">
-        <v>1.390907698153197e-07</v>
+        <v>0.4976159738563092</v>
       </c>
       <c r="G42" t="n">
-        <v>1.402676367094883e-07</v>
+        <v>0.5004561232911624</v>
       </c>
       <c r="H42" t="n">
-        <v>1.414544612427471e-07</v>
+        <v>0.5033124829146671</v>
       </c>
       <c r="I42" t="n">
-        <v>1.426513276681043e-07</v>
+        <v>0.5061851452466793</v>
       </c>
       <c r="J42" t="n">
-        <v>1.438583209514451e-07</v>
+        <v>0.509074203335113</v>
       </c>
       <c r="K42" t="n">
-        <v>1.450755267775631e-07</v>
+        <v>0.5119797507589542</v>
       </c>
       <c r="L42" t="n">
-        <v>1.463030315562431e-07</v>
+        <v>0.5149018816312926</v>
       </c>
       <c r="M42" t="n">
-        <v>1.475409224283957e-07</v>
+        <v>0.517840690602369</v>
       </c>
       <c r="N42" t="n">
-        <v>1.487892872722428e-07</v>
+        <v>0.5207962728626422</v>
       </c>
       <c r="O42" t="n">
-        <v>1.500482147095569e-07</v>
+        <v>0.5237687241458712</v>
       </c>
       <c r="P42" t="n">
-        <v>1.513177941119519e-07</v>
+        <v>0.5267581407322167</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.525981156072275e-07</v>
+        <v>0.5297646194513602</v>
       </c>
       <c r="R42" t="n">
-        <v>1.538892700857677e-07</v>
+        <v>0.5327882576856393</v>
       </c>
       <c r="S42" t="n">
-        <v>1.551913492069933e-07</v>
+        <v>0.5358291533732025</v>
       </c>
       <c r="T42" t="n">
-        <v>1.565044454058681e-07</v>
+        <v>0.5388874050111818</v>
       </c>
       <c r="U42" t="n">
-        <v>1.578286518994618e-07</v>
+        <v>0.5419631116588824</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>0.50282196969697</v>
+        <v>0.470492662473795</v>
       </c>
       <c r="B43" t="n">
-        <v>1.353852936029046e-07</v>
+        <v>0.4961998686837701</v>
       </c>
       <c r="C43" t="n">
-        <v>1.36530807932936e-07</v>
+        <v>0.4990319356805247</v>
       </c>
       <c r="D43" t="n">
-        <v>1.376860146235289e-07</v>
+        <v>0.5018801667353139</v>
       </c>
       <c r="E43" t="n">
-        <v>1.388509956831319e-07</v>
+        <v>0.5047446541047023</v>
       </c>
       <c r="F43" t="n">
-        <v>1.400258338140791e-07</v>
+        <v>0.5076254905718099</v>
       </c>
       <c r="G43" t="n">
-        <v>1.412106124184606e-07</v>
+        <v>0.510522769449318</v>
       </c>
       <c r="H43" t="n">
-        <v>1.424054156040438e-07</v>
+        <v>0.5134365845824911</v>
       </c>
       <c r="I43" t="n">
-        <v>1.436103281902438e-07</v>
+        <v>0.5163670303522161</v>
       </c>
       <c r="J43" t="n">
-        <v>1.448254357141449e-07</v>
+        <v>0.5193142016780609</v>
       </c>
       <c r="K43" t="n">
-        <v>1.460508244365729e-07</v>
+        <v>0.522278194021347</v>
       </c>
       <c r="L43" t="n">
-        <v>1.472865813482189e-07</v>
+        <v>0.5252591033882439</v>
       </c>
       <c r="M43" t="n">
-        <v>1.485327941758145e-07</v>
+        <v>0.5282570263328765</v>
       </c>
       <c r="N43" t="n">
-        <v>1.497895513883598e-07</v>
+        <v>0.531272059960454</v>
       </c>
       <c r="O43" t="n">
-        <v>1.510569422034037e-07</v>
+        <v>0.5343043019304148</v>
       </c>
       <c r="P43" t="n">
-        <v>1.523350565933779e-07</v>
+        <v>0.5373538504595889</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.53623985291983e-07</v>
+        <v>0.540420804325382</v>
       </c>
       <c r="R43" t="n">
-        <v>1.549238198006311e-07</v>
+        <v>0.5435052628689712</v>
       </c>
       <c r="S43" t="n">
-        <v>1.562346523949405e-07</v>
+        <v>0.5466073259985257</v>
       </c>
       <c r="T43" t="n">
-        <v>1.575565761312868e-07</v>
+        <v>0.5497270941924413</v>
       </c>
       <c r="U43" t="n">
-        <v>1.588896848534088e-07</v>
+        <v>0.5528646685025956</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0.5172916666666664</v>
+        <v>0.4855083857442345</v>
       </c>
       <c r="B44" t="n">
-        <v>1.360633501651896e-07</v>
+        <v>0.5045863453375791</v>
       </c>
       <c r="C44" t="n">
-        <v>1.372146016287605e-07</v>
+        <v>0.5074662782554054</v>
       </c>
       <c r="D44" t="n">
-        <v>1.383755939956e-07</v>
+        <v>0.5103626484266135</v>
       </c>
       <c r="E44" t="n">
-        <v>1.395464096848838e-07</v>
+        <v>0.5132755496670339</v>
       </c>
       <c r="F44" t="n">
-        <v>1.407271318131479e-07</v>
+        <v>0.5162050763279518</v>
       </c>
       <c r="G44" t="n">
-        <v>1.419178442001891e-07</v>
+        <v>0.5191513232991644</v>
       </c>
       <c r="H44" t="n">
-        <v>1.431186313750157e-07</v>
+        <v>0.5221143860120528</v>
       </c>
       <c r="I44" t="n">
-        <v>1.443295785818477e-07</v>
+        <v>0.5250943604426747</v>
       </c>
       <c r="J44" t="n">
-        <v>1.45550771786169e-07</v>
+        <v>0.5280913431148717</v>
       </c>
       <c r="K44" t="n">
-        <v>1.467822976808296e-07</v>
+        <v>0.5311054311033966</v>
       </c>
       <c r="L44" t="n">
-        <v>1.480242436922e-07</v>
+        <v>0.5341367220370579</v>
       </c>
       <c r="M44" t="n">
-        <v>1.492766979863778e-07</v>
+        <v>0.5371853141018815</v>
       </c>
       <c r="N44" t="n">
-        <v>1.505397494754467e-07</v>
+        <v>0.5402513060442913</v>
       </c>
       <c r="O44" t="n">
-        <v>1.518134878237881e-07</v>
+        <v>0.5433347971743077</v>
       </c>
       <c r="P44" t="n">
-        <v>1.530980034544465e-07</v>
+        <v>0.5464358873687637</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.543933875555489e-07</v>
+        <v>0.5495546770745419</v>
       </c>
       <c r="R44" t="n">
-        <v>1.556997320867778e-07</v>
+        <v>0.5526912673118255</v>
       </c>
       <c r="S44" t="n">
-        <v>1.570171297859002e-07</v>
+        <v>0.5558457596773725</v>
       </c>
       <c r="T44" t="n">
-        <v>1.5834567417535e-07</v>
+        <v>0.559018256347805</v>
       </c>
       <c r="U44" t="n">
-        <v>1.596854595688683e-07</v>
+        <v>0.5622088600829197</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0.5317613636363626</v>
+        <v>0.5055293501048217</v>
       </c>
       <c r="B45" t="n">
-        <v>1.358373313110946e-07</v>
+        <v>0.5087795836644851</v>
       </c>
       <c r="C45" t="n">
-        <v>1.36986670396819e-07</v>
+        <v>0.5116834495428475</v>
       </c>
       <c r="D45" t="n">
-        <v>1.381457342049097e-07</v>
+        <v>0.5146038892722651</v>
       </c>
       <c r="E45" t="n">
-        <v>1.393146050176332e-07</v>
+        <v>0.5175409974482015</v>
       </c>
       <c r="F45" t="n">
-        <v>1.404933658134583e-07</v>
+        <v>0.5204948692060245</v>
       </c>
       <c r="G45" t="n">
-        <v>1.416821002729463e-07</v>
+        <v>0.5234656002240892</v>
       </c>
       <c r="H45" t="n">
-        <v>1.428808927846917e-07</v>
+        <v>0.5264532867268354</v>
       </c>
       <c r="I45" t="n">
-        <v>1.440898284513131e-07</v>
+        <v>0.5294580254879058</v>
       </c>
       <c r="J45" t="n">
-        <v>1.453089930954943e-07</v>
+        <v>0.532479913833279</v>
       </c>
       <c r="K45" t="n">
-        <v>1.465384732660773e-07</v>
+        <v>0.5355190496444231</v>
       </c>
       <c r="L45" t="n">
-        <v>1.477783562442063e-07</v>
+        <v>0.5385755313614667</v>
       </c>
       <c r="M45" t="n">
-        <v>1.490287300495234e-07</v>
+        <v>0.5416494579863859</v>
       </c>
       <c r="N45" t="n">
-        <v>1.502896834464177e-07</v>
+        <v>0.5447409290862117</v>
       </c>
       <c r="O45" t="n">
-        <v>1.515613059503266e-07</v>
+        <v>0.5478500447962559</v>
       </c>
       <c r="P45" t="n">
-        <v>1.528436878340903e-07</v>
+        <v>0.5509769058233529</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.541369201343602e-07</v>
+        <v>0.5541216134491237</v>
       </c>
       <c r="R45" t="n">
-        <v>1.554410946580622e-07</v>
+        <v>0.5572842695332546</v>
       </c>
       <c r="S45" t="n">
-        <v>1.567563039889136e-07</v>
+        <v>0.5604649765167978</v>
       </c>
       <c r="T45" t="n">
-        <v>1.580826414939956e-07</v>
+        <v>0.5636638374254888</v>
       </c>
       <c r="U45" t="n">
-        <v>1.594202013303818e-07</v>
+        <v>0.5668809558730836</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>0.5462310606060603</v>
+        <v>0.5175419287211739</v>
       </c>
       <c r="B46" t="n">
-        <v>1.342551993324296e-07</v>
+        <v>0.5101773297734515</v>
       </c>
       <c r="C46" t="n">
-        <v>1.353911517732287e-07</v>
+        <v>0.513089173305326</v>
       </c>
       <c r="D46" t="n">
-        <v>1.365367156700771e-07</v>
+        <v>0.5160176362208133</v>
       </c>
       <c r="E46" t="n">
-        <v>1.376919723468787e-07</v>
+        <v>0.518962813375255</v>
       </c>
       <c r="F46" t="n">
-        <v>1.38857003815631e-07</v>
+        <v>0.5219248001653798</v>
       </c>
       <c r="G46" t="n">
-        <v>1.400318927822464e-07</v>
+        <v>0.5249036925323951</v>
       </c>
       <c r="H46" t="n">
-        <v>1.412167226524241e-07</v>
+        <v>0.527899586965094</v>
       </c>
       <c r="I46" t="n">
-        <v>1.424115775375707e-07</v>
+        <v>0.5309125805029804</v>
       </c>
       <c r="J46" t="n">
-        <v>1.436165422607714e-07</v>
+        <v>0.5339427707394123</v>
       </c>
       <c r="K46" t="n">
-        <v>1.448317023628119e-07</v>
+        <v>0.5369902558247629</v>
       </c>
       <c r="L46" t="n">
-        <v>1.460571441082505e-07</v>
+        <v>0.5400551344696005</v>
       </c>
       <c r="M46" t="n">
-        <v>1.472929544915422e-07</v>
+        <v>0.5431375059478847</v>
       </c>
       <c r="N46" t="n">
-        <v>1.485392212432149e-07</v>
+        <v>0.5462374701001828</v>
       </c>
       <c r="O46" t="n">
-        <v>1.497960328360965e-07</v>
+        <v>0.5493551273369028</v>
       </c>
       <c r="P46" t="n">
-        <v>1.510634784915967e-07</v>
+        <v>0.5524905786415468</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.523416481860399e-07</v>
+        <v>0.5556439255739818</v>
       </c>
       <c r="R46" t="n">
-        <v>1.536306326570532e-07</v>
+        <v>0.5588152702737282</v>
       </c>
       <c r="S46" t="n">
-        <v>1.549305234100078e-07</v>
+        <v>0.5620047154632705</v>
       </c>
       <c r="T46" t="n">
-        <v>1.562414127245148e-07</v>
+        <v>0.5652123644513808</v>
       </c>
       <c r="U46" t="n">
-        <v>1.575633936609764e-07</v>
+        <v>0.5684383211364691</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>0.5582891414141408</v>
+        <v>0.5325576519916135</v>
       </c>
       <c r="B47" t="n">
-        <v>1.324470484996687e-07</v>
+        <v>0.5073818375555151</v>
       </c>
       <c r="C47" t="n">
-        <v>1.335677019176961e-07</v>
+        <v>0.5102777257803657</v>
       </c>
       <c r="D47" t="n">
-        <v>1.346978373445532e-07</v>
+        <v>0.5131901423237134</v>
       </c>
       <c r="E47" t="n">
-        <v>1.358375350088727e-07</v>
+        <v>0.5161191815211444</v>
       </c>
       <c r="F47" t="n">
-        <v>1.369868758181131e-07</v>
+        <v>0.5190649382466657</v>
       </c>
       <c r="G47" t="n">
-        <v>1.381459413643027e-07</v>
+        <v>0.5220275079157797</v>
       </c>
       <c r="H47" t="n">
-        <v>1.393148139298315e-07</v>
+        <v>0.5250069864885734</v>
       </c>
       <c r="I47" t="n">
-        <v>1.404935764932927e-07</v>
+        <v>0.5280034704728274</v>
       </c>
       <c r="J47" t="n">
-        <v>1.416823127353728e-07</v>
+        <v>0.531017056927142</v>
       </c>
       <c r="K47" t="n">
-        <v>1.428811070447932e-07</v>
+        <v>0.5340478434640796</v>
       </c>
       <c r="L47" t="n">
-        <v>1.440900445243e-07</v>
+        <v>0.5370959282533291</v>
       </c>
       <c r="M47" t="n">
-        <v>1.453092109967056e-07</v>
+        <v>0.5401614100248832</v>
       </c>
       <c r="N47" t="n">
-        <v>1.46538693010982e-07</v>
+        <v>0.543244388072237</v>
       </c>
       <c r="O47" t="n">
-        <v>1.47778577848404e-07</v>
+        <v>0.5463449622556051</v>
       </c>
       <c r="P47" t="n">
-        <v>1.490289535287459e-07</v>
+        <v>0.5494632330051552</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.502899088165299e-07</v>
+        <v>0.5525993013242618</v>
       </c>
       <c r="R47" t="n">
-        <v>1.515615332273275e-07</v>
+        <v>0.555753268792777</v>
       </c>
       <c r="S47" t="n">
-        <v>1.528439170341144e-07</v>
+        <v>0.5589252375703214</v>
       </c>
       <c r="T47" t="n">
-        <v>1.541371512736785e-07</v>
+        <v>0.5621153103995928</v>
       </c>
       <c r="U47" t="n">
-        <v>1.554413277530834e-07</v>
+        <v>0.5653235906096943</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0.5691414141414141</v>
+        <v>0.5485744234800832</v>
       </c>
       <c r="B48" t="n">
-        <v>1.304128788128146e-07</v>
+        <v>0.5003931070106727</v>
       </c>
       <c r="C48" t="n">
-        <v>1.315163208302239e-07</v>
+        <v>0.5032491069679633</v>
       </c>
       <c r="D48" t="n">
-        <v>1.326290992283409e-07</v>
+        <v>0.5061214075809619</v>
       </c>
       <c r="E48" t="n">
-        <v>1.337512930036179e-07</v>
+        <v>0.5090101018858663</v>
       </c>
       <c r="F48" t="n">
-        <v>1.348829818209076e-07</v>
+        <v>0.511915283449879</v>
       </c>
       <c r="G48" t="n">
-        <v>1.360242460191182e-07</v>
+        <v>0.5148370463742393</v>
       </c>
       <c r="H48" t="n">
-        <v>1.37175166616917e-07</v>
+        <v>0.51777548529727</v>
       </c>
       <c r="I48" t="n">
-        <v>1.38335825318482e-07</v>
+        <v>0.5207306953974435</v>
       </c>
       <c r="J48" t="n">
-        <v>1.395063045193015e-07</v>
+        <v>0.5237027723964643</v>
       </c>
       <c r="K48" t="n">
-        <v>1.406866873120243e-07</v>
+        <v>0.52669181256237</v>
       </c>
       <c r="L48" t="n">
-        <v>1.418770574923578e-07</v>
+        <v>0.529697912712649</v>
       </c>
       <c r="M48" t="n">
-        <v>1.430774995650166e-07</v>
+        <v>0.5327211702173771</v>
       </c>
       <c r="N48" t="n">
-        <v>1.442880987497222e-07</v>
+        <v>0.5357616830023707</v>
       </c>
       <c r="O48" t="n">
-        <v>1.45508940987252e-07</v>
+        <v>0.5388195495523591</v>
       </c>
       <c r="P48" t="n">
-        <v>1.467401129455409e-07</v>
+        <v>0.5418948689141744</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.479817020258334e-07</v>
+        <v>0.5449877406999599</v>
       </c>
       <c r="R48" t="n">
-        <v>1.492337963688884e-07</v>
+        <v>0.5480982650903964</v>
       </c>
       <c r="S48" t="n">
-        <v>1.504964848612365e-07</v>
+        <v>0.5512265428379471</v>
       </c>
       <c r="T48" t="n">
-        <v>1.517698571414899e-07</v>
+        <v>0.5543726752701211</v>
       </c>
       <c r="U48" t="n">
-        <v>1.53054003606706e-07</v>
+        <v>0.5575367642927556</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>0.5811994949494945</v>
+        <v>0.565592243186583</v>
       </c>
       <c r="B49" t="n">
-        <v>1.274746337095787e-07</v>
+        <v>0.4885122650844428</v>
       </c>
       <c r="C49" t="n">
-        <v>1.285532148149839e-07</v>
+        <v>0.4913004549868815</v>
       </c>
       <c r="D49" t="n">
-        <v>1.296409219493652e-07</v>
+        <v>0.4941045585182865</v>
       </c>
       <c r="E49" t="n">
-        <v>1.307378323293586e-07</v>
+        <v>0.4969246665058956</v>
       </c>
       <c r="F49" t="n">
-        <v>1.318440238249416e-07</v>
+        <v>0.4997608702953437</v>
       </c>
       <c r="G49" t="n">
-        <v>1.329595749649603e-07</v>
+        <v>0.502613261753623</v>
       </c>
       <c r="H49" t="n">
-        <v>1.340845649427047e-07</v>
+        <v>0.5054819332720566</v>
       </c>
       <c r="I49" t="n">
-        <v>1.352190736215308e-07</v>
+        <v>0.508366977769293</v>
       </c>
       <c r="J49" t="n">
-        <v>1.363631815405294e-07</v>
+        <v>0.5112684886943147</v>
       </c>
       <c r="K49" t="n">
-        <v>1.375169699202446e-07</v>
+        <v>0.5141865600294656</v>
       </c>
       <c r="L49" t="n">
-        <v>1.386805206684388e-07</v>
+        <v>0.5171212862934951</v>
       </c>
       <c r="M49" t="n">
-        <v>1.398539163859078e-07</v>
+        <v>0.5200727625446193</v>
       </c>
       <c r="N49" t="n">
-        <v>1.410372403723444e-07</v>
+        <v>0.5230410843836006</v>
       </c>
       <c r="O49" t="n">
-        <v>1.422305766322522e-07</v>
+        <v>0.5260263479568434</v>
       </c>
       <c r="P49" t="n">
-        <v>1.43434009880909e-07</v>
+        <v>0.5290286499595094</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.446476255503803e-07</v>
+        <v>0.5320480876386493</v>
       </c>
       <c r="R49" t="n">
-        <v>1.458715097955848e-07</v>
+        <v>0.5350847587963519</v>
       </c>
       <c r="S49" t="n">
-        <v>1.471057495004104e-07</v>
+        <v>0.5381387617929132</v>
       </c>
       <c r="T49" t="n">
-        <v>1.483504322838816e-07</v>
+        <v>0.5412101955500217</v>
       </c>
       <c r="U49" t="n">
-        <v>1.496056465063805e-07</v>
+        <v>0.5442991595539624</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>0.5884343434343433</v>
+        <v>0.5766037735849051</v>
       </c>
       <c r="B50" t="n">
-        <v>1.254404640227237e-07</v>
+        <v>0.4787280423216641</v>
       </c>
       <c r="C50" t="n">
-        <v>1.265018337275108e-07</v>
+        <v>0.4814603886495189</v>
       </c>
       <c r="D50" t="n">
-        <v>1.275721838331519e-07</v>
+        <v>0.4842083298784351</v>
       </c>
       <c r="E50" t="n">
-        <v>1.286515903241029e-07</v>
+        <v>0.4869719550165071</v>
       </c>
       <c r="F50" t="n">
-        <v>1.297401298277351e-07</v>
+        <v>0.4897513535798433</v>
       </c>
       <c r="G50" t="n">
-        <v>1.308378796197747e-07</v>
+        <v>0.4925466155954673</v>
       </c>
       <c r="H50" t="n">
-        <v>1.319449176297892e-07</v>
+        <v>0.4953578316042327</v>
       </c>
       <c r="I50" t="n">
-        <v>1.330613224467191e-07</v>
+        <v>0.4981850926637563</v>
       </c>
       <c r="J50" t="n">
-        <v>1.341871733244571e-07</v>
+        <v>0.501028490351367</v>
       </c>
       <c r="K50" t="n">
-        <v>1.353225501874747e-07</v>
+        <v>0.5038881167670728</v>
       </c>
       <c r="L50" t="n">
-        <v>1.364675336364956e-07</v>
+        <v>0.5067640645365437</v>
       </c>
       <c r="M50" t="n">
-        <v>1.376222049542178e-07</v>
+        <v>0.5096564268141117</v>
       </c>
       <c r="N50" t="n">
-        <v>1.387866461110836e-07</v>
+        <v>0.5125652972857885</v>
       </c>
       <c r="O50" t="n">
-        <v>1.399609397710993e-07</v>
+        <v>0.5154907701722999</v>
       </c>
       <c r="P50" t="n">
-        <v>1.41145169297703e-07</v>
+        <v>0.5184329402321372</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.423394187596827e-07</v>
+        <v>0.5213919027646275</v>
       </c>
       <c r="R50" t="n">
-        <v>1.435437729371446e-07</v>
+        <v>0.5243677536130199</v>
       </c>
       <c r="S50" t="n">
-        <v>1.447583173275315e-07</v>
+        <v>0.5273605891675901</v>
       </c>
       <c r="T50" t="n">
-        <v>1.45983138151692e-07</v>
+        <v>0.5303705063687622</v>
       </c>
       <c r="U50" t="n">
-        <v>1.472183223600021e-07</v>
+        <v>0.5333976027102492</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>0.6004924242424238</v>
+        <v>0.5866142557651987</v>
       </c>
       <c r="B51" t="n">
-        <v>1.218241623572046e-07</v>
+        <v>0.4682449465044005</v>
       </c>
       <c r="C51" t="n">
-        <v>1.228549340164483e-07</v>
+        <v>0.4709174604309153</v>
       </c>
       <c r="D51" t="n">
-        <v>1.23894427182107e-07</v>
+        <v>0.4736052277643079</v>
       </c>
       <c r="E51" t="n">
-        <v>1.249427156480937e-07</v>
+        <v>0.4763083355635899</v>
       </c>
       <c r="F51" t="n">
-        <v>1.259998738327022e-07</v>
+        <v>0.4790268713846634</v>
       </c>
       <c r="G51" t="n">
-        <v>1.270659767838903e-07</v>
+        <v>0.4817609232831568</v>
       </c>
       <c r="H51" t="n">
-        <v>1.28141100184607e-07</v>
+        <v>0.4845105798172778</v>
       </c>
       <c r="I51" t="n">
-        <v>1.29225320358166e-07</v>
+        <v>0.4872759300506803</v>
       </c>
       <c r="J51" t="n">
-        <v>1.303187142736629e-07</v>
+        <v>0.4900570635553507</v>
       </c>
       <c r="K51" t="n">
-        <v>1.314213595514404e-07</v>
+        <v>0.4928540704145082</v>
       </c>
       <c r="L51" t="n">
-        <v>1.325333344685976e-07</v>
+        <v>0.4956670412255235</v>
       </c>
       <c r="M51" t="n">
-        <v>1.336547179645476e-07</v>
+        <v>0.4984960671028529</v>
       </c>
       <c r="N51" t="n">
-        <v>1.347855896466209e-07</v>
+        <v>0.5013412396809893</v>
       </c>
       <c r="O51" t="n">
-        <v>1.359260297957172e-07</v>
+        <v>0.504202651117431</v>
       </c>
       <c r="P51" t="n">
-        <v>1.370761193720044e-07</v>
+        <v>0.507080394095666</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.382359400206658e-07</v>
+        <v>0.5099745618281748</v>
       </c>
       <c r="R51" t="n">
-        <v>1.394055740776964e-07</v>
+        <v>0.5128852480594492</v>
       </c>
       <c r="S51" t="n">
-        <v>1.405851045757478e-07</v>
+        <v>0.5158125470690287</v>
       </c>
       <c r="T51" t="n">
-        <v>1.417746152500227e-07</v>
+        <v>0.5187565536745546</v>
       </c>
       <c r="U51" t="n">
-        <v>1.429741905442193e-07</v>
+        <v>0.5217173632348412</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>0.6113446969696971</v>
+        <v>0.599627882599581</v>
       </c>
       <c r="B52" t="n">
-        <v>1.184338795457796e-07</v>
+        <v>0.4521708662512641</v>
       </c>
       <c r="C52" t="n">
-        <v>1.194359655373264e-07</v>
+        <v>0.4547516371623913</v>
       </c>
       <c r="D52" t="n">
-        <v>1.204465303217515e-07</v>
+        <v>0.4573471378559808</v>
       </c>
       <c r="E52" t="n">
-        <v>1.214656456393341e-07</v>
+        <v>0.4599574524024516</v>
       </c>
       <c r="F52" t="n">
-        <v>1.22493383837358e-07</v>
+        <v>0.4625826653520553</v>
       </c>
       <c r="G52" t="n">
-        <v>1.235298178752477e-07</v>
+        <v>0.4652228617376156</v>
       </c>
       <c r="H52" t="n">
-        <v>1.245750213297478e-07</v>
+        <v>0.4678781270772815</v>
       </c>
       <c r="I52" t="n">
-        <v>1.256290684001465e-07</v>
+        <v>0.4705485473772987</v>
       </c>
       <c r="J52" t="n">
-        <v>1.266920339135424e-07</v>
+        <v>0.4732342091347938</v>
       </c>
       <c r="K52" t="n">
-        <v>1.277639933301573e-07</v>
+        <v>0.4759351993405773</v>
       </c>
       <c r="L52" t="n">
-        <v>1.288450227486923e-07</v>
+        <v>0.4786516054819606</v>
       </c>
       <c r="M52" t="n">
-        <v>1.299351989117309e-07</v>
+        <v>0.4813835155455907</v>
       </c>
       <c r="N52" t="n">
-        <v>1.310345992111862e-07</v>
+        <v>0.4841310180202986</v>
       </c>
       <c r="O52" t="n">
-        <v>1.321433016937956e-07</v>
+        <v>0.486894201899967</v>
       </c>
       <c r="P52" t="n">
-        <v>1.332613850666611e-07</v>
+        <v>0.4896731566864115</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.343889287028365e-07</v>
+        <v>0.4924679723922821</v>
       </c>
       <c r="R52" t="n">
-        <v>1.355260126469627e-07</v>
+        <v>0.4952787395439753</v>
       </c>
       <c r="S52" t="n">
-        <v>1.366727176209496e-07</v>
+        <v>0.4981055491845695</v>
       </c>
       <c r="T52" t="n">
-        <v>1.378291250297066e-07</v>
+        <v>0.5009484928767713</v>
       </c>
       <c r="U52" t="n">
-        <v>1.389953169669219e-07</v>
+        <v>0.5038076627058838</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>0.6209911616161617</v>
+        <v>0.6116404612159333</v>
       </c>
       <c r="B53" t="n">
-        <v>1.150435967343537e-07</v>
+        <v>0.4367956590526131</v>
       </c>
       <c r="C53" t="n">
-        <v>1.160169970582035e-07</v>
+        <v>0.4392886757751083</v>
       </c>
       <c r="D53" t="n">
-        <v>1.169986334613951e-07</v>
+        <v>0.4417959214219296</v>
       </c>
       <c r="E53" t="n">
-        <v>1.179885756305736e-07</v>
+        <v>0.444317477204842</v>
       </c>
       <c r="F53" t="n">
-        <v>1.189868938420128e-07</v>
+        <v>0.4468534247991268</v>
       </c>
       <c r="G53" t="n">
-        <v>1.199936589666041e-07</v>
+        <v>0.4494038463462292</v>
       </c>
       <c r="H53" t="n">
-        <v>1.210089424748877e-07</v>
+        <v>0.4519688244564167</v>
       </c>
       <c r="I53" t="n">
-        <v>1.220328164421261e-07</v>
+        <v>0.4545484422114562</v>
       </c>
       <c r="J53" t="n">
-        <v>1.230653535534209e-07</v>
+        <v>0.4571427831673054</v>
       </c>
       <c r="K53" t="n">
-        <v>1.241066271088732e-07</v>
+        <v>0.459751931356818</v>
       </c>
       <c r="L53" t="n">
-        <v>1.25156711028786e-07</v>
+        <v>0.4623759712924667</v>
       </c>
       <c r="M53" t="n">
-        <v>1.262156798589131e-07</v>
+        <v>0.4650149879690799</v>
       </c>
       <c r="N53" t="n">
-        <v>1.272836087757504e-07</v>
+        <v>0.4676690668665954</v>
       </c>
       <c r="O53" t="n">
-        <v>1.283605735918729e-07</v>
+        <v>0.4703382939528282</v>
       </c>
       <c r="P53" t="n">
-        <v>1.294466507613167e-07</v>
+        <v>0.4730227556862562</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.305419173850062e-07</v>
+        <v>0.4757225390188206</v>
       </c>
       <c r="R53" t="n">
-        <v>1.31646451216228e-07</v>
+        <v>0.4784377313987405</v>
       </c>
       <c r="S53" t="n">
-        <v>1.327603306661504e-07</v>
+        <v>0.4811684207733484</v>
       </c>
       <c r="T53" t="n">
-        <v>1.338836348093895e-07</v>
+        <v>0.4839146955919361</v>
       </c>
       <c r="U53" t="n">
-        <v>1.350164433896234e-07</v>
+        <v>0.4866766448086213</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>0.6306376262626263</v>
+        <v>0.6226519916142556</v>
       </c>
       <c r="B54" t="n">
-        <v>1.109752573606437e-07</v>
+        <v>0.4221193249084467</v>
       </c>
       <c r="C54" t="n">
-        <v>1.119142348832571e-07</v>
+        <v>0.4245285762690661</v>
       </c>
       <c r="D54" t="n">
-        <v>1.128611572289685e-07</v>
+        <v>0.4269515784621543</v>
       </c>
       <c r="E54" t="n">
-        <v>1.138160916200621e-07</v>
+        <v>0.4293884099707608</v>
       </c>
       <c r="F54" t="n">
-        <v>1.147791058475997e-07</v>
+        <v>0.4318391497258777</v>
       </c>
       <c r="G54" t="n">
-        <v>1.15750268276233e-07</v>
+        <v>0.4343038771089974</v>
       </c>
       <c r="H54" t="n">
-        <v>1.167296478490566e-07</v>
+        <v>0.4367826719546825</v>
       </c>
       <c r="I54" t="n">
-        <v>1.177173140925027e-07</v>
+        <v>0.4392756145531528</v>
       </c>
       <c r="J54" t="n">
-        <v>1.187133371212764e-07</v>
+        <v>0.4417827856528856</v>
       </c>
       <c r="K54" t="n">
-        <v>1.197177876433334e-07</v>
+        <v>0.4443042664632305</v>
       </c>
       <c r="L54" t="n">
-        <v>1.207307369648996e-07</v>
+        <v>0.4468401386570413</v>
       </c>
       <c r="M54" t="n">
-        <v>1.21752256995533e-07</v>
+        <v>0.4493904843733204</v>
       </c>
       <c r="N54" t="n">
-        <v>1.227824202532287e-07</v>
+        <v>0.4519553862198792</v>
       </c>
       <c r="O54" t="n">
-        <v>1.23821299869567e-07</v>
+        <v>0.4545349272760147</v>
       </c>
       <c r="P54" t="n">
-        <v>1.248689695949046e-07</v>
+        <v>0.4571291910951997</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.25925503803611e-07</v>
+        <v>0.4597382617077898</v>
       </c>
       <c r="R54" t="n">
-        <v>1.269909774993476e-07</v>
+        <v>0.4623622236237446</v>
       </c>
       <c r="S54" t="n">
-        <v>1.280654663203926e-07</v>
+        <v>0.4650011618353657</v>
       </c>
       <c r="T54" t="n">
-        <v>1.291490465450103e-07</v>
+        <v>0.4676551618200487</v>
       </c>
       <c r="U54" t="n">
-        <v>1.302417950968666e-07</v>
+        <v>0.4703243095430533</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>0.640284090909091</v>
+        <v>0.6316614255765204</v>
       </c>
       <c r="B55" t="n">
-        <v>1.075849745492187e-07</v>
+        <v>0.4074429907642769</v>
       </c>
       <c r="C55" t="n">
-        <v>1.084952664041352e-07</v>
+        <v>0.4097684767630205</v>
       </c>
       <c r="D55" t="n">
-        <v>1.09413260368613e-07</v>
+        <v>0.4121072355023754</v>
       </c>
       <c r="E55" t="n">
-        <v>1.103390216113025e-07</v>
+        <v>0.4144593427366761</v>
       </c>
       <c r="F55" t="n">
-        <v>1.112726158522555e-07</v>
+        <v>0.416824874652625</v>
       </c>
       <c r="G55" t="n">
-        <v>1.122141093675904e-07</v>
+        <v>0.419203907871762</v>
       </c>
       <c r="H55" t="n">
-        <v>1.131635689941974e-07</v>
+        <v>0.4215965194529449</v>
       </c>
       <c r="I55" t="n">
-        <v>1.141210621344833e-07</v>
+        <v>0.4240027868948459</v>
       </c>
       <c r="J55" t="n">
-        <v>1.150866567611559e-07</v>
+        <v>0.426422788138462</v>
       </c>
       <c r="K55" t="n">
-        <v>1.160604214220502e-07</v>
+        <v>0.4288566015696393</v>
       </c>
       <c r="L55" t="n">
-        <v>1.170424252449943e-07</v>
+        <v>0.4313043060216123</v>
       </c>
       <c r="M55" t="n">
-        <v>1.180327379427163e-07</v>
+        <v>0.4337659807775572</v>
       </c>
       <c r="N55" t="n">
-        <v>1.19031429817794e-07</v>
+        <v>0.4362417055731595</v>
       </c>
       <c r="O55" t="n">
-        <v>1.200385717676453e-07</v>
+        <v>0.4387315605991978</v>
       </c>
       <c r="P55" t="n">
-        <v>1.210542352895613e-07</v>
+        <v>0.4412356265041392</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.220784924857818e-07</v>
+        <v>0.4437539843967552</v>
       </c>
       <c r="R55" t="n">
-        <v>1.23111416068614e-07</v>
+        <v>0.4462867158487446</v>
       </c>
       <c r="S55" t="n">
-        <v>1.241530793655944e-07</v>
+        <v>0.4488339028973788</v>
       </c>
       <c r="T55" t="n">
-        <v>1.252035563246942e-07</v>
+        <v>0.4513956280481574</v>
       </c>
       <c r="U55" t="n">
-        <v>1.262629215195692e-07</v>
+        <v>0.4539719742774813</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>0.6487247474747471</v>
+        <v>0.6396698113207552</v>
       </c>
       <c r="B56" t="n">
-        <v>1.039686728836987e-07</v>
+        <v>0.3969598949470133</v>
       </c>
       <c r="C56" t="n">
-        <v>1.048483666930718e-07</v>
+        <v>0.399225548544417</v>
       </c>
       <c r="D56" t="n">
-        <v>1.057355037175672e-07</v>
+        <v>0.4015041333882483</v>
       </c>
       <c r="E56" t="n">
-        <v>1.066301469352923e-07</v>
+        <v>0.403795723283759</v>
       </c>
       <c r="F56" t="n">
-        <v>1.075323598572217e-07</v>
+        <v>0.406100392457445</v>
       </c>
       <c r="G56" t="n">
-        <v>1.08442206531705e-07</v>
+        <v>0.4084182155594515</v>
       </c>
       <c r="H56" t="n">
-        <v>1.093597515490143e-07</v>
+        <v>0.4107492676659897</v>
       </c>
       <c r="I56" t="n">
-        <v>1.102850600459291e-07</v>
+        <v>0.41309362428177</v>
       </c>
       <c r="J56" t="n">
-        <v>1.112181977103607e-07</v>
+        <v>0.4154513613424456</v>
       </c>
       <c r="K56" t="n">
-        <v>1.121592307860149e-07</v>
+        <v>0.4178225552170747</v>
       </c>
       <c r="L56" t="n">
-        <v>1.131082260770953e-07</v>
+        <v>0.4202072827105922</v>
       </c>
       <c r="M56" t="n">
-        <v>1.140652509530451e-07</v>
+        <v>0.4226056210662983</v>
       </c>
       <c r="N56" t="n">
-        <v>1.150303733533303e-07</v>
+        <v>0.4250176479683603</v>
       </c>
       <c r="O56" t="n">
-        <v>1.160036617922623e-07</v>
+        <v>0.4274434415443286</v>
       </c>
       <c r="P56" t="n">
-        <v>1.169851853638617e-07</v>
+        <v>0.4298830803676681</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.179750137467638e-07</v>
+        <v>0.4323366434603025</v>
       </c>
       <c r="R56" t="n">
-        <v>1.189732172091647e-07</v>
+        <v>0.4348042102951739</v>
       </c>
       <c r="S56" t="n">
-        <v>1.199798666138097e-07</v>
+        <v>0.4372858607988174</v>
       </c>
       <c r="T56" t="n">
-        <v>1.209950334230238e-07</v>
+        <v>0.43978167535395</v>
       </c>
       <c r="U56" t="n">
-        <v>1.220187897037853e-07</v>
+        <v>0.4422917348020735</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>0.6571654040404045</v>
+        <v>0.6496802935010488</v>
       </c>
       <c r="B57" t="n">
-        <v>1.003523712181797e-07</v>
+        <v>0.3815846877483621</v>
       </c>
       <c r="C57" t="n">
-        <v>1.012014669820094e-07</v>
+        <v>0.3837625871571339</v>
       </c>
       <c r="D57" t="n">
-        <v>1.020577470665223e-07</v>
+        <v>0.385952916954197</v>
       </c>
       <c r="E57" t="n">
-        <v>1.029212722592831e-07</v>
+        <v>0.3881557480861493</v>
       </c>
       <c r="F57" t="n">
-        <v>1.037921038621888e-07</v>
+        <v>0.3903711519045165</v>
       </c>
       <c r="G57" t="n">
-        <v>1.046703036958206e-07</v>
+        <v>0.392599200168065</v>
       </c>
       <c r="H57" t="n">
-        <v>1.055559341038322e-07</v>
+        <v>0.3948399650451248</v>
       </c>
       <c r="I57" t="n">
-        <v>1.064490579573761e-07</v>
+        <v>0.3970935191159274</v>
       </c>
       <c r="J57" t="n">
-        <v>1.073497386595665e-07</v>
+        <v>0.3993599353749573</v>
       </c>
       <c r="K57" t="n">
-        <v>1.082580401499806e-07</v>
+        <v>0.4016392872333154</v>
       </c>
       <c r="L57" t="n">
-        <v>1.091740269091973e-07</v>
+        <v>0.4039316485210981</v>
       </c>
       <c r="M57" t="n">
-        <v>1.10097763963375e-07</v>
+        <v>0.4062370934897874</v>
       </c>
       <c r="N57" t="n">
-        <v>1.110293168888677e-07</v>
+        <v>0.408555696814657</v>
       </c>
       <c r="O57" t="n">
-        <v>1.119687518168802e-07</v>
+        <v>0.41088753359719</v>
       </c>
       <c r="P57" t="n">
-        <v>1.129161354381632e-07</v>
+        <v>0.4132326793675126</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.13871535007747e-07</v>
+        <v>0.4155912100868409</v>
       </c>
       <c r="R57" t="n">
-        <v>1.148350183497165e-07</v>
+        <v>0.417963202149939</v>
       </c>
       <c r="S57" t="n">
-        <v>1.15806653862026e-07</v>
+        <v>0.4203487323875963</v>
       </c>
       <c r="T57" t="n">
-        <v>1.167865105213545e-07</v>
+        <v>0.4227478780691146</v>
       </c>
       <c r="U57" t="n">
-        <v>1.177746578880025e-07</v>
+        <v>0.4251607169048108</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>0.6656060606060605</v>
+        <v>0.6576886792452823</v>
       </c>
       <c r="B58" t="n">
-        <v>9.696208840675376e-08</v>
+        <v>0.370402718876617</v>
       </c>
       <c r="C58" t="n">
-        <v>9.778249850288647e-08</v>
+        <v>0.372516797057293</v>
       </c>
       <c r="D58" t="n">
-        <v>9.860985020616584e-08</v>
+        <v>0.3746429413657975</v>
       </c>
       <c r="E58" t="n">
-        <v>9.944420225052257e-08</v>
+        <v>0.3767812206697072</v>
       </c>
       <c r="F58" t="n">
-        <v>1.002856138668436e-07</v>
+        <v>0.3789317042296607</v>
       </c>
       <c r="G58" t="n">
-        <v>1.01134144787177e-07</v>
+        <v>0.3810944617016034</v>
       </c>
       <c r="H58" t="n">
-        <v>1.01989855248972e-07</v>
+        <v>0.3832695631390424</v>
       </c>
       <c r="I58" t="n">
-        <v>1.028528059993556e-07</v>
+        <v>0.3854570789953161</v>
       </c>
       <c r="J58" t="n">
-        <v>1.03723058299445e-07</v>
+        <v>0.3876570801258762</v>
       </c>
       <c r="K58" t="n">
-        <v>1.046006739286965e-07</v>
+        <v>0.3898696377905829</v>
       </c>
       <c r="L58" t="n">
-        <v>1.05485715189291e-07</v>
+        <v>0.3920948236560129</v>
       </c>
       <c r="M58" t="n">
-        <v>1.063782449105573e-07</v>
+        <v>0.394332709797781</v>
       </c>
       <c r="N58" t="n">
-        <v>1.072783264534319e-07</v>
+        <v>0.396583368702874</v>
       </c>
       <c r="O58" t="n">
-        <v>1.081860237149576e-07</v>
+        <v>0.3988468732719996</v>
       </c>
       <c r="P58" t="n">
-        <v>1.091014011328188e-07</v>
+        <v>0.4011232968219465</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.100245236899166e-07</v>
+        <v>0.403412713087961</v>
       </c>
       <c r="R58" t="n">
-        <v>1.109554569189818e-07</v>
+        <v>0.4057151962261332</v>
       </c>
       <c r="S58" t="n">
-        <v>1.118942669072268e-07</v>
+        <v>0.4080308208158007</v>
       </c>
       <c r="T58" t="n">
-        <v>1.128410203010374e-07</v>
+        <v>0.410359661861963</v>
       </c>
       <c r="U58" t="n">
-        <v>1.137957843107041e-07</v>
+        <v>0.4127017947977121</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>0.6752525252525252</v>
+        <v>0.6666981132075471</v>
       </c>
       <c r="B59" t="n">
-        <v>9.424986215761376e-08</v>
+        <v>0.357823003895902</v>
       </c>
       <c r="C59" t="n">
-        <v>9.504732371958892e-08</v>
+        <v>0.3598652831949702</v>
       </c>
       <c r="D59" t="n">
-        <v>9.585153271788145e-08</v>
+        <v>0.3619192188288462</v>
       </c>
       <c r="E59" t="n">
-        <v>9.666254624351492e-08</v>
+        <v>0.3639848773262081</v>
       </c>
       <c r="F59" t="n">
-        <v>9.748042187056828e-08</v>
+        <v>0.3660623255954462</v>
       </c>
       <c r="G59" t="n">
-        <v>9.830521766026292e-08</v>
+        <v>0.3681516309268323</v>
       </c>
       <c r="H59" t="n">
-        <v>9.913699216508462e-08</v>
+        <v>0.370252860994698</v>
       </c>
       <c r="I59" t="n">
-        <v>9.997580443294004e-08</v>
+        <v>0.3723660838596265</v>
       </c>
       <c r="J59" t="n">
-        <v>1.008217140113486e-07</v>
+        <v>0.3744913679706582</v>
       </c>
       <c r="K59" t="n">
-        <v>1.016747809516699e-07</v>
+        <v>0.3766287821675068</v>
       </c>
       <c r="L59" t="n">
-        <v>1.025350658133667e-07</v>
+        <v>0.3787783956827902</v>
       </c>
       <c r="M59" t="n">
-        <v>1.034026296683039e-07</v>
+        <v>0.3809402781442718</v>
       </c>
       <c r="N59" t="n">
-        <v>1.042775341050841e-07</v>
+        <v>0.3831144995771164</v>
       </c>
       <c r="O59" t="n">
-        <v>1.051598412334203e-07</v>
+        <v>0.3853011304061584</v>
       </c>
       <c r="P59" t="n">
-        <v>1.060496136885441e-07</v>
+        <v>0.3875002414581827</v>
       </c>
       <c r="Q59" t="n">
-        <v>1.069469146356532e-07</v>
+        <v>0.3897119039642194</v>
       </c>
       <c r="R59" t="n">
-        <v>1.078518077743949e-07</v>
+        <v>0.3919361895618498</v>
       </c>
       <c r="S59" t="n">
-        <v>1.087643573433882e-07</v>
+        <v>0.3941731702975286</v>
       </c>
       <c r="T59" t="n">
-        <v>1.096846281247845e-07</v>
+        <v>0.3964229186289156</v>
       </c>
       <c r="U59" t="n">
-        <v>1.106126854488662e-07</v>
+        <v>0.3986855074272241</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>0.6836931818181812</v>
+        <v>0.6757075471698106</v>
       </c>
       <c r="B60" t="n">
-        <v>8.972948507571471e-08</v>
+        <v>0.3452432889151867</v>
       </c>
       <c r="C60" t="n">
-        <v>9.048869908076061e-08</v>
+        <v>0.3472137693326469</v>
       </c>
       <c r="D60" t="n">
-        <v>9.12543369040751e-08</v>
+        <v>0.3491954962918946</v>
       </c>
       <c r="E60" t="n">
-        <v>9.202645289850312e-08</v>
+        <v>0.3511885339827085</v>
       </c>
       <c r="F60" t="n">
-        <v>9.280510187677696e-08</v>
+        <v>0.3531929469612313</v>
       </c>
       <c r="G60" t="n">
-        <v>9.359033911540712e-08</v>
+        <v>0.3552088001520609</v>
       </c>
       <c r="H60" t="n">
-        <v>9.438222035860668e-08</v>
+        <v>0.3572361588503531</v>
       </c>
       <c r="I60" t="n">
-        <v>9.518080182224842e-08</v>
+        <v>0.3592750887239364</v>
       </c>
       <c r="J60" t="n">
-        <v>9.598614019785564e-08</v>
+        <v>0.3613256558154396</v>
       </c>
       <c r="K60" t="n">
-        <v>9.679829265662679e-08</v>
+        <v>0.3633879265444304</v>
       </c>
       <c r="L60" t="n">
-        <v>9.7617316853494e-08</v>
+        <v>0.3654619677095671</v>
       </c>
       <c r="M60" t="n">
-        <v>9.844327093121594e-08</v>
+        <v>0.3675478464907622</v>
       </c>
       <c r="N60" t="n">
-        <v>9.927621352450555e-08</v>
+        <v>0.3696456304513583</v>
       </c>
       <c r="O60" t="n">
-        <v>1.001162037641925e-07</v>
+        <v>0.3717553875403169</v>
       </c>
       <c r="P60" t="n">
-        <v>1.009633012814207e-07</v>
+        <v>0.3738771860944185</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.018175662118819e-07</v>
+        <v>0.3760110948404772</v>
       </c>
       <c r="R60" t="n">
-        <v>1.026790592000844e-07</v>
+        <v>0.3781571828975661</v>
       </c>
       <c r="S60" t="n">
-        <v>1.035478414036584e-07</v>
+        <v>0.3803155197792561</v>
       </c>
       <c r="T60" t="n">
-        <v>1.044239744976976e-07</v>
+        <v>0.3824861753958678</v>
       </c>
       <c r="U60" t="n">
-        <v>1.053075206791374e-07</v>
+        <v>0.3846692200567358</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>0.693339646464646</v>
+        <v>0.6817138364779869</v>
       </c>
       <c r="B61" t="n">
-        <v>8.656522111838464e-08</v>
+        <v>0.3347601930979242</v>
       </c>
       <c r="C61" t="n">
-        <v>8.729766183358006e-08</v>
+        <v>0.3366708411140445</v>
       </c>
       <c r="D61" t="n">
-        <v>8.803629983440989e-08</v>
+        <v>0.3385923941777684</v>
       </c>
       <c r="E61" t="n">
-        <v>8.878118755699412e-08</v>
+        <v>0.3405249145297924</v>
       </c>
       <c r="F61" t="n">
-        <v>8.953237788112227e-08</v>
+        <v>0.3424684647660524</v>
       </c>
       <c r="G61" t="n">
-        <v>9.028992413400728e-08</v>
+        <v>0.3444231078397515</v>
       </c>
       <c r="H61" t="n">
-        <v>9.105388009407134e-08</v>
+        <v>0.3463889070633992</v>
       </c>
       <c r="I61" t="n">
-        <v>9.18242999947635e-08</v>
+        <v>0.3483659261108616</v>
       </c>
       <c r="J61" t="n">
-        <v>9.260123852840975e-08</v>
+        <v>0.3503542290194245</v>
       </c>
       <c r="K61" t="n">
-        <v>9.338475085009577e-08</v>
+        <v>0.3523538801918669</v>
       </c>
       <c r="L61" t="n">
-        <v>9.417489258158228e-08</v>
+        <v>0.354364944398548</v>
       </c>
       <c r="M61" t="n">
-        <v>9.497171981525357e-08</v>
+        <v>0.3563874867795044</v>
       </c>
       <c r="N61" t="n">
-        <v>9.577528911809972e-08</v>
+        <v>0.3584215728465602</v>
       </c>
       <c r="O61" t="n">
-        <v>9.658565753573219e-08</v>
+        <v>0.3604672684854492</v>
       </c>
       <c r="P61" t="n">
-        <v>9.740288259643348e-08</v>
+        <v>0.3625246399579485</v>
       </c>
       <c r="Q61" t="n">
-        <v>9.822702231524112e-08</v>
+        <v>0.3645937539040257</v>
       </c>
       <c r="R61" t="n">
-        <v>9.90581351980662e-08</v>
+        <v>0.3666746773439964</v>
       </c>
       <c r="S61" t="n">
-        <v>9.989628024584669e-08</v>
+        <v>0.3687674776806958</v>
       </c>
       <c r="T61" t="n">
-        <v>1.007415169587359e-07</v>
+        <v>0.3708722227016615</v>
       </c>
       <c r="U61" t="n">
-        <v>1.015939053403264e-07</v>
+        <v>0.3729889805813291</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>0.7017803030303033</v>
+        <v>0.6957285115303977</v>
       </c>
       <c r="B62" t="n">
-        <v>8.362697601514964e-08</v>
+        <v>0.3137940014633986</v>
       </c>
       <c r="C62" t="n">
-        <v>8.433455581834104e-08</v>
+        <v>0.3155849846768392</v>
       </c>
       <c r="D62" t="n">
-        <v>8.504812255543515e-08</v>
+        <v>0.3173861899495157</v>
       </c>
       <c r="E62" t="n">
-        <v>8.576772688273581e-08</v>
+        <v>0.31919767562396</v>
       </c>
       <c r="F62" t="n">
-        <v>8.649341988515726e-08</v>
+        <v>0.3210195003756942</v>
       </c>
       <c r="G62" t="n">
-        <v>8.722525307985037e-08</v>
+        <v>0.3228517232151324</v>
       </c>
       <c r="H62" t="n">
-        <v>8.796327841986003e-08</v>
+        <v>0.3246944034894911</v>
       </c>
       <c r="I62" t="n">
-        <v>8.870754829781328e-08</v>
+        <v>0.3265476008847116</v>
       </c>
       <c r="J62" t="n">
-        <v>8.945811554963865e-08</v>
+        <v>0.3284113754273937</v>
       </c>
       <c r="K62" t="n">
-        <v>9.021503345831705e-08</v>
+        <v>0.3302857874867395</v>
       </c>
       <c r="L62" t="n">
-        <v>9.097835575766433e-08</v>
+        <v>0.3321708977765095</v>
       </c>
       <c r="M62" t="n">
-        <v>9.174813663614574e-08</v>
+        <v>0.3340667673569884</v>
       </c>
       <c r="N62" t="n">
-        <v>9.252443074072295e-08</v>
+        <v>0.3359734576369635</v>
       </c>
       <c r="O62" t="n">
-        <v>9.330729318073343e-08</v>
+        <v>0.3378910303757133</v>
       </c>
       <c r="P62" t="n">
-        <v>9.409677953180257e-08</v>
+        <v>0.339819547685008</v>
       </c>
       <c r="Q62" t="n">
-        <v>9.489294583978904e-08</v>
+        <v>0.3417590720311222</v>
       </c>
       <c r="R62" t="n">
-        <v>9.569584862476367e-08</v>
+        <v>0.3437096662368567</v>
       </c>
       <c r="S62" t="n">
-        <v>9.650554488502159e-08</v>
+        <v>0.345671393483575</v>
       </c>
       <c r="T62" t="n">
-        <v>9.732209210112863e-08</v>
+        <v>0.3476443173132484</v>
       </c>
       <c r="U62" t="n">
-        <v>9.814554824000201e-08</v>
+        <v>0.3496285016305151</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>0.7162499999999995</v>
+        <v>0.7127463312368973</v>
       </c>
       <c r="B63" t="n">
-        <v>7.842854237096464e-08</v>
+        <v>0.2914300637199046</v>
       </c>
       <c r="C63" t="n">
-        <v>7.909213748368739e-08</v>
+        <v>0.2930934044771534</v>
       </c>
       <c r="D63" t="n">
-        <v>7.976134736955673e-08</v>
+        <v>0.2947662387727126</v>
       </c>
       <c r="E63" t="n">
-        <v>8.043621953597116e-08</v>
+        <v>0.2964486207910718</v>
       </c>
       <c r="F63" t="n">
-        <v>8.111680189229613e-08</v>
+        <v>0.2981406050259787</v>
       </c>
       <c r="G63" t="n">
-        <v>8.180314275326506e-08</v>
+        <v>0.2998422462822053</v>
       </c>
       <c r="H63" t="n">
-        <v>8.249529084240928e-08</v>
+        <v>0.3015535996773224</v>
       </c>
       <c r="I63" t="n">
-        <v>8.319329529551678e-08</v>
+        <v>0.3032747206434848</v>
       </c>
       <c r="J63" t="n">
-        <v>8.389720566412057e-08</v>
+        <v>0.3050056649292274</v>
       </c>
       <c r="K63" t="n">
-        <v>8.460707191901626e-08</v>
+        <v>0.3067464886012702</v>
       </c>
       <c r="L63" t="n">
-        <v>8.532294445380952e-08</v>
+        <v>0.308497248046335</v>
       </c>
       <c r="M63" t="n">
-        <v>8.604487408849343e-08</v>
+        <v>0.3102579999729713</v>
       </c>
       <c r="N63" t="n">
-        <v>8.677291207305638e-08</v>
+        <v>0.3120288014133936</v>
       </c>
       <c r="O63" t="n">
-        <v>8.750711009112025e-08</v>
+        <v>0.3138097097253282</v>
       </c>
       <c r="P63" t="n">
-        <v>8.824752026360944e-08</v>
+        <v>0.3156007825938715</v>
       </c>
       <c r="Q63" t="n">
-        <v>8.89941951524508e-08</v>
+        <v>0.3174020780333583</v>
       </c>
       <c r="R63" t="n">
-        <v>8.974718776430539e-08</v>
+        <v>0.319213654389241</v>
       </c>
       <c r="S63" t="n">
-        <v>9.050655155433104e-08</v>
+        <v>0.3210355703399794</v>
       </c>
       <c r="T63" t="n">
-        <v>9.127234042997738e-08</v>
+        <v>0.3228678848989411</v>
       </c>
       <c r="U63" t="n">
-        <v>9.204460875481269e-08</v>
+        <v>0.3247106574163134</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>0.7307196969696972</v>
+        <v>0.7267610062893085</v>
       </c>
       <c r="B64" t="n">
-        <v>7.390816528906477e-08</v>
+        <v>0.2739582373577999</v>
       </c>
       <c r="C64" t="n">
-        <v>7.453351284485824e-08</v>
+        <v>0.2755218574461489</v>
       </c>
       <c r="D64" t="n">
-        <v>7.516415155574952e-08</v>
+        <v>0.2770944019158353</v>
       </c>
       <c r="E64" t="n">
-        <v>7.580012619095849e-08</v>
+        <v>0.278675921702878</v>
       </c>
       <c r="F64" t="n">
-        <v>7.644148189850394e-08</v>
+        <v>0.2802664680340134</v>
       </c>
       <c r="G64" t="n">
-        <v>7.708826420840838e-08</v>
+        <v>0.281866092428356</v>
       </c>
       <c r="H64" t="n">
-        <v>7.774051903593043e-08</v>
+        <v>0.2834748466990655</v>
       </c>
       <c r="I64" t="n">
-        <v>7.839829268482426e-08</v>
+        <v>0.2850927829550264</v>
       </c>
       <c r="J64" t="n">
-        <v>7.906163185062668e-08</v>
+        <v>0.2867199536025351</v>
       </c>
       <c r="K64" t="n">
-        <v>7.973058362397219e-08</v>
+        <v>0.2883564113469974</v>
       </c>
       <c r="L64" t="n">
-        <v>8.040519549393587e-08</v>
+        <v>0.2900022091946362</v>
       </c>
       <c r="M64" t="n">
-        <v>8.108551535140458e-08</v>
+        <v>0.291657400454208</v>
       </c>
       <c r="N64" t="n">
-        <v>8.177159149247686e-08</v>
+        <v>0.2933220387387296</v>
       </c>
       <c r="O64" t="n">
-        <v>8.246347262189153e-08</v>
+        <v>0.294996177967215</v>
       </c>
       <c r="P64" t="n">
-        <v>8.316120785648506e-08</v>
+        <v>0.2966798723664211</v>
       </c>
       <c r="Q64" t="n">
-        <v>8.386484672867852e-08</v>
+        <v>0.2983731764726054</v>
       </c>
       <c r="R64" t="n">
-        <v>8.457443918999393e-08</v>
+        <v>0.3000761451332912</v>
       </c>
       <c r="S64" t="n">
-        <v>8.529003561460025e-08</v>
+        <v>0.3017888335090452</v>
       </c>
       <c r="T64" t="n">
-        <v>8.601168680288944e-08</v>
+        <v>0.3035112970752635</v>
       </c>
       <c r="U64" t="n">
-        <v>8.673944398508296e-08</v>
+        <v>0.3052435916239684</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>0.7439835858585864</v>
+        <v>0.7397746331236893</v>
       </c>
       <c r="B65" t="n">
-        <v>6.983982591535478e-08</v>
+        <v>0.2620773954315689</v>
       </c>
       <c r="C65" t="n">
-        <v>7.043075066991191e-08</v>
+        <v>0.263573205465066</v>
       </c>
       <c r="D65" t="n">
-        <v>7.102667532332294e-08</v>
+        <v>0.2650775528531588</v>
       </c>
       <c r="E65" t="n">
-        <v>7.162764218044702e-08</v>
+        <v>0.2665904863229063</v>
       </c>
       <c r="F65" t="n">
-        <v>7.223369390409088e-08</v>
+        <v>0.2681120548794771</v>
       </c>
       <c r="G65" t="n">
-        <v>7.284487351803727e-08</v>
+        <v>0.2696423078077385</v>
       </c>
       <c r="H65" t="n">
-        <v>7.34612244100994e-08</v>
+        <v>0.271181294673851</v>
       </c>
       <c r="I65" t="n">
-        <v>7.408279033520091e-08</v>
+        <v>0.2727290653268748</v>
       </c>
       <c r="J65" t="n">
-        <v>7.470961541848209e-08</v>
+        <v>0.2742856699003844</v>
       </c>
       <c r="K65" t="n">
-        <v>7.534174415843243e-08</v>
+        <v>0.2758511588140919</v>
       </c>
       <c r="L65" t="n">
-        <v>7.597922143004948e-08</v>
+        <v>0.2774255827754811</v>
       </c>
       <c r="M65" t="n">
-        <v>7.662209248802449e-08</v>
+        <v>0.279008992781449</v>
       </c>
       <c r="N65" t="n">
-        <v>7.727040296995519e-08</v>
+        <v>0.2806014401199583</v>
       </c>
       <c r="O65" t="n">
-        <v>7.792419889958557e-08</v>
+        <v>0.2822029763716981</v>
       </c>
       <c r="P65" t="n">
-        <v>7.858352669007304e-08</v>
+        <v>0.2838136534117549</v>
       </c>
       <c r="Q65" t="n">
-        <v>7.924843314728338e-08</v>
+        <v>0.2854335234112935</v>
       </c>
       <c r="R65" t="n">
-        <v>7.991896547311353e-08</v>
+        <v>0.2870626388392455</v>
       </c>
       <c r="S65" t="n">
-        <v>8.059517126884245e-08</v>
+        <v>0.2887010524640102</v>
       </c>
       <c r="T65" t="n">
-        <v>8.127709853851021e-08</v>
+        <v>0.2903488173551628</v>
       </c>
       <c r="U65" t="n">
-        <v>8.19647956923261e-08</v>
+        <v>0.2920059868851739</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>0.7548358585858581</v>
+        <v>0.7567924528301891</v>
       </c>
       <c r="B66" t="n">
-        <v>6.712759966621478e-08</v>
+        <v>0.2453044421239484</v>
       </c>
       <c r="C66" t="n">
-        <v>6.769557588661437e-08</v>
+        <v>0.2467045203153018</v>
       </c>
       <c r="D66" t="n">
-        <v>6.826835783503855e-08</v>
+        <v>0.2481125894705567</v>
       </c>
       <c r="E66" t="n">
-        <v>6.884598617343936e-08</v>
+        <v>0.2495286951982403</v>
       </c>
       <c r="F66" t="n">
-        <v>6.942850190781551e-08</v>
+        <v>0.2509528833671906</v>
       </c>
       <c r="G66" t="n">
-        <v>7.001594639112321e-08</v>
+        <v>0.2523852001080433</v>
       </c>
       <c r="H66" t="n">
-        <v>7.060836132621205e-08</v>
+        <v>0.2538256918147245</v>
       </c>
       <c r="I66" t="n">
-        <v>7.120578876878534e-08</v>
+        <v>0.2552744051459548</v>
       </c>
       <c r="J66" t="n">
-        <v>7.180827113038569e-08</v>
+        <v>0.2567313870267598</v>
       </c>
       <c r="K66" t="n">
-        <v>7.241585118140593e-08</v>
+        <v>0.25819668464999</v>
       </c>
       <c r="L66" t="n">
-        <v>7.302857205412523e-08</v>
+        <v>0.2596703454778503</v>
       </c>
       <c r="M66" t="n">
-        <v>7.364647724577112e-08</v>
+        <v>0.2611524172434363</v>
       </c>
       <c r="N66" t="n">
-        <v>7.426961062160743e-08</v>
+        <v>0.2626429479522809</v>
       </c>
       <c r="O66" t="n">
-        <v>7.489801641804827e-08</v>
+        <v>0.2641419858839094</v>
       </c>
       <c r="P66" t="n">
-        <v>7.553173924579836e-08</v>
+        <v>0.2656495795934026</v>
       </c>
       <c r="Q66" t="n">
-        <v>7.617082409301995e-08</v>
+        <v>0.2671657779129706</v>
       </c>
       <c r="R66" t="n">
-        <v>7.68153163285266e-08</v>
+        <v>0.2686906299535338</v>
       </c>
       <c r="S66" t="n">
-        <v>7.746526170500389e-08</v>
+        <v>0.2702241851063135</v>
       </c>
       <c r="T66" t="n">
-        <v>7.812070636225739e-08</v>
+        <v>0.2717664930444324</v>
       </c>
       <c r="U66" t="n">
-        <v>7.878169683048819e-08</v>
+        <v>0.2733176037245227</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>0.7668939393939386</v>
+        <v>0.7698060796645699</v>
       </c>
       <c r="B67" t="n">
-        <v>6.441537341707479e-08</v>
+        <v>0.236219092415654</v>
       </c>
       <c r="C67" t="n">
-        <v>6.496040110331681e-08</v>
+        <v>0.2375673158591794</v>
       </c>
       <c r="D67" t="n">
-        <v>6.551004034675416e-08</v>
+        <v>0.2389232343049804</v>
       </c>
       <c r="E67" t="n">
-        <v>6.606433016643172e-08</v>
+        <v>0.2402868916723794</v>
       </c>
       <c r="F67" t="n">
-        <v>6.662330991154013e-08</v>
+        <v>0.2416583321313687</v>
       </c>
       <c r="G67" t="n">
-        <v>6.718701926420913e-08</v>
+        <v>0.2430376001040416</v>
       </c>
       <c r="H67" t="n">
-        <v>6.775549824232468e-08</v>
+        <v>0.2444247402660309</v>
       </c>
       <c r="I67" t="n">
-        <v>6.832878720236977e-08</v>
+        <v>0.2458197975479564</v>
       </c>
       <c r="J67" t="n">
-        <v>6.890692684228932e-08</v>
+        <v>0.2472228171368797</v>
       </c>
       <c r="K67" t="n">
-        <v>6.948995820437943e-08</v>
+        <v>0.2486338444777681</v>
       </c>
       <c r="L67" t="n">
-        <v>7.007792267820099e-08</v>
+        <v>0.2500529252749669</v>
       </c>
       <c r="M67" t="n">
-        <v>7.067086200351774e-08</v>
+        <v>0.2514801054936793</v>
       </c>
       <c r="N67" t="n">
-        <v>7.126881827325965e-08</v>
+        <v>0.2529154313614556</v>
       </c>
       <c r="O67" t="n">
-        <v>7.187183393651097e-08</v>
+        <v>0.2543589493696904</v>
       </c>
       <c r="P67" t="n">
-        <v>7.247995180152369e-08</v>
+        <v>0.2558107062751283</v>
       </c>
       <c r="Q67" t="n">
-        <v>7.309321503875651e-08</v>
+        <v>0.2572707491013791</v>
       </c>
       <c r="R67" t="n">
-        <v>7.371166718393966e-08</v>
+        <v>0.2587391251404398</v>
       </c>
       <c r="S67" t="n">
-        <v>7.433535214116536e-08</v>
+        <v>0.2602158819542277</v>
       </c>
       <c r="T67" t="n">
-        <v>7.496431418600457e-08</v>
+        <v>0.26170106737612</v>
       </c>
       <c r="U67" t="n">
-        <v>7.559859796865028e-08</v>
+        <v>0.2631947295125033</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>0.782569444444445</v>
+        <v>0.7828197064989523</v>
       </c>
       <c r="B68" t="n">
-        <v>6.147712831383981e-08</v>
+        <v>0.2278326157618438</v>
       </c>
       <c r="C68" t="n">
-        <v>6.19972950880778e-08</v>
+        <v>0.2291329732842973</v>
       </c>
       <c r="D68" t="n">
-        <v>6.252186306777942e-08</v>
+        <v>0.2304407526136793</v>
       </c>
       <c r="E68" t="n">
-        <v>6.305086949217343e-08</v>
+        <v>0.2317559961100464</v>
       </c>
       <c r="F68" t="n">
-        <v>6.358435191557514e-08</v>
+        <v>0.2330787463752254</v>
       </c>
       <c r="G68" t="n">
-        <v>6.412234821005223e-08</v>
+        <v>0.234409046254194</v>
       </c>
       <c r="H68" t="n">
-        <v>6.46648965681134e-08</v>
+        <v>0.2357469388364677</v>
       </c>
       <c r="I68" t="n">
-        <v>6.521203550541957e-08</v>
+        <v>0.2370924674574964</v>
       </c>
       <c r="J68" t="n">
-        <v>6.576380386351823e-08</v>
+        <v>0.2384456757000674</v>
       </c>
       <c r="K68" t="n">
-        <v>6.632024081260073e-08</v>
+        <v>0.2398066073957171</v>
       </c>
       <c r="L68" t="n">
-        <v>6.688138585428304e-08</v>
+        <v>0.2411753066261514</v>
       </c>
       <c r="M68" t="n">
-        <v>6.744727882440991e-08</v>
+        <v>0.2425518177246729</v>
       </c>
       <c r="N68" t="n">
-        <v>6.80179598958829e-08</v>
+        <v>0.243936185277617</v>
       </c>
       <c r="O68" t="n">
-        <v>6.859346958151222e-08</v>
+        <v>0.2453284541257961</v>
       </c>
       <c r="P68" t="n">
-        <v>6.917384873689278e-08</v>
+        <v>0.2467286693659522</v>
       </c>
       <c r="Q68" t="n">
-        <v>6.975913856330447e-08</v>
+        <v>0.2481368763522177</v>
       </c>
       <c r="R68" t="n">
-        <v>7.034938061063716e-08</v>
+        <v>0.249553120697584</v>
       </c>
       <c r="S68" t="n">
-        <v>7.094461678034027e-08</v>
+        <v>0.2509774482753794</v>
       </c>
       <c r="T68" t="n">
-        <v>7.154488932839734e-08</v>
+        <v>0.2524099052207548</v>
       </c>
       <c r="U68" t="n">
-        <v>7.215024086832588e-08</v>
+        <v>0.2538505379321778</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>0.7922159090909094</v>
+        <v>0.798836477987422</v>
       </c>
       <c r="B69" t="n">
-        <v>5.966897748107972e-08</v>
+        <v>0.216650646890097</v>
       </c>
       <c r="C69" t="n">
-        <v>6.0173845232546e-08</v>
+        <v>0.2178871831844546</v>
       </c>
       <c r="D69" t="n">
-        <v>6.06829847422564e-08</v>
+        <v>0.219130777025278</v>
       </c>
       <c r="E69" t="n">
-        <v>6.119643215416822e-08</v>
+        <v>0.2203814686936025</v>
       </c>
       <c r="F69" t="n">
-        <v>6.171422391805812e-08</v>
+        <v>0.2216392987003679</v>
       </c>
       <c r="G69" t="n">
-        <v>6.223639679210942e-08</v>
+        <v>0.2229043077877305</v>
       </c>
       <c r="H69" t="n">
-        <v>6.276298784552173e-08</v>
+        <v>0.2241765369303835</v>
       </c>
       <c r="I69" t="n">
-        <v>6.329403446114242e-08</v>
+        <v>0.2254560273368832</v>
       </c>
       <c r="J69" t="n">
-        <v>6.382957433812052e-08</v>
+        <v>0.2267428204509844</v>
       </c>
       <c r="K69" t="n">
-        <v>6.436964549458296e-08</v>
+        <v>0.2280369579529826</v>
       </c>
       <c r="L69" t="n">
-        <v>6.491428627033344e-08</v>
+        <v>0.2293384817610644</v>
       </c>
       <c r="M69" t="n">
-        <v>6.546353532957422e-08</v>
+        <v>0.2306474340326646</v>
       </c>
       <c r="N69" t="n">
-        <v>6.601743166365094e-08</v>
+        <v>0.2319638571658322</v>
       </c>
       <c r="O69" t="n">
-        <v>6.657601459382057e-08</v>
+        <v>0.2332877938006037</v>
       </c>
       <c r="P69" t="n">
-        <v>6.713932377404288e-08</v>
+        <v>0.2346192868203841</v>
       </c>
       <c r="Q69" t="n">
-        <v>6.77073991937954e-08</v>
+        <v>0.2359583793533359</v>
       </c>
       <c r="R69" t="n">
-        <v>6.828028118091242e-08</v>
+        <v>0.2373051147737763</v>
       </c>
       <c r="S69" t="n">
-        <v>6.885801040444781e-08</v>
+        <v>0.2386595367035818</v>
       </c>
       <c r="T69" t="n">
-        <v>6.944062787756202e-08</v>
+        <v>0.2400216890136013</v>
       </c>
       <c r="U69" t="n">
-        <v>7.002817496043383e-08</v>
+        <v>0.2413916158250771</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>0.8090972222222216</v>
+        <v>0.8098480083857441</v>
       </c>
       <c r="B70" t="n">
-        <v>5.718277008603473e-08</v>
+        <v>0.2117585355087076</v>
       </c>
       <c r="C70" t="n">
-        <v>5.766660168118992e-08</v>
+        <v>0.2129671500157733</v>
       </c>
       <c r="D70" t="n">
-        <v>5.815452704466237e-08</v>
+        <v>0.2141826627053524</v>
       </c>
       <c r="E70" t="n">
-        <v>5.864658081441122e-08</v>
+        <v>0.2154051129489082</v>
       </c>
       <c r="F70" t="n">
-        <v>5.914279792147237e-08</v>
+        <v>0.2166345403426175</v>
       </c>
       <c r="G70" t="n">
-        <v>5.964321359243819e-08</v>
+        <v>0.2178709847086527</v>
       </c>
       <c r="H70" t="n">
-        <v>6.014786335195832e-08</v>
+        <v>0.2191144860964716</v>
       </c>
       <c r="I70" t="n">
-        <v>6.065678302526148e-08</v>
+        <v>0.2203650847841148</v>
       </c>
       <c r="J70" t="n">
-        <v>6.117000874069883e-08</v>
+        <v>0.2216228212795106</v>
       </c>
       <c r="K70" t="n">
-        <v>6.168757693230866e-08</v>
+        <v>0.2228877363217862</v>
       </c>
       <c r="L70" t="n">
-        <v>6.220952434240287e-08</v>
+        <v>0.2241598708825887</v>
       </c>
       <c r="M70" t="n">
-        <v>6.27358880241753e-08</v>
+        <v>0.2254392661674108</v>
       </c>
       <c r="N70" t="n">
-        <v>6.326670534433216e-08</v>
+        <v>0.2267259636169263</v>
       </c>
       <c r="O70" t="n">
-        <v>6.380201398574472e-08</v>
+        <v>0.228020004908332</v>
       </c>
       <c r="P70" t="n">
-        <v>6.434185195012442e-08</v>
+        <v>0.229321431956698</v>
       </c>
       <c r="Q70" t="n">
-        <v>6.48862575607206e-08</v>
+        <v>0.2306302869163251</v>
       </c>
       <c r="R70" t="n">
-        <v>6.543526946504107e-08</v>
+        <v>0.2319466121821103</v>
       </c>
       <c r="S70" t="n">
-        <v>6.598892663759581e-08</v>
+        <v>0.2332704503909202</v>
       </c>
       <c r="T70" t="n">
-        <v>6.65472683826636e-08</v>
+        <v>0.2346018444229715</v>
       </c>
       <c r="U70" t="n">
-        <v>6.711033433708243e-08</v>
+        <v>0.2359408374032205</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>0.825978535353535</v>
+        <v>0.8318710691823901</v>
       </c>
       <c r="B71" t="n">
-        <v>5.537461925327473e-08</v>
+        <v>0.2040709319093817</v>
       </c>
       <c r="C71" t="n">
-        <v>5.584315182565823e-08</v>
+        <v>0.2052356693221314</v>
       </c>
       <c r="D71" t="n">
-        <v>5.631564871913945e-08</v>
+        <v>0.2064070544883264</v>
       </c>
       <c r="E71" t="n">
-        <v>5.679214347640612e-08</v>
+        <v>0.207585125350103</v>
       </c>
       <c r="F71" t="n">
-        <v>5.727266992395545e-08</v>
+        <v>0.2087699200661529</v>
       </c>
       <c r="G71" t="n">
-        <v>5.775726217449547e-08</v>
+        <v>0.2099614770129591</v>
       </c>
       <c r="H71" t="n">
-        <v>5.824595462936674e-08</v>
+        <v>0.2111598347860387</v>
       </c>
       <c r="I71" t="n">
-        <v>5.873878198098444e-08</v>
+        <v>0.2123650322011932</v>
       </c>
       <c r="J71" t="n">
-        <v>5.923577921530123e-08</v>
+        <v>0.213577108295766</v>
       </c>
       <c r="K71" t="n">
-        <v>5.973698161429099e-08</v>
+        <v>0.2147961023299062</v>
       </c>
       <c r="L71" t="n">
-        <v>6.024242475845337e-08</v>
+        <v>0.2160220537878413</v>
       </c>
       <c r="M71" t="n">
-        <v>6.075214452933971e-08</v>
+        <v>0.217255002379155</v>
       </c>
       <c r="N71" t="n">
-        <v>6.126617711210031e-08</v>
+        <v>0.2184949880400742</v>
       </c>
       <c r="O71" t="n">
-        <v>6.178455899805318e-08</v>
+        <v>0.2197420509347623</v>
       </c>
       <c r="P71" t="n">
-        <v>6.230732698727464e-08</v>
+        <v>0.2209962314566198</v>
       </c>
       <c r="Q71" t="n">
-        <v>6.283451819121163e-08</v>
+        <v>0.2222575702295939</v>
       </c>
       <c r="R71" t="n">
-        <v>6.336617003531645e-08</v>
+        <v>0.2235261081094925</v>
       </c>
       <c r="S71" t="n">
-        <v>6.390232026170345e-08</v>
+        <v>0.2248018861853093</v>
       </c>
       <c r="T71" t="n">
-        <v>6.444300693182838e-08</v>
+        <v>0.2260849457805535</v>
       </c>
       <c r="U71" t="n">
-        <v>6.498826842919049e-08</v>
+        <v>0.2273753284545888</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>0.8452714646464644</v>
+        <v>0.8428825995807123</v>
       </c>
       <c r="B72" t="n">
-        <v>5.379248727460973e-08</v>
+        <v>0.201275439691445</v>
       </c>
       <c r="C72" t="n">
-        <v>5.424763320206799e-08</v>
+        <v>0.2024242217971708</v>
       </c>
       <c r="D72" t="n">
-        <v>5.470663018430689e-08</v>
+        <v>0.2035795605912261</v>
       </c>
       <c r="E72" t="n">
-        <v>5.516951080565166e-08</v>
+        <v>0.2047414934959922</v>
       </c>
       <c r="F72" t="n">
-        <v>5.563630792612815e-08</v>
+        <v>0.2059100581474386</v>
       </c>
       <c r="G72" t="n">
-        <v>5.610705468379561e-08</v>
+        <v>0.2070852923963434</v>
       </c>
       <c r="H72" t="n">
-        <v>5.658178449709912e-08</v>
+        <v>0.2082672343095177</v>
       </c>
       <c r="I72" t="n">
-        <v>5.706053106724202e-08</v>
+        <v>0.20945592217104</v>
       </c>
       <c r="J72" t="n">
-        <v>5.754332838057835e-08</v>
+        <v>0.2106513944834953</v>
       </c>
       <c r="K72" t="n">
-        <v>5.803021071102553e-08</v>
+        <v>0.2118536899692227</v>
       </c>
       <c r="L72" t="n">
-        <v>5.852121262249756e-08</v>
+        <v>0.2130628475715696</v>
       </c>
       <c r="M72" t="n">
-        <v>5.901636897135858e-08</v>
+        <v>0.214278906456153</v>
       </c>
       <c r="N72" t="n">
-        <v>5.951571490889743e-08</v>
+        <v>0.2155019060121281</v>
       </c>
       <c r="O72" t="n">
-        <v>6.001928588382309e-08</v>
+        <v>0.2167318858534643</v>
       </c>
       <c r="P72" t="n">
-        <v>6.052711764478108e-08</v>
+        <v>0.2179688858202279</v>
       </c>
       <c r="Q72" t="n">
-        <v>6.10392462428913e-08</v>
+        <v>0.2192129459798735</v>
       </c>
       <c r="R72" t="n">
-        <v>6.155570803430741e-08</v>
+        <v>0.2204641066285407</v>
       </c>
       <c r="S72" t="n">
-        <v>6.207653968279763e-08</v>
+        <v>0.22172240829236</v>
       </c>
       <c r="T72" t="n">
-        <v>6.260177816234757e-08</v>
+        <v>0.2229878917287652</v>
       </c>
       <c r="U72" t="n">
-        <v>6.313146075978503e-08</v>
+        <v>0.2242605979278137</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>0.8621527777777779</v>
+        <v>0.8609014675052404</v>
       </c>
       <c r="B73" t="n">
-        <v>5.288841185822983e-08</v>
+        <v>0.1970822013645399</v>
       </c>
       <c r="C73" t="n">
-        <v>5.333590827430223e-08</v>
+        <v>0.1982070505097298</v>
       </c>
       <c r="D73" t="n">
-        <v>5.378719102154553e-08</v>
+        <v>0.1993383197455756</v>
       </c>
       <c r="E73" t="n">
-        <v>5.42422921366492e-08</v>
+        <v>0.2004760457148257</v>
       </c>
       <c r="F73" t="n">
-        <v>5.470124392736979e-08</v>
+        <v>0.201620265269367</v>
       </c>
       <c r="G73" t="n">
-        <v>5.516407897482435e-08</v>
+        <v>0.2027710154714195</v>
       </c>
       <c r="H73" t="n">
-        <v>5.563083013580343e-08</v>
+        <v>0.2039283335947361</v>
       </c>
       <c r="I73" t="n">
-        <v>5.61015305451036e-08</v>
+        <v>0.20509225712581</v>
       </c>
       <c r="J73" t="n">
-        <v>5.657621361787964e-08</v>
+        <v>0.2062628237650892</v>
       </c>
       <c r="K73" t="n">
-        <v>5.70549130520168e-08</v>
+        <v>0.2074400714281973</v>
       </c>
       <c r="L73" t="n">
-        <v>5.753766283052291e-08</v>
+        <v>0.2086240382471619</v>
       </c>
       <c r="M73" t="n">
-        <v>5.802449722394088e-08</v>
+        <v>0.2098147625716498</v>
       </c>
       <c r="N73" t="n">
-        <v>5.851545079278161e-08</v>
+        <v>0.2110122829702088</v>
       </c>
       <c r="O73" t="n">
-        <v>5.901055838997743e-08</v>
+        <v>0.2122166382315171</v>
       </c>
       <c r="P73" t="n">
-        <v>5.950985516335629e-08</v>
+        <v>0.2134278673656398</v>
       </c>
       <c r="Q73" t="n">
-        <v>6.001337655813693e-08</v>
+        <v>0.2146460096052928</v>
       </c>
       <c r="R73" t="n">
-        <v>6.05211583194452e-08</v>
+        <v>0.2158711044071127</v>
       </c>
       <c r="S73" t="n">
-        <v>6.103323649485155e-08</v>
+        <v>0.2171031914529358</v>
       </c>
       <c r="T73" t="n">
-        <v>6.154964743693007e-08</v>
+        <v>0.2183423106510826</v>
       </c>
       <c r="U73" t="n">
-        <v>6.207042780583918e-08</v>
+        <v>0.2195885021376509</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>0.8742108585858583</v>
+        <v>0.8779192872117404</v>
       </c>
       <c r="B74" t="n">
-        <v>5.243637415003974e-08</v>
+        <v>0.1956844552555715</v>
       </c>
       <c r="C74" t="n">
-        <v>5.288004581041921e-08</v>
+        <v>0.1968013267472493</v>
       </c>
       <c r="D74" t="n">
-        <v>5.33274714401647e-08</v>
+        <v>0.1979245727970253</v>
       </c>
       <c r="E74" t="n">
-        <v>5.377868280214783e-08</v>
+        <v>0.19905422978777</v>
       </c>
       <c r="F74" t="n">
-        <v>5.423371192799047e-08</v>
+        <v>0.2001903343100097</v>
       </c>
       <c r="G74" t="n">
-        <v>5.469259112033857e-08</v>
+        <v>0.2013329231631115</v>
       </c>
       <c r="H74" t="n">
-        <v>5.515535295515545e-08</v>
+        <v>0.2024820333564754</v>
       </c>
       <c r="I74" t="n">
-        <v>5.562203028403424e-08</v>
+        <v>0.2036377021107332</v>
       </c>
       <c r="J74" t="n">
-        <v>5.609265623653014e-08</v>
+        <v>0.2047999668589537</v>
       </c>
       <c r="K74" t="n">
-        <v>5.656726422251228e-08</v>
+        <v>0.2059688652478553</v>
       </c>
       <c r="L74" t="n">
-        <v>5.704588793453543e-08</v>
+        <v>0.2071444351390259</v>
       </c>
       <c r="M74" t="n">
-        <v>5.752856135023189e-08</v>
+        <v>0.2083267146101486</v>
       </c>
       <c r="N74" t="n">
-        <v>5.801531873472355e-08</v>
+        <v>0.2095157419562355</v>
       </c>
       <c r="O74" t="n">
-        <v>5.850619464305444e-08</v>
+        <v>0.2107115556908679</v>
       </c>
       <c r="P74" t="n">
-        <v>5.900122392264374e-08</v>
+        <v>0.2119141945474437</v>
       </c>
       <c r="Q74" t="n">
-        <v>5.950044171575958e-08</v>
+        <v>0.2131236974804324</v>
       </c>
       <c r="R74" t="n">
-        <v>6.000388346201393e-08</v>
+        <v>0.2143401036666366</v>
       </c>
       <c r="S74" t="n">
-        <v>6.051158490087836e-08</v>
+        <v>0.215563452506461</v>
       </c>
       <c r="T74" t="n">
-        <v>6.102358207422115e-08</v>
+        <v>0.2167937836251883</v>
       </c>
       <c r="U74" t="n">
-        <v>6.153991132886609e-08</v>
+        <v>0.2180311368742632</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>0.8947095959595962</v>
+        <v>0.8929350104821799</v>
       </c>
       <c r="B75" t="n">
-        <v>5.243637415003974e-08</v>
+        <v>0.1963833283100557</v>
       </c>
       <c r="C75" t="n">
-        <v>5.288004581041921e-08</v>
+        <v>0.1975041886284896</v>
       </c>
       <c r="D75" t="n">
-        <v>5.33274714401647e-08</v>
+        <v>0.1986314462713004</v>
       </c>
       <c r="E75" t="n">
-        <v>5.377868280214783e-08</v>
+        <v>0.1997651377512978</v>
       </c>
       <c r="F75" t="n">
-        <v>5.423371192799047e-08</v>
+        <v>0.2009052997896884</v>
       </c>
       <c r="G75" t="n">
-        <v>5.469259112033857e-08</v>
+        <v>0.2020519693172655</v>
       </c>
       <c r="H75" t="n">
-        <v>5.515535295515545e-08</v>
+        <v>0.2032051834756058</v>
       </c>
       <c r="I75" t="n">
-        <v>5.562203028403424e-08</v>
+        <v>0.2043649796182716</v>
       </c>
       <c r="J75" t="n">
-        <v>5.609265623653014e-08</v>
+        <v>0.2055313953120214</v>
       </c>
       <c r="K75" t="n">
-        <v>5.656726422251228e-08</v>
+        <v>0.2067044683380263</v>
       </c>
       <c r="L75" t="n">
-        <v>5.704588793453543e-08</v>
+        <v>0.2078842366930939</v>
       </c>
       <c r="M75" t="n">
-        <v>5.752856135023189e-08</v>
+        <v>0.2090707385908992</v>
       </c>
       <c r="N75" t="n">
-        <v>5.801531873472355e-08</v>
+        <v>0.2102640124632222</v>
       </c>
       <c r="O75" t="n">
-        <v>5.850619464305444e-08</v>
+        <v>0.2114640969611925</v>
       </c>
       <c r="P75" t="n">
-        <v>5.900122392264374e-08</v>
+        <v>0.2126710309565418</v>
       </c>
       <c r="Q75" t="n">
-        <v>5.950044171575958e-08</v>
+        <v>0.2138848535428627</v>
       </c>
       <c r="R75" t="n">
-        <v>6.000388346201393e-08</v>
+        <v>0.2151056040368747</v>
       </c>
       <c r="S75" t="n">
-        <v>6.051158490087836e-08</v>
+        <v>0.2163333219796984</v>
       </c>
       <c r="T75" t="n">
-        <v>6.102358207422115e-08</v>
+        <v>0.2175680471381354</v>
       </c>
       <c r="U75" t="n">
-        <v>6.153991132886609e-08</v>
+        <v>0.2188098195059571</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>0.9115909090909097</v>
+        <v>0.9119549266247383</v>
       </c>
       <c r="B76" t="n">
-        <v>5.243637415003974e-08</v>
+        <v>0.1963833283100557</v>
       </c>
       <c r="C76" t="n">
-        <v>5.288004581041921e-08</v>
+        <v>0.1975041886284896</v>
       </c>
       <c r="D76" t="n">
-        <v>5.33274714401647e-08</v>
+        <v>0.1986314462713004</v>
       </c>
       <c r="E76" t="n">
-        <v>5.377868280214783e-08</v>
+        <v>0.1997651377512978</v>
       </c>
       <c r="F76" t="n">
-        <v>5.423371192799047e-08</v>
+        <v>0.2009052997896884</v>
       </c>
       <c r="G76" t="n">
-        <v>5.469259112033857e-08</v>
+        <v>0.2020519693172655</v>
       </c>
       <c r="H76" t="n">
-        <v>5.515535295515545e-08</v>
+        <v>0.2032051834756058</v>
       </c>
       <c r="I76" t="n">
-        <v>5.562203028403424e-08</v>
+        <v>0.2043649796182716</v>
       </c>
       <c r="J76" t="n">
-        <v>5.609265623653014e-08</v>
+        <v>0.2055313953120214</v>
       </c>
       <c r="K76" t="n">
-        <v>5.656726422251228e-08</v>
+        <v>0.2067044683380263</v>
       </c>
       <c r="L76" t="n">
-        <v>5.704588793453543e-08</v>
+        <v>0.2078842366930939</v>
       </c>
       <c r="M76" t="n">
-        <v>5.752856135023189e-08</v>
+        <v>0.2090707385908992</v>
       </c>
       <c r="N76" t="n">
-        <v>5.801531873472355e-08</v>
+        <v>0.2102640124632222</v>
       </c>
       <c r="O76" t="n">
-        <v>5.850619464305444e-08</v>
+        <v>0.2114640969611925</v>
       </c>
       <c r="P76" t="n">
-        <v>5.900122392264374e-08</v>
+        <v>0.2126710309565418</v>
       </c>
       <c r="Q76" t="n">
-        <v>5.950044171575958e-08</v>
+        <v>0.2138848535428627</v>
       </c>
       <c r="R76" t="n">
-        <v>6.000388346201393e-08</v>
+        <v>0.2151056040368747</v>
       </c>
       <c r="S76" t="n">
-        <v>6.051158490087836e-08</v>
+        <v>0.2163333219796984</v>
       </c>
       <c r="T76" t="n">
-        <v>6.102358207422115e-08</v>
+        <v>0.2175680471381354</v>
       </c>
       <c r="U76" t="n">
-        <v>6.153991132886609e-08</v>
+        <v>0.2188098195059571</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>0.9296780303030304</v>
+        <v>0.9339779874213843</v>
       </c>
       <c r="B77" t="n">
-        <v>5.221035529594483e-08</v>
+        <v>0.1963833283100557</v>
       </c>
       <c r="C77" t="n">
-        <v>5.265211457847784e-08</v>
+        <v>0.1975041886284896</v>
       </c>
       <c r="D77" t="n">
-        <v>5.309761164947443e-08</v>
+        <v>0.1986314462713004</v>
       </c>
       <c r="E77" t="n">
-        <v>5.354687813489729e-08</v>
+        <v>0.1997651377512978</v>
       </c>
       <c r="F77" t="n">
-        <v>5.399994592830095e-08</v>
+        <v>0.2009052997896884</v>
       </c>
       <c r="G77" t="n">
-        <v>5.445684719309583e-08</v>
+        <v>0.2020519693172655</v>
       </c>
       <c r="H77" t="n">
-        <v>5.491761436483159e-08</v>
+        <v>0.2032051834756058</v>
       </c>
       <c r="I77" t="n">
-        <v>5.53822801534997e-08</v>
+        <v>0.2043649796182716</v>
       </c>
       <c r="J77" t="n">
-        <v>5.585087754585555e-08</v>
+        <v>0.2055313953120214</v>
       </c>
       <c r="K77" t="n">
-        <v>5.632343980776017e-08</v>
+        <v>0.2067044683380263</v>
       </c>
       <c r="L77" t="n">
-        <v>5.680000048654185e-08</v>
+        <v>0.2078842366930939</v>
       </c>
       <c r="M77" t="n">
-        <v>5.728059341337754e-08</v>
+        <v>0.2090707385908992</v>
       </c>
       <c r="N77" t="n">
-        <v>5.776525270569467e-08</v>
+        <v>0.2102640124632222</v>
       </c>
       <c r="O77" t="n">
-        <v>5.82540127695931e-08</v>
+        <v>0.2114640969611925</v>
       </c>
       <c r="P77" t="n">
-        <v>5.874690830228762e-08</v>
+        <v>0.2126710309565418</v>
       </c>
       <c r="Q77" t="n">
-        <v>5.924397429457107e-08</v>
+        <v>0.2138848535428627</v>
       </c>
       <c r="R77" t="n">
-        <v>5.974524603329847e-08</v>
+        <v>0.2151056040368747</v>
       </c>
       <c r="S77" t="n">
-        <v>6.025075910389193e-08</v>
+        <v>0.2163333219796984</v>
       </c>
       <c r="T77" t="n">
-        <v>6.076054939286687e-08</v>
+        <v>0.2175680471381354</v>
       </c>
       <c r="U77" t="n">
-        <v>6.127465309037971e-08</v>
+        <v>0.2188098195059571</v>
       </c>
     </row>
     <row r="78">
@@ -5943,64 +5454,64 @@
         <v>0.955</v>
       </c>
       <c r="B78" t="n">
-        <v>5.288841185822983e-08</v>
+        <v>0.1977810744190238</v>
       </c>
       <c r="C78" t="n">
-        <v>5.333590827430223e-08</v>
+        <v>0.1989099123909697</v>
       </c>
       <c r="D78" t="n">
-        <v>5.378719102154553e-08</v>
+        <v>0.2000451932198504</v>
       </c>
       <c r="E78" t="n">
-        <v>5.42422921366492e-08</v>
+        <v>0.2011869536783531</v>
       </c>
       <c r="F78" t="n">
-        <v>5.470124392736979e-08</v>
+        <v>0.2023352307490453</v>
       </c>
       <c r="G78" t="n">
-        <v>5.516407897482435e-08</v>
+        <v>0.2034900616255732</v>
       </c>
       <c r="H78" t="n">
-        <v>5.563083013580343e-08</v>
+        <v>0.2046514837138661</v>
       </c>
       <c r="I78" t="n">
-        <v>5.61015305451036e-08</v>
+        <v>0.2058195346333481</v>
       </c>
       <c r="J78" t="n">
-        <v>5.657621361787964e-08</v>
+        <v>0.2069942522181566</v>
       </c>
       <c r="K78" t="n">
-        <v>5.70549130520168e-08</v>
+        <v>0.2081756745183679</v>
       </c>
       <c r="L78" t="n">
-        <v>5.753766283052291e-08</v>
+        <v>0.2093638398012296</v>
       </c>
       <c r="M78" t="n">
-        <v>5.802449722394088e-08</v>
+        <v>0.2105587865524</v>
       </c>
       <c r="N78" t="n">
-        <v>5.851545079278161e-08</v>
+        <v>0.211760553477195</v>
       </c>
       <c r="O78" t="n">
-        <v>5.901055838997743e-08</v>
+        <v>0.2129691795018413</v>
       </c>
       <c r="P78" t="n">
-        <v>5.950985516335629e-08</v>
+        <v>0.2141847037747376</v>
       </c>
       <c r="Q78" t="n">
-        <v>6.001337655813693e-08</v>
+        <v>0.2154071656677226</v>
       </c>
       <c r="R78" t="n">
-        <v>6.05211583194452e-08</v>
+        <v>0.2166366047773504</v>
       </c>
       <c r="S78" t="n">
-        <v>6.103323649485155e-08</v>
+        <v>0.2178730609261729</v>
       </c>
       <c r="T78" t="n">
-        <v>6.154964743693007e-08</v>
+        <v>0.2191165741640294</v>
       </c>
       <c r="U78" t="n">
-        <v>6.207042780583918e-08</v>
+        <v>0.2203671847693444</v>
       </c>
     </row>
   </sheetData>
